--- a/noticias/piura/excel/noticias_piura_20261005_20261012.xlsx
+++ b/noticias/piura/excel/noticias_piura_20261005_20261012.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -470,10 +470,128 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Sechura: Pescadores rechazan la licitación del Lote Z-69</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>En una conferencia de prensa realizada en la sede de la Municipalidad Provincial de Sechura , dirigentes de los 11 gremios pesqueros que integran el Comité de Gestión de Pesca y Acuicultura (COGPESCA) alzaron su voz de protesta contra la decisión del Gobierno central de someter a concurso internacional la licitación del Lote Z-69. PUEDES LEER ► Cura Mori: Peregrino del Señor Cautivo muere tras despiste de motofurgón La medida busca adjudicar la explotación de hidrocarburos en el mar por un periodo de 30 años, abarcando amplias zonas pesqueras de Vice y Sechura . Los representantes del sector recordaron que la extracción de petróleo científicamente es incompatible con la pesca artesanal, la pesca industrial y la maricultura. Esta última actividad genera empleo masivo en la zona y abastece el 90% de la oferta nacional de exportación de concha de abanico, además de aportar decisivamente a la soberanía alimentaria del país. Ante esta situación, los gremios pesqueros interpusieron una demanda de acción de amparo en el Poder Judicial, la cual ya ha sido admitida y cuya audiencia quedó fijada para el próximo 22 de octubre. El asesor legal del comité, el abogado Carlos Bancayán Saavedra , sustentó la demanda en la vulneración del derecho constitucional a un ambiente sano y equilibrado, invocando el principio precautorio establecido en la Ley General del Ambiente. El abogado advirtió que la infraestructura del Lote Z-69 proviene de las décadas de 1970 y 1980 , acumulando entre 40 y 50 años de antigüedad sin modernización, lo que representa un elevadísimo riesgo de derrames similares a los ocurridos en Talara y Ventanilla.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/sechura-pescadores-rechazan-la-licitacion-del-lote-z-69/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fenómeno El Niño: el mar frente a Talara está caliente y temperatura llega a los 26.4 °C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>De acuerdo con la información difundida, estas condiciones favorecen temperaturas del aire superiores a lo habitual, tanto durante el día como por la noche.
+Si persisten las anomalías positivas del mar, se prevé que las temperaturas del aire continúen elevadas durante las próximas semanas.
+Lea también: ¿Un aluvión como el ocurrido en Chile podría suceder en el Perú? Esto revela el Senamhi Sobre este tema, el especialista en Meteorología del Servicio Nacional de Meteorología e Hidrología (Senamhi), Nelson Quispe, explicó que, para evaluar el potencial de lluvias en la costa norte, es importante observar la temperatura absoluta del mar y no únicamente sus anomalías respecto de los valores habituales.
+Detalló que, cuando la temperatura superficial del mar supera los 26 grados Celsius, la atmósfera puede volverse más inestable y aumentar la posibilidad de formación de nubes que generen precipitaciones.
+Lea también: El Niño: previsiones del Senamhi dan cuenta de temperaturas de 40 grados en costa norte “Lo que debemos fijarnos ahora es el valor absoluto de la temperatura.
+Ese valor absoluto es que esté por encima de los 26 grados, 26.5 o 27 grados.
+Ese es el valor que debemos observar ahora”, manifestó.
+El especialista indicó que esta condición ya se registra en Tumbes, mientras que el calentamiento se extiende hacia el extremo norte de Piura; y agregó que cuando las temperaturas de alrededor de 26 grados abarquen Tumbes, Piura y Lambayeque, podrán comenzar a presentarse lluvias más generalizadas en esa zona.
+Senamhi advierte temperaturas de hasta 36 °C La Dirección Zonal 01 del Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) emitió el Aviso Meteorológico Regional N.° 181 por el incremento de la temperatura diurna en la costa y sierra norte, vigente del 10 al 13 de octubre.
+El pronóstico contempla temperaturas máximas de entre 25 °C y 36 °C en la costa norte, y de entre 22 °C y 33 °C en la sierra norte.
+También se prevé escasa nubosidad hacia el mediodía, condición que favorecerá el aumento de la radiación ultravioleta (UV), además de ráfagas de viento cercanas a los 40 kilómetros por hora, principalmente por la tarde.
+No se descartan lluvias dispersas en la costa norte.
+Prevén lluvias y lloviznas en la región El Senamhi también publicó el Aviso Meteorológico Regional N.° 182 por lloviznas en la costa norte, previsto para el 13 y 14 de octubre.
+El evento estará acompañado por un incremento de la velocidad del viento y presencia de niebla y neblina en sectores cercanos al litoral, principalmente durante la noche, la madrugada y las primeras horas de la mañana.
+A estas condiciones se suma el Aviso Meteorológico Regional N.° 183, que pronostica lluvias de ligera a moderada intensidad en la costa y sierra norte entre el 12 y el 13 de octubre, acompañadas de ráfagas de viento cercanas a los 40 kilómetros por hora.
+Los acumulados previstos son de alrededor de 17 milímetros por día en la costa norte y de entre 8 y 17 milímetros por día en la sierra norte.
+Las condiciones previstas combinan temperaturas elevadas, alta radiación UV, viento y precipitaciones.
+La evolución del tiempo dependerá de la persistencia de estos factores durante los próximos días.
+Más en Andina:</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-fenomeno-nino-mar-frente-a-talara-esta-caliente-y-temperatura-llega-a-los-264-°c-1095606.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Resultados ONPE en región Piura al 96.028 %: aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación región Piura según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/resultados-en-piura-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>La razón por la que este 13 de octubre es un día no laborable en el Perú</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Octubre llega cada año teñido de morado en el Perú, especialmente en Lima, donde miles de fieles acompañan las tradicionales procesiones del Señor de los Milagros. Durante este mes, las calles de la capital se llenan de devoción, cánticos y muestras de fe en honor al Cristo Moreno. Sin embargo, las celebraciones de octubre no se limitan únicamente a esta emblemática tradición religiosa. El calendario también contempla otra festividad que tendrá lugar este 13 de octubre. Con motivo de esta celebración, se ha dispuesto que la fecha sea considerada día no laborable, una medida que despierta el interés de quienes buscan conocer cómo se desarrollarán las actividades durante la jornada. La coincidencia con uno de los meses más representativos de la tradición limeña añade un elemento particular al calendario. Por ello, es importante conocer qué se conmemora en esta fecha y a quiénes alcanza la disposición. Cada 13 de octubre, el departamento de Piura vive una jornada especial marcada por la fe y la tradición en honor al Señor Cautivo de Ayabaca. Desde hace cuatro años, una ordenanza regional establece un día no laborable para los trabajadores de los sectores público y privado, con el propósito de facilitar su participación en esta celebración religiosa. La festividad, reconocida como Patrimonio Cultural de la Nación, congrega a numerosos devotos que llegan para expresar su fervor y renovar sus promesas. Así, la fecha se ha convertido en una de las más significativas para la identidad religiosa de esta región. La disposición contempla que las horas dejadas de trabajar sean compensadas posteriormente, de acuerdo con las condiciones establecidas para su recuperación. De esta manera, la jornada permite que los fieles participen en las actividades dedicadas al Cristo Cautivo sin dejar de lado sus responsabilidades laborales. Cada año, la devoción moviliza a creyentes que encuentran en esta imagen un símbolo de esperanza y espiritualidad. Por ello, el 13 de octubre no solo destaca por la suspensión de labores, sino también por la profunda tradición que representa para el pueblo piurano. Durante la primera quincena de octubre, Piura se llena de fervor religioso con la celebración que reúne a miles de devotos del Señor Cautivo de Ayabaca. En medio de esta tradición católica, cada 13 de octubre se establece una jornada no laborable para los trabajadores de la región, conforme a la Ordenanza Regional 443, promulgada el 26 de agosto de 2019. La medida busca facilitar la participación de la población en las actividades conmemorativas. Sin embargo, su aplicación en el ámbito privado contempla condiciones específicas. Según el artículo 5 de la normativa, las empresas privadas “podrán acogerse a lo dispuesto en la presente ordenanza regional, previo acuerdo entre el empleador y sus trabajadores”. Esto significa que la aplicación de la jornada debe considerar el entendimiento entre ambas partes. No obstante, si no se alcanza un consenso, la decisión final sobre otorgar el día no laborable recaerá en el titular de la empresa. De esta manera, la disposición establece diferencias en su aplicación según el sector laboral, en medio de una de las celebraciones religiosas más representativas de Piura. La historia del Señor Cautivo de Ayabaca se remonta a 1751, cuando el sacerdote español de apellido García Guerrero habría decidido obsequiar a su comunidad una imagen de Jesucristo. Según la tradición más difundida, la iniciativa comenzó con un tronco de cedro que habría sangrado después de recibir el hachazo de un labrador en el cerro Sahumerio, en la zona de Jililí. Tiempo después, tres misteriosos jinetes llegaron a la provincia montados en caballos albinos y vestidos con elegantes ponchos blancos de lana. Al presentarse como talladores, aceptaron esculpir la figura religiosa, pero impusieron una condición: nadie debía observarlos ni interrumpir su trabajo. Los días transcurrieron hasta que la impaciencia de los pobladores venció la espera y, convencidos de que habían sido engañados, decidieron abrir por la fuerza el recinto donde trabajaban los visitantes. La sorpresa fue mayúscula: no encontraron a los tres hombres y la comida permanecía intacta, pero ante sus ojos se alzaba una imponente escultura de Cristo Nazareno, con las manos cruzadas y una altura de 1,80 metros. Para los habitantes de Ayabaca, los talladores eran ángeles enviados por Dios, quienes desaparecieron después de culminar aquella misteriosa obra. Desde entonces, la imagen es considerada una “obra de ángeles” y se convirtió en símbolo de fe y devoción, una tradición que tomó mayor fuerza con la inauguración del templo actual en 1904, a cargo del reverendo padre Tomás Eliseo Velásquez. Cada 13 de octubre, miles de fieles acuden a venerar al Señor Cautivo y mantener viva esta historia.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/respuestas/por-que/la-razon-por-la-que-este-13-de-octubre-es-un-dia-no-laborable-en-el-peru-tdpe-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>ERM 2026: hoy inician las audiencias de recuento de votos en diferentes JEE</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>De acuerdo con un reporte del Jurado Nacional de Elecciones (JNE), hasta el mediodía de ayer se tenían programadas 105 audiencias, siendo el JEE Lima Sur 2 el primero en realizar este procedimiento excepcional.
 Las audiencias podrán ser seguidas por el portal web del JNE , mediante los enlaces de YouTube que se encontrarán en el botón Recuento de votos ERM 2026 , así como a través del canal JNE Media (552 de Movistar) y redes sociales del ente electoral.
@@ -510,27 +628,118 @@
 La programación de audiencias puede ser vista en el botón Recuento de votos ERM 2026 del portal web del JNE.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-erm-2026-hoy-inician-las-audiencias-recuento-votos-diferentes-jee-1095545.aspx</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>46307</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Perupetro estima que bajo el subsuelo habría gas natural equivalente a tres Camiseas</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fue entonces cuando el país se puso en modo emergencia.
+El Ministerio de Energía y Minas ( Minem ) declaró el suministro en emergencia por 14 días y priorizó a hogares, hospitales y transporte público.
+A mediados de ese mes, Transportadora de Gas del Perú (TGP), responsable de transportar el gas, informó que había concluido la reparación y que el 14 de marzo las entregas recuperarían su capacidad total.
+Este incidente expuso la dependencia del país de una infraestructura y una zona productora altamente concentradas, señala informe publicado en el Diario El Peruano.
+- Minem da un nuevo paso para llevar gas natural a 7 regiones del centro y sur del país Por ello, quedaron varias preguntas flotando: si una sola ruta y un solo gran yacimiento sostienen buena parte de la energía del país, ¿dónde está el próximo Camisea? ¿contamos con alternativas para reponer las actuales reservas? Y de encontrarlos, ¿cuánto tiempo queda disponible para alcanzar dicho objetivo? Reloj con fecha No cabe duda que Camisea cambió la historia energética del Perú.
+Desde que empezó a producir, en 2004, la producción nacional de hidrocarburos —petróleo, gas y líquidos— se triplicó, de acuerdo con Perupetro .
+Hoy, los lotes 88, 56 y 57, de la zona de Camisea, aportan 96 de cada 100 pies cúbicos de gas que se producen en el país.
+Pero todo yacimiento tiene un horizonte.
+El Libro Anual de Recursos de Hidrocarburos 2024 del Minem registra reservas probadas de gas por 7.1 billones de pies cúbicos, suficientes para unos 13 años y medio al ritmo actual.
+El ingeniero Pedro Arce, vocero de Perupetro , explicó que, con la demanda proyectada, esa curva se acerca a cero hacia 2039, casi al mismo tiempo que vence, en 2040, el contrato del Lote 88, el corazón de Camisea.
+El reloj marca un plazo de 14 años desde la actualidad para actuar a tiempo.
+Para Patricia Figueroa, directora ejecutiva de la Sociedad Peruana de Hidrocarburos (SPH), la mirada del sector privado es clara: “el Perú no se está quedando sin gas, pero siempre enfrentamos un problema serio de reposición de reservas.
+No explorar significa no reponer reservas y no desarrollar infraestructura significa no aprovechar las reservas que tenemos”, comentó.
+Según Arce, el Perú cuenta con 18 cuencas sedimentarias con potencial de petróleo y gas, pero solo cinco producen hoy.
+Las estimaciones de Perupetro suman 45.87 billones de pies cúbicos de gas y 35,218 millones de barriles de petróleo por descubrir.
+Son “recursos prospectivos”, es decir, estimaciones técnicas de lo que podría haber que solo se convierten en reservas cuando se comprueba.
+Para tener una idea de a cuánto asciende, estas estimaciones son equivalentes a más de 6 veces las reservas probadas actuales, más de 3 Camiseas o unos 520 millones de piscinas olímpicas.
+Asimismo, equivaldría a más de 75 años de producción al ritmo actual, si todo se confirmara.
+Según Perupetro tres cuencas concentran cerca del 81% del gas: Madre de Dios (20.4 billones), Ucayali (casi 10) y Tumbes-Progreso (6.8).
+Sin embargo, Madre de Dios, con casi la mitad, es también una zona sensible: parte del potencial se superpone con áreas naturales protegidas, donde la ley impide actividades extractivas y donde el debate sobre cómo compatibilizar conservación y desarrollo sigue abierto.
+Arce identificó en Candamo, dentro del Parque Nacional Bahuaja Sonene, el punto de mayor complejidad.
+Pero hay otras rutas.
+Según un cálculo sobre las cifras de Perupetro y del Minem , sin contar Madre de Dios, el gas por descubrir equivale a casi dos Camiseas : más de 25 billones, es decir, 3.5 veces las reservas actuales.
+Perforar para saber Las reservas aparecerán realmente cuando alguien perfore.
+Cada pozo exploratorio es una pregunta que se le hace a la tierra y no todas las respuestas son afirmativas.
+Perupetro mantiene cinco contratos de exploración y ofrece más de medio centenar de áreas promocionales, además de nuevos contratos de explotación firmados en el último año, como los lotes I y VI.
+El ministro de Energía y Minas, Guillermo Shinno, reconoció en setiembre que la exploración ha caído y anunció que el Gobierno prepara una reforma del marco legal de hidrocarburos para competir con la región y sumar reservas de petróleo y gas.
+Gonzalo Raffo, socio del área de Energía del estudio Hernández &amp; Cía, explica la lógica: explorar es apostar.
+Cuesta mucho, y a veces no se encuentra nada.
+Por eso, propone flexibilizar el trato a los gastos de los pozos que no dan resultado.
+“Si se quiere incrementar la exploración, lo que hay que hacer es flexibilizar las normas respecto de cómo se aplican las pérdidas.
+Si se dan a los inversionistas los incentivos necesarios para que hagan inversión exploratoria, se van a encontrar más reservas”, destacó.
+A criterio del abogado, otra clave es la demanda ya que, al día de hoy, “no hay una que justifique la necesidad de contar con mayor volumen de gas, en caso hubiese un descubrimiento”.
+Pero descubrir es la mitad del camino; la otra mitad es llevar el gas a los hogares.
+ProInversión registra una cartera en esa dirección.
+La institución precisó a este diario que la masificación del gas en Arequipa, Moquegua y Tacna, con una inversión de 349 millones de dólares, está en estructuración, con convocatoria prevista para el cuarto trimestre de 2026, y apunta a casi 224,000 usuarios en sus primeros ocho años.
+La adenda de Cálidda , de 474 millones de dólares, extendería el servicio a 15 localidades de siete regiones.
+El gasoducto al sur, de 2,000 millones, tendría 923 kilómetros, y una planta de fraccionamiento en La Convención, de 30 millones, procesaría líquidos de Camisea.
+Arturo Vásquez, exviceministro de Energía, subraya que “tenemos un potencial de gas natural magnífico”.
+En ese sentido, propone que los ductos cuenten con una retribución asegurada, como ya ocurre con las líneas de transmisión eléctrica.
+“Se puede hacer si se cambian las reglas de juego para poder crear un esquema de retribución similar al que ya existe en las líneas de transmisión eléctrica ”, planteó.
+La SPH pide simplificar trámites y cumplir los plazos de ley.
+“No estamos pidiendo privilegios.
+Estamos pidiendo que se tomen los plazos necesarios, los plazos de ley”.
+Gonzalo Raffo plantea una línea base ambiental compartida por el Estado, ya que “se puede ahorrar mucho tiempo en los permisos ambientales”.
+Asimismo, plantea la activación de un fideicomiso de abandono y la descentralización de la producción y el consumo.
+Arturo Vásquez, por su parte, pide planificar la infraestructura del gas con reglas claras.
+“Deberíamos pensar ya en un esquema de planificación de la infraestructura de gas”, indicó.
+La buena noticia es que toda esta agenda coincide con la que plantea el Minem .
+Camisea no apareció de la noche a la mañana: fue la suma de exploración, inversión y decisiones sostenidas.
+El Perú tiene hoy el mapa, la experiencia y una agenda de reformas sobre la mesa.
+Falta lo que la exploración siempre exige: tiempo.
+Y ese, como indica el reloj de Perupetro , ya empezó a correr.
+La carrera hacia 2040 no se gana en el último tramo: se gana con las primeras perforaciones, las primeras tuberías y las primeras decisiones, las que todavía están a tiempo de tomarse.
+Plan B Tras la emergencia de marzo, el entonces ministro de Energía y Minas, Ángelo Alfaro, anunció que se impulsaría una planta regasificadora .
+En setiembre, el ministro Guillermo Shinno relanzó la idea ante la Comisión de Energía y Minas del Congreso de la república: una planta en el litoral de Lima o Ica, con almacenamiento para al menos 15 días o tres semanas.
+Funciona así: un barco trae gas natural licuado —enfriado hasta volverse líquido— y la planta lo devuelve a su estado gaseoso para inyectarlo a los ductos.
+Colombia lo hace desde 2016 en Cartagena, con un buque-terminal que recibe gas de Estados Unidos y Trinidad y Tobago.
+Según su operador, en 2024 cubrió hasta 30% de la demanda nacional.
+No reemplaza explorar, pero da tiempo suficiente ante otra posible emergencia.
+Datos - Canon transferido por hidrocarburos (Desde 1993 a junio de 2026): Cusco, S/ 26,884 millones; Piura, S/ 9,408 millones; Loreto, S/ 5,969 millones; Tumbes, S/ 2,750 millones; Ucayali, S/ 2,080 millones.
+- Solo entre enero y junio de 2026, las regiones productoras recibieron S/ 1,138 millones.
+Cusco percibe más de US$ 1 millón diario por canon gasífero; Piura, cerca de S/ 1 millón.
+- Hay 25 contratos de explotación de hidrocarburos: 12 en la selva, 10 en la costa y 3 en el mar.
+Más en Andina: ?? ¡El turrón de Doña Pepa tiene 130 marcas registradas y vigentes en el Perú! En el mes del Señor de los Milagros, Indecopi destaca el interés de empresas y emprendedores por diferenciar este tradicional dulce limeño.
+Entre las marcas con trayectoria figuran la Antigua Pastelería y Panadería Huérfanos, San Martín, San José, Belgravia y Turrones Doña Pepa de Jaramillo.
+?? https://t.co/kgbXka6aru (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 11, 2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-perupetro-estima-bajo-subsuelo-habria-gas-natural-equivalente-a-tres-camiseas-1095552.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Torneo Clausura: Así quedó la tabla de posiciones con cuatro equipos en lo más alto</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>El la jornada 11, Sporting Cristal ganó de visita al UTC de Cajamarca con un gol de Luis Iberico, con lo cual sumó 22 unidades, pero mantiene la misma diferencia de goles (11) que Deportivo Garcilaso (22), que perdió el viernes con Sport Huancayo por 0-1 en su estadio del Cusco.
 A su vez, Sport Huancayo , que venció con gol del ecuatoriano Daniel Porozo, alcanzó a Garcilaso y Cristal en puntaje, aunque tiene siete goles anotados menos que ambos clubes.
@@ -546,77 +755,209 @@
 Fecha 11 Jueves 8 de octubre Estadio 25 de Noviembre de Moquegua CD Moquegua 0 - Cienciano 2 Estadio Municipal Ambrosio Maco Arroyo ‘La Matanza’ de Piura Atlético Grau 0 - Chankas CYC 0 Viernes 9 de octubre Estadio Inca Garcilaso de la Vega del Cusco Deportivo Garcilaso 0 - Sport Huancayo 1 Sábado 10 de octubre Estadio Unión Tarma ADT 0 - FC Cajamarca 0 Estadio Municipal Juan Maldonado Gamarra de Cutervo Comerciantes Unidos 1 - Juan Pablo II 1 Estadio Monumental de Ate Universitario 2 - Melgar 2 Domingo 11 de octubre Estadio Héroes de San Ramón de Cajamarca UTC 0- Sporting Cristal 1 Estadio Miguel Grau del Callao Sport Boys 3 - Alianza Atlético 1 Estadio Inca Garcilaso de la Vega del Cusco Cusco FC 1 - Alianza Lima 2 Tabla del Torneo Clausura Tabla Acumulada (Apertura+Clausura)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-torneo-clausura-asi-quedo-tabla-posiciones-cuatro-equipos-lo-mas-alto-1095567.aspx</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Talara: EPS Grau: hoy concluyen trabajos y volverá el agua</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mientras los vecinos de varios sectores de la ciudad se quejaron por no contar hace cuatro días con el servicio de agua potable en sus respectivos domicilios, la EPS Grau anunció que recién hoy serán concluidos los trabajos en la Estación de Bombeo de Aguas Residuales (EBAR), para luego, de manera paulatina, reanudar la distribución del recurso hídrico. PUEDES LEER ► Nueva fecha para segunda vuelta en medio de cuestionamientos La empresa prestadora del servicio indicó que, debido a la complejidad de los trabajos correctivos, recién hoy lunes se prevé culminar con la reparación de la línea de impulsión que va desde la cámara de bombeo, ubicado en el sector Los Estibadores del asentamiento San Pedro, hasta la Planta de Tratamiento de Aguas Residuales (PTAR), en Cerro Rajado. Según detalló la Zonal Talara, con el personal técnico y la maquinaria pesada necesaria se continúa interviniendo en la tubería de material GRP de 24 pulgadas de diámetro , con el propósito de finalizar la rehabilitación de la línea alrededor de las 08:00 a.m. de hoy lunes. La EPS Grau recalcó que, como m edida temporal preventiva, ayer domingo y hoy, se brindará un abastecimiento restringido de agua potable en los asentamientos afectados de la ciudad por la afectación de la referida red, y que la dotación se llevará a cabo en horario nocturno.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/talara-eps-grau-hoy-concluyen-trabajos-y-volvera-el-agua/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Gobierno fortalece calidad del agua en beneficio de más de dos millones de peruanos</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Con esta transferencia de partidas, autorizada mediante el Decreto Supremo 174-2026-EF, se podrá financiar la adquisición de insumos esenciales para la cloración de alrededor de 13,800 sistemas de agua potable (SAP) en favor de más de dos millones de pobladores de las zonas rurales del país , señaló el MVCS.
+Precisó que los recursos serán destinados a la adquisición de 256,889 kilos de hipoclorito de calcio y más de 2 millones 651,712 unidades de reactivos DPD, insumos indispensables para las actividades de limpieza, desinfección, monitoreo y adecuada cloración de los sistemas de agua potable, garantizando la protección de la salud y el bienestar de la población rural.
+Municipalidades beneficiarias Las municipalidades beneficiarias se encuentran en Amazonas, Áncash, Apurímac, Arequipa, Ayacucho, Cajamarca, Cusco, Huancavelica, Huánuco, Junín, La Libertad, Lambayeque, Lima, Loreto, Moquegua, Pasco, Piura, Puno, San Martín, Tacna y Ucayali.
+En este proceso el PNSR brinda acompañamiento técnico a los gobiernos locales para la incorporación de los recursos transferidos en su Presupuesto Institucional Modificado (PIM), a fin de facilitar el inicio de los respectivos procesos de adquisición y garantizar la disponibilidad oportuna de estos insumos estratégicos.
+El Ministerio de Vivienda indicó que, con esta intervención, se fortalece la gestión de los servicios de agua potable en el ámbito rural y contribuye a la sostenibilidad de los sistemas, al favorecer la disponibilidad de insumos necesarios para su adecuada operación, mantenimiento y control de la calidad del agua.
+Más en Andina: ???? Perú crecería 3.2% en 2026, según el Banco Mundial.
+La inversión privada en minería e infraestructura, la recuperación del consumo y la demanda global de cobre serían claves para la expansión económica.
+?? https://t.co/goSIyt3I9v?? William Rios Rosales https://t.co/gKM1UjIxKK (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 12, 2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-gobierno-fortalece-calidad-del-agua-beneficio-mas-dos-millones-peruanos-1095602.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cura Mori: Peregrino del Señor Cautivo muere tras despiste de motofurgón</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>La fe que lo llevó hasta el Señor Cautivo de Ayabaca terminó convirtiéndose en una dolorosa despedida para una familia del distrito de Cura Mori, en el Bajo Piura. Álvaro Vílchez Yarlequé, de 52 año s, perdió la vida la noche del último sábado cuando regresaba a casa después de cumplir su promesa de peregrinación. PUEDES LEER ► Sullana: Acusan a siete policías de presunto cobro de coima El accidente ocurrió aproximadamente a las 9:00 de la noche del sábado, cerca del puente de Tondopa. Vílchez viajaba en un motofurgón junto con otros tres peregrinos, quienes retornaban a sus hogares tras visitar al venerado Señor Cautivo de Ayabaca. Por causas que son materia de investigación, el vehículo menor terminó despistándose en una bajada, provocando el accidente que dejó a sus cuatro ocupantes afectados. Tras lo ocurrido, los peregrinos fueron trasladados al establecimiento de salud de Las Lomas. NO RESISTIÓ En el centro de salud se confirmó el deceso de Álvaro Vílchez, cuya muerte ha causado profundo pesar entre sus familiares, amigos y personas que compartieron con él la peregrinación. La víctima mortal era propietaria del restaurante El León Dormido y residía en Cura Mori. Su partida deja un vacío entre sus seres queridos, quienes ahora enfrentan el dolor de perderlo cuando retornaba de cumplir una promesa religiosa. TRES HERIDOS Los otros tres ocupantes que resultaron heridos fueron identificados como Carlos Santos y Jhon Culupu, mientras que la identidad del tercer herido no había sido precisada en la información preliminar. Todos serían también del distrito de Cura Mori. Las circunstancias exactas del despiste deberán ser esclarecidas por las autoridades competentes. Mientras tanto, la noticia enluta a una familia del Bajo Piura y deja una dolorosa historia detrás de una peregrinación que, para Álvaro, terminó lejos del hogar al que esperaba regresar. RACHA TRÁGICA La racha de accidentes de tránsito sigue impara en la región. Ya van 147 fallecidos por accidentes de tránsito en lo que va del año. Las autoridades exhortan a los conductores a circular por las carreteras a moderada velocidad y con los vehículos en buenas condiciones para evitar accidentes.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/cura-mori-peregrino-del-senor-cautivo-muere-tras-despiste-de-motofurgon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nueva fecha para segunda vuelta en medio de cuestionamientos</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>El Pleno del Jurado Nacional de Elecciones (JNE) acordó que el próximo 6 de diciembre se realizará la Segunda Elección Regional (SER 2026) , en aquellas circunscripciones en las cuales ninguna de las fórmulas que participaron en las recientes Elecciones Regionales obtenga no menos del 30% de los votos válidos. PUEDES LEER ► Sechura: Instalan mesa de diálogo tras paro de pescadores De esta forma, modificó el numeral 4 de su Acuerdo del 30 de setiembre de 2026, en el que había establecido el 29 de noviembre como fecha para la realización de la citada elección. La modificación La decisión fue adoptada luego de evaluar la solicitud de reconsideración de la fecha presentada por la ONPE . Conforme al acuerdo del supremo tribunal electoral, la modificación “responde a la necesidad de compatibilizar las actividades de organización y logística electoral con las exigencias de certeza, predictibilidad y continuidad que deben regir el desarrollo de todo proceso electoral”. Señala que la modificación de una fecha inicialmente prevista para la realización de una elección debe encontrarse sustentada en razones objetivas, verificables y compatibles con el marco constitucional y legal vigente. Indica que la adecuada culminación de la SER 2026 no comprende únicamente la ejecución de la jornada de votación y el cómputo de resultados, sino también la resolución de las controversias electorales que pudieran presentarse y la proclamación de las autoridades electas. Cuestiona nulidad Nelson Mío Reyes, candidato a la alcaldía provincial de Morropón por Somos Perú , cuestionó la decisión del Jurado Electoral Especial (JEE) de Morropón de declarar la nulidad de las elecciones municipales en el distrito de San Juan de Bigote. El candidato sostuvo que, antes de adoptar una medida de esta naturaleza, se debió evaluar todo el material electoral lacrado que permanece bajo custodia fiscal, a fin de esclarecer lo ocurrido y determinar si existen condiciones para validar los resultados. Mío Reyes consideró que el material electoral debía ser abierto y revisado en una audiencia pública, con participación de las organizaciones políticas, la prensa y autoridades competentes. Según manifestó, existen actas y ánforas que estarían intactas y cuya información, afirmó, debió ser considerada antes de emitir la resolución. Asimismo, rechazó que se adelanten opiniones sin que se haya examinado integralmente dicho material.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/nueva-fecha-para-segunda-vuelta-en-medio-de-cuestionamientos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Piura: Asesinan a balazos a joven en la vía pública</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Un nuevo hecho de sangre conmocionó la tarde de ayer a los vecinos del distrito de Castilla . Un joven identificado como José Eduardo Gómez Carreño, de 24 años, fue asesinado a balazos en el sector La Esperanza, del asentamiento humano Las Montero, detrás de la urbanización Villa California. PUEDES LEER ► “El Niño se está fortaleciendo rápidamente”, advierte Organización Meteorológica Mundial El crimen fue reportado aproximadamente a las 2:20 p. m. , cuando los vecinos escucharon varios disparos que desataron el temor y la preocupación en la zona. Al salir de sus viviendas para averiguar lo ocurrido, encontraron al joven tendido en plena vía pública, en posición decúbito dorsal y en medio de un charco de sangre. Según la información preliminar, la víctima habría recibido cinco impactos de bala, varios de ellos en el rostro, que le causaron la muerte. En el lugar quedaron sus zapatos fuera de posición, mientras los moradores observaban con preocupación la escena y alertaban a las autoridades. Tras conocerse el hecho, efectivos de la Policía Nacional de la Comisaría de El Indio y personal de Serenazgo de Castilla llegaron al lugar para acordonar la zona y realizar las primeras diligencias. Los agentes iniciaron las investigaciones con el objetivo de determinar las circunstancias del ataque e identificar a los responsables. El móvil del asesinato aún no ha sido establecido. Sin embargo, trascendió que una de las hipótesis que se maneja es un posible asalto y robo, aunque esta versión deberá ser corroborada por los investigadores. No se descarta ninguna línea de investigación mientras se recogen testimonios y otros elementos que permitan reconstruir lo sucedido. PASIÓN POR EL FÚTBOL La víctima, que deja una niña en la orfandad, residía en el asentamiento humano Ciudad del Niño y era natural del distrito de Villa María del Triunfo, en Lima . Además, era aficionado al fútbol y había jugado por el club Huáscar de la Liga Distrital de Fútbol de Castilla, donde compartió su pasión por este deporte. En su perfil de Facebook, el joven tenía una frase que reflejaba sus prioridades: “Amor al fútbol y a mi familia”. Su muerte generó consternación entre quienes lo conocían. De acuerdo con los datos proporcionados, Gómez Carreño cumpliría años el próximo 11 de noviembre. 115 HOMICIDIOS Cabe mencionar que con este nuevo asesinato, la cifra de homicidios en la región Piura se elevaría a 115 en lo que va del año, según el registro proporcionado.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-asesinan-a-balazos-a-joven-en-la-via-publica/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Piura: Caen cinco presuntos extorsionadores  que serían del ‘Tren de Aragua’</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cinco ciudadanos venezolanos fueron detenidos por la Policía, sindicados de integrar presuntamente la banda criminal denominada ‘Tren de Aragua’ y estar implicados en un caso de extorsión agravada contra un ciudadano dedicado a actividades comerciales en Piura. La intervención se realizó el pasado viernes 9 de octubre, tras una denuncia policial. Personal de la Sección de Secuestros y Extorsiones de la DIVINCRI Piura , en coordinación con agentes de la DIGIMIN y otras unidades especializadas, identificó a los sospechosos y desplegó un operativo que permitió su captura. Según la información policial, los investigados habrían exigido al agraviado pagos de entre S/ 200 y S/ 300 para permitirle continuar con sus actividades comerciales, bajo presuntas amenazas. La primera intervención se efectuó en la Av. Motupe, a una cuadra de la avenida Don Bosco. En ese lugar, los agentes intervinieron un automóvil Mitsubishi Lancer blanco, de placa M4B-154, en cuyo interior viajaban tres de los sospechosos. Durante el registro vehicular, la Policía encontró dos cartuchos de dinamita, además de cinco municiones sin percutir, de calibre .380 Auto. En el A.H. Nueva Esoeranza intervinieron a dos personas más con arma de fuego y 15 municiones, 5 celulares, tarjetas de crédito y un automóvil. Las personas intervenidas fueron identificadas con las iniciales M. C.R. (37), W. V. S. H. (46), A. J. B. S. (25), J. M. C. B. (34) y V. P. H. C. (16), de nacionalidad venezolana.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-caen-cinco-presuntos-extorsionadores-que-serian-del-tren-de-aragua/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>El Comercio</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>46306</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Morropón (Piura)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Morropón, según el conteo oficial de la ONPE al 93.347% , arroja el siguiente resultado (actualizado el 11/10/2026, a las 00:45.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-morropon-piura-noticia/</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
         <v>46306</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Resultados ONPE en región Piura al 96.028 %: conoce aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación región Piura según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/resultados-en-piura-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>¿Un aluvión como el ocurrido en Chile podría suceder en el Perú? Esto revela el Senamhi</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>El especialista en Meteorología del Servicio Nacional de Meteorología e Hidrología (Senamhi), Nelson Quispe, afirma que el Perú podría registrar episodios de lluvias intensas, huaicos y activación de quebradas similares a los ocurridos recientemente en Chile, especialmente durante el próximo verano, debido a las condiciones asociadas al fenómeno El Niño y al calentamiento de la temperatura superficial del mar.
 Lea también: Enfen: lluvias intensas serán más frecuentes desde octubre por El Niño extraordinario En declaraciones a la Agencia Andina, Quispe explicó que las precipitaciones de corta duración y gran intensidad pueden desencadenar emergencias en distintas regiones del país, incluso en escenarios en los que se proyecta un déficit de lluvias para determinadas zonas.
@@ -657,27 +998,27 @@
 Más en Andina: ¡Hallazgo en Trujillo! Descubren tumba de infante de élite mochica en la huaca de la Luna https://t.co/8J3T2uL3ME https://t.co/dnQUuFSeKN (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 9, 2026</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-un-aluvion-como-ocurrido-chile-podria-suceder-el-peru-esto-revela-senamhi-1095328.aspx</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>46306</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Clausura: Así está la lucha por el primer lugar tras empate de Universitario ante Melgar</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>El Garcilaso desperdició la oportunidad de distanciarse más y convertirse en líder en solitario del segundo certamen al caer 1-0 ante Sport Huancayo en el Cusco.
 Con este sorprendente resultado, los cusqueños se quedaron en 22 puntos en lo más alto de la tabla, pero fueron alcanzados por el equipo huanacaíno, que también sumó 22 puntos.
@@ -694,59 +1035,27 @@
 Alianza Lima Transmisión: L1 Max (Claro TV, DirecTV, Win, Best Cable, Movistar TV y Mi Fibra) y L1 Play</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-clausura-asi-esta-lucha-por-primer-lugar-tras-empate-universitario-ante-melgar-1095476.aspx</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B18" s="2" t="n">
         <v>46306</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Minam y gobiernos regionales impulsan acciones para conservar la biodiversidad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Así lo informó el Minam que precisó que en la cita participaron representantes de Arequipa, Ayacucho, Cajamarca, Áncash, Lambayeque, Amazonas, Apurímac, Ica, Madre de Dios, Puno y Piura , entre otras regiones.
-Durante el encuentro se abordó la articulación de las prioridades regionales con la Estrategia Nacional de Diversidad Biológica al 2050 y su Plan de Acción al 2030.
-Prioridades regionales Sostuvo que las Estrategias Regionales de Diversidad Biológica permiten a los gobiernos regionales identificar y priorizar los ecosistemas, especies, servicios ecosistémicos y territorios que requieren atención.
-Asimismo, contribuyen a vincular estas prioridades con inversiones públicas, cooperación internacional y otras fuentes de financiamiento para su implementación.
-Durante la reunión, el Minam presentó la guía que orientará a los gobiernos regionales en la elaboración y actualización de sus estrategias, desde el diagnóstico y la definición de prioridades hasta su aprobación, implementación y seguimiento.
-Como resultado de la jornada, el Minam y los gobiernos regionales trabajarán conjuntamente en la definición de hojas de ruta para avanzar, desde diciembre de 2026 y durante 2027 , en la elaboración y actualización de sus Estrategias Regionales de Diversidad Biológica, con asistencia técnica del sector.
-Por último, el Minam resaltó que con estas acciones promueve una gestión descentralizada de la biodiversidad para que las prioridades de cada región se traduzcan en acciones e inversiones orientadas a la conservación, recuperación y uso sostenible de la diversidad biológica del país.
-Más en Andina: Hace más de 1,400 años aproximadamente, la muerte repentina de un infante miembro de la élite mochica, generó un importante ritual funerario al pie de la huaca de la Luna, uno de los templos religiosos más importantes de esta sociedad prehispánica, que se asentó en el valle del actual distrito de Moche, en la provincia de Trujillo.??https://t.co/GeKo8fnBPE (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 11, 2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-minam-y-gobiernos-regionales-impulsan-acciones-para-conservar-biodiversidad-1095488.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Presidenta Fujimori: el Gobierno está del lado de los peruanos que quieren vivir en paz</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>A través de sus cuentas de redes sociales, la Jefa de Estado compartió un texto acompañado de un corto video sobre la presentación de las primeras acciones del Comando Unificado para enfrentar la criminalidad y la delincuencia , en la sede del Cuartel General del Ejército.
 Lea también: Gobierno reafirma que lucha contra la criminalidad "no tiene punto de retorno" "Son momentos de tensión.
@@ -759,261 +1068,212 @@
 Más en Andina: El papa León XIV anunció este domingo que deberá operarse "en los próximos días" de un nódulo en un pulmón que le ha sido detectado en una fase "muy inicial y bien localizado", afirmó tras el rezo del Ángelus dominical.??https://t.co/b8mODZ2emo https://t.co/UOvQYiXeTH (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 11, 2026</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-presidenta-fujimori-gobierno-esta-del-lado-los-peruanos-quieren-vivir-paz-1095490.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sechura: Instalan mesa de diálogo tras paro de pescadores</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>La recién instalada mesa de diálogo entre el Ministerio de la Producción y los gremios pesqueros artesanales, que contó con la asistencia de unas 16 asociaciones y más de seis invitados, dio inicio a un proceso de negociación tras el paro de pescadores artesanales, orientado al reordenamiento del sector. Durante este primer encuentro, realizado en Lima , los dirigentes expusieron sus petitorios con el objetivo de garantizar la estabilidad operativa y económica de los pescadores artesanales durante lo que resta del año. Según explicó Julio Seminario Panta, secretario de la Asociación Unificada de Pescadores Artesanales de la Bahía de Sechura , la mesa de trabajo ha establecido un nuevo esquema en el que todas las solicitudes deberán presentarse por escrito, eliminando las intervenciones verbales y las votaciones a mano alzada. Las organizaciones acreditadas tienen como plazo límite el viernes 17 de octubre para presentar sus informes y propuestas por escrito, los cuales se debatirán formalmente en la primera sesión de trabajo, programada para el viernes 23 de octubre. El petitorio del gremio de Sechura abarca cinco puntos clave para la sostenibilidad de la actividad pesquera: continuidad de las faenas hasta diciembre, modificación de la Resolución N.° 348, revisión de los topes de captura, medidas de alivio frente al Fenómeno El Niño y transparencia e información técnica. Seminario Panta advirtió que la pota se ha alejado de su zona habitual, lo que obliga a las embarcaciones a desplazarse a mayores distancias, hacia zonas frente a Chicama, para poder faenar.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/sechura-instalan-mesa-de-dialogo-tras-paro-de-pescadores/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Sullana: Acusan a siete policías de presunto cobro de coima</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Siete agentes policiales que laboran en el Área Antidrogas (Areant) de Sullana son investigados preliminarmente por presuntamente solicitar dinero a los familiares de dos mujeres detenidas por tráfico ilícito de drogas, a cambio de omitir actos de su función. PUEDES LEER ► Piura: Anuncia revisión del contrato del sistema de fotopapeletas La situación de los efectivos se agravó luego de que la Policía y la Fiscalía Anticorrupción obtuvieran nuevos indicios durante las diligencias realizadas en las últimas días. Entre los investigados figura el oficial M. A. V., señalado como jefe de la unidad, junto con los suboficiales D. J. R., L. A. V., M. R. L., F. Ch. R., J. Z. T. y E. A. S. Inicialmente, cinco de ellos tenían la condición de testigos, pero los nuevos elementos recabados motivaron que pasaran a ser comprendidos en la investigación. Según las indagaciones preliminares, los policías habrían solicitado inicialmente S/ 50 mil y, posteriormente, utilizando un celular de uno de los detenidos, se habrían comunicado con sus familiares para acordar el pago de S/ 30 mil. Como parte de ese supuesto trato, se habría concretado la entrega de S/ 5 mil en billetes previamente fotocopiados por las autoridades anticorrupción. El Informe Policial n.° 35 de la Dirección Contra la Corrupción de Piura habría sido determinante para que el Segundo Despacho de la Fiscalía Anticorrupción de Sullana modificara la situación de los implicados y dispusiera nuevas diligencias. Entre las medidas solicitadas figuran las declaraciones de los siete investigados y el levantamiento del secreto de las comunicaciones y del secreto bancario, con el propósito de esclarecer los hechos y determinar si habría responsabilidades. Las pesquisas apuntan a una posible concertación entre los agentes, extremo que deberá ser corroborado. Como se informó, el 2 de octubre, uno de los policías investigados recibió el dinero fotocopiado, pero al advertir que sus colegas se disponían a intervenir en flagrancia, escapó en motocicleta junto a otro policía.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/sullana-acusan-a-siete-policias-de-presunto-cobro-de-coima/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Somos Perú espera que JNE ordene el recuento de votos en S. Juan de Bigote</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>El recurso de apelación de Somos Perú contra la resolución del Jurado Electoral Especial de Morropón, que anuló las elecciones en San Juan de Bigote, busca que el Jurado Nacional de Elecciones (JNE) disponga el recuento de votos entre el material que se pudo recuperar en el local. Según el abogado y personal legal titular de la organización política, Alex Ochoa Huamán, falta mayor sustento en la resolución del JEE Morropón. “Sí es probable [que se ordene el recuento de votos] dado que los fundamentos en la resolución de nulidad carecen de motivación suficiente. El acta fiscal y los informes de ODPE no son suficientes para demostrar que el material recuperado no se pueda contabilizar”, informó el abogado. Como se informó, el JEE de Morropón declaró la nulidad de las elecciones en el distrito de San Juan de Bigote luego de los actos de vandalismo contra el material electoral. En su resolución, el JEE señala que no hay certeza para verificar que el material recuperado y lacrado por la Fiscalía, no haya sido alterado porque se rompió la cadena de custodia. “La resolución se basa en informes, más no de la verificación del material recuperado. Dicho material electoral aún sigue lacrado y custodiado, en la Fiscalía de Derechos Humanos. El 2do Despacho de Fiscalia de Chulucanas envió el día de ayer el paquete electoral lacrado” , informó. El abogado también sostiene que no se puede generalizar lo sucedido con el material electoral, si no hay sustento preciso. “Se cuestiona el alcance de esa conclusión y solicitamos examinar su sustento: qué material abarca, qué custodia tuvo cada paquete y porqué la ruptura de las cédulas invalida también posibles ejemplares auténticos de actas o copias entregadas antes del incidente. Si el oficio contiene soporte individualizado suficiente, deberá ponderarse expresamente ”, sostuvo.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/somos-peru-espera-que-jne-ordene-el-recuento-de-votos-en-s-juan-de-bigote/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Piura: Anuncia revisión del contrato del sistema de fotopapeletas</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>El alcalde electo de Piura, Miguel Cueva Celi, ratificó que revisará el contrato con la empresa que aplica las fotopapeletas por infracciones de tránsito, al considerar que se trata de “un abuso” en contra de los conductores piuranos. Sostuvo que se buscará un acuerdo con la empresa a cargo de la fiscalización electrónica para llegar a un final feliz. “No ha sido el momento para las fotopapeletas y se tendrá que revisar el contrato y se verá a qué final feliz llego con la empresa [...] Piura está destruida ”, comentó Cueva. De otro lado, la autoridad municipal electa no dudó en calificar el sistema como un abuso. “ Las fotopapeletas de mayo las están pasando a cobranza coactiva. A una profesora le han descontado casi S/1.000 porque el vehículo de su hijo está a su nombre. Eso es un abuso y no puede ser. Definitivamente, lo revisaré porque Piura no está preparada para estas fotopapeletas y con estos costos”, manifestó Cueva. El alcalde electo resaltó que la ciudad tiene vías destruidas y no se puede castigar a los conductores de esta manera. “Es un abuso” Asimismo, Cueva advirtió que una de las finalidades del sistema de fotopapeletas sería la recaudación a favor de la comuna. “Con ese tipo de abuso no puedes querer salir de lo rojo que tienen en gastos corrientes por exceso de personal que la misma gestión ha tomado. Es una desesperación que no tienen cómo pagar al personal y no puedes utilizar este tipo de medios. Estoy mortificado por este tipo de abuso” , declaró Cueva. Recaudación Según una investigación de l portal Norte Sostenible, la Municipalidad de Piura proyectó que en el primer año de funcionamiento del sistema se podrían imponer 103 mil 830 papeletas. Esto podría generar una recaudación de 4.2 millones de soles, aproximadamente, hasta el 15 de mayo del año 2027 , fecha en que se cumple el primer año. Cabe indicar que en setiembre del 2025, la comuna otorgó la buena pro para el servicio de instalación, operación y mantenimiento del sistema de fotopapeletas al consorcio Setrapi, conformado por las empresas SEMOECSA SAS (de origen ecuatoriano) y la peruana Prototipo del Perú SAC. La contratista cobraría S/ 2 millones 072 mil 824.46 por brindar el servicio en un periodo de 730 días calendarios. De otro lado, Cueva señaló que otro problema del sistema es que no hubo una adecuada difusión del sistema entre la población. “No hubo socialización [adecuada] del tema y han tomado por sorpresa a los piuranos”, manifestó Cueva, en cuya gestión se tendrá que analizar este millonario contrato.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/piura-anuncia-revision-del-contrato-del-sistema-de-fotopapeletas/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Piura: Caen cinco presuntos extorsionadores  que serían del ‘Tren de Aragua’</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Cinco ciudadanos venezolanos fueron detenidos por la Policía, sindicados de integrar presuntamente la banda criminal denominada ‘Tren de Aragua’ y estar implicados en un caso de extorsión agravada contra un ciudadano dedicado a actividades comerciales en Piura. La intervención se realizó el pasado viernes 9 de octubre, tras una denuncia policial. Personal de la Sección de Secuestros y Extorsiones de la DIVINCRI Piura , en coordinación con agentes de la DIGIMIN y otras unidades especializadas, identificó a los sospechosos y desplegó un operativo que permitió su captura. Según la información policial, los investigados habrían exigido al agraviado pagos de entre S/ 200 y S/ 300 para permitirle continuar con sus actividades comerciales, bajo presuntas amenazas. La primera intervención se efectuó en la Av. Motupe, a una cuadra de la avenida Don Bosco. En ese lugar, los agentes intervinieron un automóvil Mitsubishi Lancer blanco, de placa M4B-154, en cuyo interior viajaban tres de los sospechosos. Durante el registro vehicular, la Policía encontró dos cartuchos de dinamita, además de cinco municiones sin percutir, de calibre .380 Auto. En el A.H. Nueva Esoeranza intervinieron a dos personas más con arma de fuego y 15 municiones, 5 celulares, tarjetas de crédito y un automóvil. Las personas intervenidas fueron identificadas con las iniciales M. C.R. (37), W. V. S. H. (46), A. J. B. S. (25), J. M. C. B. (34) y V. P. H. C. (16), de nacionalidad venezolana.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/piura-caen-cinco-presuntos-extorsionadores-que-serian-del-tren-de-aragua/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Piura: Asesinan a balazos a joven en la vía pública</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Un nuevo hecho de sangre conmocionó la tarde de ayer a los vecinos del distrito de Castilla . Un joven identificado como José Eduardo Gómez Carreño, de 24 años, fue asesinado a balazos en el sector La Esperanza, del asentamiento humano Las Montero, detrás de la urbanización Villa California. PUEDES LEER ► “El Niño se está fortaleciendo rápidamente”, advierte Organización Meteorológica Mundial El crimen fue reportado aproximadamente a las 2:20 p. m. , cuando los vecinos escucharon varios disparos que desataron el temor y la preocupación en la zona. Al salir de sus viviendas para averiguar lo ocurrido, encontraron al joven tendido en plena vía pública, en posición decúbito dorsal y en medio de un charco de sangre. Según la información preliminar, la víctima habría recibido cinco impactos de bala, varios de ellos en el rostro, que le causaron la muerte. En el lugar quedaron sus zapatos fuera de posición, mientras los moradores observaban con preocupación la escena y alertaban a las autoridades. Tras conocerse el hecho, efectivos de la Policía Nacional de la Comisaría de El Indio y personal de Serenazgo de Castilla llegaron al lugar para acordonar la zona y realizar las primeras diligencias. Los agentes iniciaron las investigaciones con el objetivo de determinar las circunstancias del ataque e identificar a los responsables. El móvil del asesinato aún no ha sido establecido. Sin embargo, trascendió que una de las hipótesis que se maneja es un posible asalto y robo, aunque esta versión deberá ser corroborada por los investigadores. No se descarta ninguna línea de investigación mientras se recogen testimonios y otros elementos que permitan reconstruir lo sucedido. PASIÓN POR EL FÚTBOL La víctima, que deja una niña en la orfandad, residía en el asentamiento humano Ciudad del Niño y era natural del distrito de Villa María del Triunfo, en Lima . Además, era aficionado al fútbol y había jugado por el club Huáscar de la Liga Distrital de Fútbol de Castilla, donde compartió su pasión por este deporte. En su perfil de Facebook, el joven tenía una frase que reflejaba sus prioridades: “Amor al fútbol y a mi familia”. Su muerte generó consternación entre quienes lo conocían. De acuerdo con los datos proporcionados, Gómez Carreño cumpliría años el próximo 11 de noviembre. 115 HOMICIDIOS Cabe mencionar que con este nuevo asesinato, la cifra de homicidios en la región Piura se elevaría a 115 en lo que va del año, según el registro proporcionado.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/piura-asesinan-a-balazos-a-joven-en-la-via-publica/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Gobierno trabajará en otra salida del río Piura tras rechazo de Chutuque</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>El Ejecutivo autorizó el listado de intervenciones priorizadas para que se ejecuten bajo la modalidad de obras por impuestos, para preparar a las regiones ante el fenómeno El Niño. De un total de 45 intervenciones a nivel nacional por 118 millones de soles, en el caso de la región se dio prioridad a una nueva salida del río Piura hacia las lagunas en el desierto de Sechura. El servicio se denomina “limpieza, descolmatación y conformación de bordos con material propio del cauce del río Piura – bifurcación a río Loco, sector río Piura – río Loco, distrito de Cristo Nos valga, provincia de Sechura”. Según el presidente de la Cámara de Comercio, Javier Bereche se trataría de una tercera alternativa luego que se descartara intervenir con dinamita el sector de Chutuque en el cauce del río. Este sector es considerado como un islote o un tapón de rocas del río de una extensión de 6.7 kilómetros que necesitaba un trabajo de medio año con explosivos y maquinaria minera. “La Cámara de Comercio desde el 8 de julio hizo un llamado al gobierno de Balcázar de empezar estos trabajos de voladura del tapón de Chutuque, pero ahora estamos octubre y no hay tiempo”, indicó. La segunda alternativa era descolmatar un canal de derivación de Chutuque, pero tampoco se consideró. “Unos kilómetros antes de llegar al tapón existe un canal tapado de arena que se usó en 1998. Es un brazo del río de 5 kilómetros que va hacia Pampa de Salinas. Lo malo es que se iba a volver a llenar de sedimento en la primera avenida y tendría que volver a limpiarse en enero”, informó. Esto fue un acuerdo con el gobierno, sin embargo, el lunes salió la resolución ministerial N° 411-2026-Midagri, en el cual aparece el listado que se indica “Han encontrado otra forma de sacar el río hacia las lagunas, que sería por Cristo Nos Valga”, dijo.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/gobierno-trabajara-en-otra-salida-del-rio-piura-tras-rechazo-de-chutuque/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>“Las fotopapeletas tienen contrato”, advierte regidora</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>La regidora y encargada del despacho de alcaldía, Lucy Chunga, se pronunció sobre el anuncio del alcalde electo Miguel Cueva, de anular las fotopapeletas y recordó que se trata de un servicio con un contrato vigente. “Ya son decisiones políticas en las que el nuevo alcalde electo tiene que ver todas las actuaciones y sobre todo decir la forma en cómo lo va a hacer considerando que dentro de la Municipalidad existe un contrato entre la entidad edil y la empresa que presta el servicio de fotopapeletas”, afirmó. Cabe indicar que el 3 de septiembre del 2025, la Municipalidad otorgó la buena pro por dos años para el servicio de instalación, operación y mantenimiento del sistema de fotopapeletas al consorcio Setrapi, conformado por las empresas SEMOECSA SAS y Prototipo del Perú SAC por S/2 millones 072 mil. En esa línea, la regidora consideró que hay un tema contractual que deben analizarse, sobre todo lo relacionado a las penalidades. “Son decisiones políticas que el nuevo alcalde tiene que analizar y ver la mejor salida”, manifestó. Recordó que se promovió el sistema para ordenar el tránsito en ciudad y proteger a la población.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/las-fotopapeletas-tienen-contrato-advierte-regidora/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Extinguen incendios forestales en distritos de Cusco, Ayacucho, Puno, Piura y Huancavelica</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Los incendios reportados en Cusco se registraron entre el 4 y 8 de octubre, los mismos que fueron liquidados por personal municipal distrital y provincial, efectivos de Serenazgo y pobladores locales, dejando un total de 963 hectáreas de cobertura natural destruida, sin daños a la vida y salud de la población.
-Todas estas emergencias se encuentran cerradas.
-Similar situación se presenta en los eventos registrados en las jurisdicciones ayacuchanas, donde el fuego fue sofocado por los respectivos municipios locales, con apoyo de bomberos voluntarios y pobladores locales.
-Hasta el momento se han consumido 576 hectáreas de vegetación y la Evaluación de Daños y Análisis de Necesidades (EDAN) que realizan las municipalidades distritales se mantiene en proceso.
-Asimismo, en Puno, los incendios que se desarrollaron entre el 7 y 8 de octubre también están extinguidos y reportaron 806 hectáreas de vegetación destruida.
-Cabe señalar que en Huacullani se registraron 2 personas heridas, quienes fueron atendidas en el centro de salud local.
-Igualmente, en Sondorillo (Piura) y Santo Tomás de Pata (Huancavelica) el fuego ya cesó y consumió 4.2 ha de cobertura natural.
-Incendios controlados y activos Por otro lado, aún se mantienen activos los incendios forestales que se presentan en los distritos de Mariscal Gamarra, Huancarama y Chuquibambilla (Apurímac); Sihuas (Áncash); mientras que en Carapo (Ayacucho) y Huando (Huancavelica) el fuego ya está controlado.
-De acuerdo a la EDAN que elaboran los gobiernos locales, hasta el momento se reportan, en total, la destrucción de 310 hectáreas de cobertura natural, además de 3 viviendas inhabitables en el distrito de Mariscal Gamarra.
-El Indeci, a través del Centro de Operaciones de Emergencia Nacional (COEN), continúa monitoreando este tipo de eventos que se registran en diferentes regiones, en coordinación con los Centros de Operaciones de Emergencia Regional, Provincial y Distrital, así como con las autoridades respectivas las acciones de respuesta en atención de la población damnificada y afectada.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-extinguen-incendios-forestales-distritos-cusco-ayacucho-puno-piura-y-huancavelica-1095392.aspx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sullana: Acusan a siete policías de presunto cobro de coima</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Siete agentes policiales que laboran en el Área Antidrogas (Areant) de Sullana son investigados preliminarmente por presuntamente solicitar dinero a los familiares de dos mujeres detenidas por tráfico ilícito de drogas, a cambio de omitir actos de su función. PUEDES LEER ► Piura: Anuncia revisión del contrato del sistema de fotopapeletas La situación de los efectivos se agravó luego de que la Policía y la Fiscalía Anticorrupción obtuvieran nuevos indicios durante las diligencias realizadas en las últimas días. Entre los investigados figura el oficial M. A. V., señalado como jefe de la unidad, junto con los suboficiales D. J. R., L. A. V., M. R. L., F. Ch. R., J. Z. T. y E. A. S. Inicialmente, cinco de ellos tenían la condición de testigos, pero los nuevos elementos recabados motivaron que pasaran a ser comprendidos en la investigación. Según las indagaciones preliminares, los policías habrían solicitado inicialmente S/ 50 mil y, posteriormente, utilizando un celular de uno de los detenidos, se habrían comunicado con sus familiares para acordar el pago de S/ 30 mil. Como parte de ese supuesto trato, se habría concretado la entrega de S/ 5 mil en billetes previamente fotocopiados por las autoridades anticorrupción. El Informe Policial n.° 35 de la Dirección Contra la Corrupción de Piura habría sido determinante para que el Segundo Despacho de la Fiscalía Anticorrupción de Sullana modificara la situación de los implicados y dispusiera nuevas diligencias. Entre las medidas solicitadas figuran las declaraciones de los siete investigados y el levantamiento del secreto de las comunicaciones y del secreto bancario, con el propósito de esclarecer los hechos y determinar si habría responsabilidades. Las pesquisas apuntan a una posible concertación entre los agentes, extremo que deberá ser corroborado. Como se informó, el 2 de octubre, uno de los policías investigados recibió el dinero fotocopiado, pero al advertir que sus colegas se disponían a intervenir en flagrancia, escapó en motocicleta junto a otro policía.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/sullana-acusan-a-siete-policias-de-presunto-cobro-de-coima/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sechura: Instalan mesa de diálogo tras paro de pescadores</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>La recién instalada mesa de diálogo entre el Ministerio de la Producción y los gremios pesqueros artesanales, que contó con la asistencia de unas 16 asociaciones y más de seis invitados, dio inicio a un proceso de negociación tras el paro de pescadores artesanales, orientado al reordenamiento del sector. Durante este primer encuentro, realizado en Lima , los dirigentes expusieron sus petitorios con el objetivo de garantizar la estabilidad operativa y económica de los pescadores artesanales durante lo que resta del año. Según explicó Julio Seminario Panta, secretario de la Asociación Unificada de Pescadores Artesanales de la Bahía de Sechura , la mesa de trabajo ha establecido un nuevo esquema en el que todas las solicitudes deberán presentarse por escrito, eliminando las intervenciones verbales y las votaciones a mano alzada. Las organizaciones acreditadas tienen como plazo límite el viernes 17 de octubre para presentar sus informes y propuestas por escrito, los cuales se debatirán formalmente en la primera sesión de trabajo, programada para el viernes 23 de octubre. El petitorio del gremio de Sechura abarca cinco puntos clave para la sostenibilidad de la actividad pesquera: continuidad de las faenas hasta diciembre, modificación de la Resolución N.° 348, revisión de los topes de captura, medidas de alivio frente al Fenómeno El Niño y transparencia e información técnica. Seminario Panta advirtió que la pota se ha alejado de su zona habitual, lo que obliga a las embarcaciones a desplazarse a mayores distancias, hacia zonas frente a Chicama, para poder faenar.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/sechura-instalan-mesa-de-dialogo-tras-paro-de-pescadores/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Somos Perú espera que JNE ordene el recuento de votos en S. Juan de Bigote</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>El recurso de apelación de Somos Perú contra la resolución del Jurado Electoral Especial de Morropón, que anuló las elecciones en San Juan de Bigote, busca que el Jurado Nacional de Elecciones (JNE) disponga el recuento de votos entre el material que se pudo recuperar en el local. Según el abogado y personal legal titular de la organización política, Alex Ochoa Huamán, falta mayor sustento en la resolución del JEE Morropón. “Sí es probable [que se ordene el recuento de votos] dado que los fundamentos en la resolución de nulidad carecen de motivación suficiente. El acta fiscal y los informes de ODPE no son suficientes para demostrar que el material recuperado no se pueda contabilizar”, informó el abogado. Como se informó, el JEE de Morropón declaró la nulidad de las elecciones en el distrito de San Juan de Bigote luego de los actos de vandalismo contra el material electoral. En su resolución, el JEE señala que no hay certeza para verificar que el material recuperado y lacrado por la Fiscalía, no haya sido alterado porque se rompió la cadena de custodia. “La resolución se basa en informes, más no de la verificación del material recuperado. Dicho material electoral aún sigue lacrado y custodiado, en la Fiscalía de Derechos Humanos. El 2do Despacho de Fiscalia de Chulucanas envió el día de ayer el paquete electoral lacrado” , informó. El abogado también sostiene que no se puede generalizar lo sucedido con el material electoral, si no hay sustento preciso. “Se cuestiona el alcance de esa conclusión y solicitamos examinar su sustento: qué material abarca, qué custodia tuvo cada paquete y porqué la ruptura de las cédulas invalida también posibles ejemplares auténticos de actas o copias entregadas antes del incidente. Si el oficio contiene soporte individualizado suficiente, deberá ponderarse expresamente ”, sostuvo.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/somos-peru-espera-que-jne-ordene-el-recuento-de-votos-en-s-juan-de-bigote/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Piura: Anuncia revisión del contrato del sistema de fotopapeletas</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>El alcalde electo de Piura, Miguel Cueva Celi, ratificó que revisará el contrato con la empresa que aplica las fotopapeletas por infracciones de tránsito, al considerar que se trata de “un abuso” en contra de los conductores piuranos. Sostuvo que se buscará un acuerdo con la empresa a cargo de la fiscalización electrónica para llegar a un final feliz. “No ha sido el momento para las fotopapeletas y se tendrá que revisar el contrato y se verá a qué final feliz llego con la empresa [...] Piura está destruida ”, comentó Cueva. De otro lado, la autoridad municipal electa no dudó en calificar el sistema como un abuso. “ Las fotopapeletas de mayo las están pasando a cobranza coactiva. A una profesora le han descontado casi S/1.000 porque el vehículo de su hijo está a su nombre. Eso es un abuso y no puede ser. Definitivamente, lo revisaré porque Piura no está preparada para estas fotopapeletas y con estos costos”, manifestó Cueva. El alcalde electo resaltó que la ciudad tiene vías destruidas y no se puede castigar a los conductores de esta manera. “Es un abuso” Asimismo, Cueva advirtió que una de las finalidades del sistema de fotopapeletas sería la recaudación a favor de la comuna. “Con ese tipo de abuso no puedes querer salir de lo rojo que tienen en gastos corrientes por exceso de personal que la misma gestión ha tomado. Es una desesperación que no tienen cómo pagar al personal y no puedes utilizar este tipo de medios. Estoy mortificado por este tipo de abuso” , declaró Cueva. Recaudación Según una investigación de l portal Norte Sostenible, la Municipalidad de Piura proyectó que en el primer año de funcionamiento del sistema se podrían imponer 103 mil 830 papeletas. Esto podría generar una recaudación de 4.2 millones de soles, aproximadamente, hasta el 15 de mayo del año 2027 , fecha en que se cumple el primer año. Cabe indicar que en setiembre del 2025, la comuna otorgó la buena pro para el servicio de instalación, operación y mantenimiento del sistema de fotopapeletas al consorcio Setrapi, conformado por las empresas SEMOECSA SAS (de origen ecuatoriano) y la peruana Prototipo del Perú SAC. La contratista cobraría S/ 2 millones 072 mil 824.46 por brindar el servicio en un periodo de 730 días calendarios. De otro lado, Cueva señaló que otro problema del sistema es que no hubo una adecuada difusión del sistema entre la población. “No hubo socialización [adecuada] del tema y han tomado por sorpresa a los piuranos”, manifestó Cueva, en cuya gestión se tendrá que analizar este millonario contrato.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-anuncia-revision-del-contrato-del-sistema-de-fotopapeletas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B23" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Minam y gobiernos regionales impulsan acciones para conservar la biodiversidad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Así lo informó el Minam que precisó que en la cita participaron representantes de Arequipa, Ayacucho, Cajamarca, Áncash, Lambayeque, Amazonas, Apurímac, Ica, Madre de Dios, Puno y Piura , entre otras regiones.
+Durante el encuentro se abordó la articulación de las prioridades regionales con la Estrategia Nacional de Diversidad Biológica al 2050 y su Plan de Acción al 2030.
+Prioridades regionales Sostuvo que las Estrategias Regionales de Diversidad Biológica permiten a los gobiernos regionales identificar y priorizar los ecosistemas, especies, servicios ecosistémicos y territorios que requieren atención.
+Asimismo, contribuyen a vincular estas prioridades con inversiones públicas, cooperación internacional y otras fuentes de financiamiento para su implementación.
+Durante la reunión, el Minam presentó la guía que orientará a los gobiernos regionales en la elaboración y actualización de sus estrategias, desde el diagnóstico y la definición de prioridades hasta su aprobación, implementación y seguimiento.
+Como resultado de la jornada, el Minam y los gobiernos regionales trabajarán conjuntamente en la definición de hojas de ruta para avanzar, desde diciembre de 2026 y durante 2027 , en la elaboración y actualización de sus Estrategias Regionales de Diversidad Biológica, con asistencia técnica del sector.
+Por último, el Minam resaltó que con estas acciones promueve una gestión descentralizada de la biodiversidad para que las prioridades de cada región se traduzcan en acciones e inversiones orientadas a la conservación, recuperación y uso sostenible de la diversidad biológica del país.
+Más en Andina: Hace más de 1,400 años aproximadamente, la muerte repentina de un infante miembro de la élite mochica, generó un importante ritual funerario al pie de la huaca de la Luna, uno de los templos religiosos más importantes de esta sociedad prehispánica, que se asentó en el valle del actual distrito de Moche, en la provincia de Trujillo.??https://t.co/GeKo8fnBPE (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 11, 2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-minam-y-gobiernos-regionales-impulsan-acciones-para-conservar-biodiversidad-1095488.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
         <v>46305</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>El Niño: Vivienda capacita a operadores de motobombas en Piura para reforzar respuesta</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Durante la jornada, los participantes recibieron instrucción teórica y práctica sobre el funcionamiento, operación y mantenimiento de las motobombas, con el propósito de que puedan utilizar estos equipos de manera adecuada y oportuna durante una emergencia.
+La capacitación estuvo a cargo de especialistas de la Unidad para la Mejora de la Prestación de los Servicios (UMPS) del Programa Nacional de Saneamiento Urbano (PNSU) y estuvo dirigida a los operadores que tendrán a su cargo la primera respuesta con estos equipos para facilitar la evacuación de agua y contribuir a reducir los efectos de posibles inundaciones.
+El sector Vivienda también informó que cuenta con maquinaria y equipos disponibles y preparados para intervenir ante situaciones de emergencia, en coordinación con las autoridades locales, como parte de las acciones de prevención frente al Fenómeno El Niño.
+En setiembre, el MVCS entregó 20 motobombas completamente equipadas a siete gobiernos locales de Piura para ayudar en la evacuación oportuna de agua y reducir el impacto de posibles lluvias intensas e inundaciones.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-el-nino-vivienda-capacita-a-operadores-motobombas-piura-para-reforzar-respuesta-1095453.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cobros en recibo de agua pasan de S/50 a S/300 en Sullana</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Nuevamente, las oficinas de EPS Grau se convirtieron en escenario de reclamos. Decenas de ciudadanos llegan para exigir una explicación por el incremento de sus recibos de agua potable, cuyos montos, según denunciaron, se han elevado considerablemente en los últimos meses. Los usuarios mostraron recibos con cobros de 200 y hasta 300 soles mensuales, cuando anteriormente, según señalaron, sus consumos no superaban los 50 o 70 soles. Para los afectados, estos cobros no guardaría relación con el servicio que reciben, debido a las constantes deficiencias que se presentan en el abastecimiento. “Esto ya se ha vuelto una estafa, una viveza por parte de la empresa”, expresó uno de los usuarios, reflejando el malestar que existe entre los vecinos que aseguran no tener dinero para pagar. Durante la jornada, las instalaciones permanecieron abarrotadas de personas que esperaban ser atendidas. Sin embargo, lo que más indignó a los vecinos fue, según manifestaron, que después de realizar sus reclamos continúan sin obtener respuesta positiva. Al respecto, el jefe zonal de Sullana de la EPS Grau, Luis Ho, señaló que el incremento tarifario no lo estipula la entidad, sino Sunass. Resaltó que se recibirán las quejas para que luego un inspector acuda a la vivienda a revisar si corresponde el monto facturado. En tanto, la Superintendencia Nacional del Servicio de Saneamiento (Sunass), informó que la tarifa se aprueba en base a la propuesta de EPS Grau y que las tarifas del quinto año regulatorio se han dado en enero y no en los últimos meses.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/cobros-en-recibo-de-agua-pasan-de-s-50-a-s-300-en-sullana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>El Niño: ANIN invierte S/ 1.4 millones para prevenir desbordes del río La Leche</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>La intervención abarca cerca de dos kilómetros de cauce, demanda una inversión superior a S/ 1.4 millones y tiene un plazo aproximado de 50 días.
 Para ejecutarla, la ANIN movilizó equipos de su propia flota: una excavadora, un cargador frontal, cuatro volquetes y dos tractores, lo que le permite intervenir de forma directa y oportuna.
@@ -1025,55 +1285,27 @@
 Estas acciones se realizan gracias a un convenio de cooperación interinstitucional, el Gobierno Regional de Lambayeque proporciona la maquinaria necesaria y la ANIN suministra el combustible para mantener las labores de limpieza y descolmatación del cauce, así como la conformación de un dique con material de la zona, de acuerdo con la ficha técnica del sector.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-el-nino-anin-invierte-s-14-millones-para-prevenir-desbordes-del-rio-leche-1095397.aspx</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B27" s="2" t="n">
         <v>46305</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>El Niño: Vivienda capacita a operadores de motobombas en Piura para reforzar respuesta</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Durante la jornada, los participantes recibieron instrucción teórica y práctica sobre el funcionamiento, operación y mantenimiento de las motobombas, con el propósito de que puedan utilizar estos equipos de manera adecuada y oportuna durante una emergencia.
-La capacitación estuvo a cargo de especialistas de la Unidad para la Mejora de la Prestación de los Servicios (UMPS) del Programa Nacional de Saneamiento Urbano (PNSU) y estuvo dirigida a los operadores que tendrán a su cargo la primera respuesta con estos equipos para facilitar la evacuación de agua y contribuir a reducir los efectos de posibles inundaciones.
-El sector Vivienda también informó que cuenta con maquinaria y equipos disponibles y preparados para intervenir ante situaciones de emergencia, en coordinación con las autoridades locales, como parte de las acciones de prevención frente al Fenómeno El Niño.
-En setiembre, el MVCS entregó 20 motobombas completamente equipadas a siete gobiernos locales de Piura para ayudar en la evacuación oportuna de agua y reducir el impacto de posibles lluvias intensas e inundaciones.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-el-nino-vivienda-capacita-a-operadores-motobombas-piura-para-reforzar-respuesta-1095453.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Comando Unificado desbarató bandas criminales e incautó armas en primeros 3 días de labor</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Así lo dio a conocer el comandante general de la Policía Nacional del Perú, general Fredy López, durante la presentación de las primeras acciones del Comando Unificado, actividad en la que participó la presidenta de la república, Keiko Fujimori; así como el presidente del Consejo de Ministros, Luis Galarreta; y el titular de Defensa, Rafael Belaunde.
 Lee también: [ Presidenta Keiko Fujimori: Es momento de definición hoy que enfrentamos a la delincuencia ] ??Presidenta Keiko Fujimori: Es momento de definición hoy que enfrentamos a la delincuenciahttps://t.co/NfZ3XCUopj https://t.co/RrUcqDRFkM — Agencia Andina (@Agencia_Andina) October 11, 2026 El alto mando policial indicó que en las intervenciones contra la criminalidad participaron de manera conjunta efectivos de las Fuerzas Armadas y de la Policía Nacional , parte de los cuales se trasladó desde la capital hacia las regiones del país.
@@ -1093,27 +1325,27 @@
 Añadió que conforme se vaya generando información de inteligencia sobre los blancos de alto valor estratégico de las organizaciones criminales, las Fuerza de Operaciones Especiales de las Fuerzas Armadas intervendrán en apoyo de la Policía Nacional.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-comando-unificado-desbarato-bandas-criminales-e-incauto-armas-primeros-3-dias-labor-1095461.aspx</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B28" s="2" t="n">
         <v>46305</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Chiclayo: títulos de propiedad a colegios permitirán dar servicios básicos a estudiantes</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>?? ¡Colegios de Chiclayo recibieron títulos de propiedad!La presidenta de la República, Keiko Fujimori, entregó títulos de propiedad a colegios de Chiclayo, lo que les permitirá gestionar el acceso a agua potable y otros servicios esenciales.#NDPhttps://t.co/ynxHBrT1kj — Ministerio de Educación (@MineduPeru) October 10, 2026 La entrega de estos títulos forma parte del proceso de formalización que el Ministerio de Educación (Minedu), bajo la gestión del ministro José Antonio Chang Escobedo, viene desarrollando a nivel nacional para que más colegios públicos cuenten con la documentación de sus terrenos y puedan gestionar el acceso a servicios esenciales.
 Lee también: [ Solo 5.7% de peruanos tendría cuentas de inversión bursátil, ¿puede crecer esta cifra? ] Trabajo integral Como parte de esta estrategia nacional de formalización, el Viceministerio de Gestión Institucional y la Superintendencia Nacional de los Registros Públicos, Sunarp, han suscrito un importante convenio de cooperación interinstitucional para acelerar la titulación de cientos de colegios públicos que, hasta la fecha, de manera increíble, no cuentan con su documentación oficial.
@@ -1124,162 +1356,27 @@
 El Ministerio de Educación continuará trabajando para que los colegios públicos cuenten con la titulación de sus terrenos, un paso necesario para facilitar el acceso a servicios esenciales y avanzar hacia una infraestructura educativa digna, segura y adecuada para el aprendizaje .</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-chiclayo-titulos-propiedad-a-colegios-permitiran-dar-servicios-basicos-a-estudiantes-1095463.aspx</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
         <v>46305</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Elecciones 2026: Santiago Paz quedaría fuera de carrera con fallo de JEE Morropón</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>El Jurado Electoral Especial de Morropón declaró la nulidad total de la elección en el distrito de San Juan de Bigote, lo cual deja sin opciones al candidato de Somos Perú, Santiago Paz, de pasar a la segunda vuelta. En la resolución N° 00811-2026-JEE-MORR/JNE, los magistrados indicaron que se rompió la cadena de custodia de las cédulas y actas, lo cual hace inviable corroborar si los datos que ahí aparecen son auténticos. “La ausencia de información de las actas de las 23 mesas y la ruptura general de la cadena de custodia, valoradas junto con los daños y la recuperación parcial descritos en el acta fiscal, impiden considerar que el simple conteo del material hallado reconstruya de manera confiable la votación distrital. El recuento no restablece por sí mismo la integridad anterior del conjunto recuperado”, se lee en el documento. Nulidad Para el JEE Morropón se ha acreditado la imposibilidad material de recomponer el resultado auténtico de la voluntad popular, con lo cual la nulidad total alcanza a las elecciones de gobernador. Sobre el tema, el candidato de Somos Perú, Santiago Paz, calificó esta decisión de “injusta, nefasta y que no se ajusta a la ley”. Agregó que interpondrán recurso de apelación ante el Jurado Nacional de Elecciones (JNE). Según Paz, al anular la elección en San Juan de Bigote, lo sacan de carrera. “Las nuevas elecciones [que se harán el distrito] nos dejan fuera de esta contienda electoral”, afirmó. Agrega que luego de la resolución de las 186 actas observadas, la diferencia respecto al candidato Guillermo La Torre de Podemos se podía acortar a un promedio de 1.500 votos. “Con Bigote estaríamos en segunda vuelta con una ventaja amplia en relación a nuestro rival. Hay cifras de 1.500 a 2.000 votos sobre nuestro rival, pero eso se tiene que verificar”, afirmó. Paz recordó que ese distrito es un bastión de Somos Perú con más de 6.000 electores y en el cual el candidato de Podemos no era favorito. En esa línea, Paz exigió que la Fiscalía entregue a la ONPE las cajas con el material lacrado que lograron recuperar de 22 mesas de sufragio. “Iremos hasta las últimas instancias. No es un tema mío sino de respeto de miles de militantes que nos han puesto en segunda vuelta”, finalizó.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/elecciones-2026-santiago-paz-quedaria-fuera-de-carrera-con-fallo-de-jee-morropon/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Comando Unificado: desarticulan dos bandas criminales en Lima</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>El primer operativo se ejecutó a las 02:32 horas en Villa El Salvador , tras el asalto y robo de un vehículo, ocurrido la noche del viernes 9 de octubre, a la altura del peaje de Villa.
-Lee también: [ Mininter: Inteligencia y PNP capturan en Piura a 7 presuntos integrantes de Tren de Aragua ] Como resultado de la intervención, la Policía desarticuló a la banda criminal “Los Malditos de la Panamericana” y detuvo a dos de sus presuntos integrantes.
-Durante los hechos, un sujeto aún no identificado fue abatido y otros dos resultaron heridos por proyectiles de arma de fuego.
-Se trata de José Enrique Solórzano Cedeño, de 34 años, de nacionalidad venezolana, y Wilfredo Martínez Cedeño, de 23 años, de nacionalidad peruana.
-En esta intervención, los efectivos policiales incautaron una pistola Glock calibre 380, encontrada debajo del asiento del copiloto del vehículo.
-Ofensiva nacional El segundo operativo se realizó a la altura del cruce de las avenidas Canta Callao y Alisos , donde la Policía desarticuló a la banda criminal “Los Chukis de Huandoy”.
-La intervención permitió detener a Dervin Gonzales Hernández, de 25 años, de nacionalidad venezolana.
-Durante esta operación, otro sujeto, cuya identidad no ha sido establecida, fue abatido tras un enfrentamiento con personal policial.
-Como parte de las diligencias, los agentes incautaron una pistola marca Bersa, modelo Thunder, calibre 380, abastecida con tres municiones, así como dos cargadores de fusil AKM con 40 municiones.
-El caso quedó a disposición del Departamento de Investigación Criminal (Depincri) de Los Olivos .
-Estas intervenciones forman parte de la ofensiva nacional contra el crimen organizado , que busca enfrentar a las organizaciones delictivas, retirar armas de circulación y reforzar la capacidad de respuesta policial frente a hechos que amenazan la seguridad de la ciudadanía.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-comando-unificado-desarticulan-dos-bandas-criminales-lima-1095470.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Cobros en recibo de agua pasan de S/50 a S/300 en Sullana</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Nuevamente, las oficinas de EPS Grau se convirtieron en escenario de reclamos. Decenas de ciudadanos llegan para exigir una explicación por el incremento de sus recibos de agua potable, cuyos montos, según denunciaron, se han elevado considerablemente en los últimos meses. Los usuarios mostraron recibos con cobros de 200 y hasta 300 soles mensuales, cuando anteriormente, según señalaron, sus consumos no superaban los 50 o 70 soles. Para los afectados, estos cobros no guardaría relación con el servicio que reciben, debido a las constantes deficiencias que se presentan en el abastecimiento. “Esto ya se ha vuelto una estafa, una viveza por parte de la empresa”, expresó uno de los usuarios, reflejando el malestar que existe entre los vecinos que aseguran no tener dinero para pagar. Durante la jornada, las instalaciones permanecieron abarrotadas de personas que esperaban ser atendidas. Sin embargo, lo que más indignó a los vecinos fue, según manifestaron, que después de realizar sus reclamos continúan sin obtener respuesta positiva. Al respecto, el jefe zonal de Sullana de la EPS Grau, Luis Ho, señaló que el incremento tarifario no lo estipula la entidad, sino Sunass. Resaltó que se recibirán las quejas para que luego un inspector acuda a la vivienda a revisar si corresponde el monto facturado. En tanto, la Superintendencia Nacional del Servicio de Saneamiento (Sunass), informó que la tarifa se aprueba en base a la propuesta de EPS Grau y que las tarifas del quinto año regulatorio se han dado en enero y no en los últimos meses.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/cobros-en-recibo-de-agua-pasan-de-s-50-a-s-300-en-sullana/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Delincuentes desvalijan tienda de celulares en pleno centro de Catacaos</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>La delincuencia vuelve a golpear el corazón comercial de Catacaos. Esta vez, delincuentes ingresaron durante la madrugada a una tienda dedicada a la venta de celulares, ubicada en la intersección de la calle Chorrillos con la avenida José Cayetano Heredia, de donde sustrajeron mercadería y dejaron el establecimiento completamente revuelto. Según información proporcionada por efectivos de Serenazgo, alrededor de las 3:00 de la madrugada recibieron la alerta sobre un posible robo y se desplazaron hasta el establecimiento. Al llegar, encontraron la puerta enrollable parcialmente levantada, situación que despertó sus sospechas y motivó la comunicación inmediata con la Policía Nacional. Tras ser alertados, los agentes policiales acudieron al lugar para inspeccionar la escena y realizar las diligencias correspondientes. En el interior del negocio habrían encontrado un saco que presuntamente iba a ser utilizado por los delincuentes para trasladar la mercadería sustraída. De acuerdo con la información preliminar, los ladrones se habrían llevado carcasas para celulares, luego de violentar la puerta enrollable para ingresar al establecimiento. Aunque dejaron todo revuelto, no habrían conseguido llevarse los equipos celulares, considerados los productos de mayor valor del negocio. PRECUPACIÓN Sin embargo, este nuevo hecho genera preocupación entre los comerciantes, pues hace aproximadamente un mes la misma tienda habría sido víctima de otro robo, en aquella ocasión de celulares valorizados en más de 30 mil soles. Ante la reiteración de estos hechos delictivos, los comerciantes de las zonas aledañas hicieron un llamado a las autoridades policiales para que refuercen el patrullaje en el centro de Catacaos, especialmente durante la madrugada y en los sectores donde se concentra la actividad comercial. Los vecinos y empresarios expresaron su preocupación por la inseguridad que afecta al distrito y exigieron acciones concretas para prevenir nuevos asaltos y proteger sus negocios. La reiteración de robos mantiene en alerta a los comerciantes, quienes temen que sus establecimientos vuelvan a convertirse en blanco de la delincuencia.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/delincuentes-desvalijan-tienda-de-celulares-en-pleno-centro-de-catacaos/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>JEE declara válida la elección de Canchaque: Renovación Popular no apareció en cédula</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>El Jurado Electoral Especial de Morropón declaró válida la elección distrital en Canchaque pese a que se registró una grave irregularidad que perjudicó al partido Renovación Popular. Según el personero, el símbolo del partido no apareció en la cédula de sufragio para alcalde distrital, a pesar que el candidato estaba habilitado. El JEE consideró que era una grave irregularidad que afectó el derecho del candidato, sin embargo, consideró que no alteró resultados. “Ni la votación obtenida por “Renovación” en la elección regional utilizada como referencia, ni siquiera la consideración hipotética de la totalidad de votos blancos y nulos como potenciales votos a su favor, permiten advertir una incidencia suficiente para sostener que la omisión de incorporación de dicha organización en la cédula distrital hubiese modificado el resultado”, se lee.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/jee-declara-valida-la-eleccion-de-canchaque-renovacion-popular-no-aparecio-en-cedula/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Mininter: Inteligencia y PNP capturan en Piura a 7 presuntos integrantes de Tren de Aragua</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>La intervención se realizó en el marco de las acciones de inteligencia para anticiparse al crimen y recuperar el control territorial en el país, informa el Ministerio del Interior.
 Las investigaciones se iniciaron a partir de las denuncias de las víctimas, quienes señalaron que eran amenazadas y obligadas a pagar determinadas sumas de dinero para continuar con sus actividades comerciales.
@@ -1295,34 +1392,9 @@
 Más en Andina:</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-mininter-inteligencia-y-pnp-capturan-piura-a-7-presuntos-integrantes-tren-aragua-1095467.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Sucamec incauta 29 armas y cerca de 200 kilos de explosivos en Piura y Ayacucho</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>La Superintendencia Nacional de Control de Servicios de Seguridad, Armas, Municiones y Explosivos de Uso Civil (Sucamec) incautó en Ayacucho y Piura 29 armas de fuego y alrededor de 198 kilos de material explosivo que se encontraban fuera de las condiciones de autorización y seguridad. En San Juan Bautista, Ayacucho, la Sucamec retiró 23 armas de fuego de un establecimiento cuya autorización se encontraba vencida y que incumplía las condiciones exigidas para la custodia de armamento. En el marco de la estrategia del Ministerio del Interior (Mininter) para anticiparse al crimen y recuperar el control territorial, el material incautado en Ayacucho comprende 17 pistolas, cuatro revólveres y dos carabinas, informó la institución en una nota de prensa. Mientras tanto, en Paita (Piura) fueron retiradas otras seis armas de una empresa de vigilancia privada que no cumplía los requisitos para prestar servicios de seguridad con armamento: cuatro escopetas y dos carabinas. El superintendente nacional de la Sucamec, Eswin Manay Guerrero, destacó que estas acciones responden al compromiso de la gestión del ministro del Interior, César Astudillo, de reforzar la fiscalización a nivel nacional y cerrar espacios al accionar criminal. “Nuestra prioridad es fortalecer el control para contribuir a la lucha frontal contra la inseguridad y proteger a la ciudadanía –comentó Manay–. Cada arma que retiramos de una situación irregular reduce el riesgo de que pueda ser desviada o utilizada para fines ilícitos”. Explosivos sin autorización En Talara Alta, Piura, la Sucamec –junto con el Ministerio Público y unidades especializadas de la Policía Nacional del Perú– intervino un inmueble donde se almacenaban alrededor de 198 kilos de material explosivo “trasladado desde Loreto sin contar con la autorización correspondiente”. El material, utilizado para la perforación de pozos petroleros, fue retirado de inmediato debido al riesgo que representaba su almacenamiento en un lugar no autorizado, precisó la entidad. “Estas acciones forman parte del fortalecimiento de los controles impulsados por el Ministerio del Interior, a través de la Sucamec, para prevenir el desvío y uso ilícito de armas, municiones y explosivos, y contribuir a la seguridad de la ciudadanía”, finalizó el Mininter.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/sucamec-incauta-29-armas-y-cerca-de-200-kilos-de-explosivos-en-piura-y-ayacucho/</t>
         </is>
       </c>
     </row>
@@ -1333,14 +1405,341 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Comando Unificado: desarticulan dos bandas criminales en Lima</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>El primer operativo se ejecutó a las 02:32 horas en Villa El Salvador , tras el asalto y robo de un vehículo, ocurrido la noche del viernes 9 de octubre, a la altura del peaje de Villa.
+Lee también: [ Mininter: Inteligencia y PNP capturan en Piura a 7 presuntos integrantes de Tren de Aragua ] Como resultado de la intervención, la Policía desarticuló a la banda criminal “Los Malditos de la Panamericana” y detuvo a dos de sus presuntos integrantes.
+Durante los hechos, un sujeto aún no identificado fue abatido y otros dos resultaron heridos por proyectiles de arma de fuego.
+Se trata de José Enrique Solórzano Cedeño, de 34 años, de nacionalidad venezolana, y Wilfredo Martínez Cedeño, de 23 años, de nacionalidad peruana.
+En esta intervención, los efectivos policiales incautaron una pistola Glock calibre 380, encontrada debajo del asiento del copiloto del vehículo.
+Ofensiva nacional El segundo operativo se realizó a la altura del cruce de las avenidas Canta Callao y Alisos , donde la Policía desarticuló a la banda criminal “Los Chukis de Huandoy”.
+La intervención permitió detener a Dervin Gonzales Hernández, de 25 años, de nacionalidad venezolana.
+Durante esta operación, otro sujeto, cuya identidad no ha sido establecida, fue abatido tras un enfrentamiento con personal policial.
+Como parte de las diligencias, los agentes incautaron una pistola marca Bersa, modelo Thunder, calibre 380, abastecida con tres municiones, así como dos cargadores de fusil AKM con 40 municiones.
+El caso quedó a disposición del Departamento de Investigación Criminal (Depincri) de Los Olivos .
+Estas intervenciones forman parte de la ofensiva nacional contra el crimen organizado , que busca enfrentar a las organizaciones delictivas, retirar armas de circulación y reforzar la capacidad de respuesta policial frente a hechos que amenazan la seguridad de la ciudadanía.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-comando-unificado-desarticulan-dos-bandas-criminales-lima-1095470.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Elecciones 2026: Santiago Paz quedaría fuera de carrera con fallo de JEE Morropón</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>El Jurado Electoral Especial de Morropón declaró la nulidad total de la elección en el distrito de San Juan de Bigote, lo cual deja sin opciones al candidato de Somos Perú, Santiago Paz, de pasar a la segunda vuelta. En la resolución N° 00811-2026-JEE-MORR/JNE, los magistrados indicaron que se rompió la cadena de custodia de las cédulas y actas, lo cual hace inviable corroborar si los datos que ahí aparecen son auténticos. “La ausencia de información de las actas de las 23 mesas y la ruptura general de la cadena de custodia, valoradas junto con los daños y la recuperación parcial descritos en el acta fiscal, impiden considerar que el simple conteo del material hallado reconstruya de manera confiable la votación distrital. El recuento no restablece por sí mismo la integridad anterior del conjunto recuperado”, se lee en el documento. Nulidad Para el JEE Morropón se ha acreditado la imposibilidad material de recomponer el resultado auténtico de la voluntad popular, con lo cual la nulidad total alcanza a las elecciones de gobernador. Sobre el tema, el candidato de Somos Perú, Santiago Paz, calificó esta decisión de “injusta, nefasta y que no se ajusta a la ley”. Agregó que interpondrán recurso de apelación ante el Jurado Nacional de Elecciones (JNE). Según Paz, al anular la elección en San Juan de Bigote, lo sacan de carrera. “Las nuevas elecciones [que se harán el distrito] nos dejan fuera de esta contienda electoral”, afirmó. Agrega que luego de la resolución de las 186 actas observadas, la diferencia respecto al candidato Guillermo La Torre de Podemos se podía acortar a un promedio de 1.500 votos. “Con Bigote estaríamos en segunda vuelta con una ventaja amplia en relación a nuestro rival. Hay cifras de 1.500 a 2.000 votos sobre nuestro rival, pero eso se tiene que verificar”, afirmó. Paz recordó que ese distrito es un bastión de Somos Perú con más de 6.000 electores y en el cual el candidato de Podemos no era favorito. En esa línea, Paz exigió que la Fiscalía entregue a la ONPE las cajas con el material lacrado que lograron recuperar de 22 mesas de sufragio. “Iremos hasta las últimas instancias. No es un tema mío sino de respeto de miles de militantes que nos han puesto en segunda vuelta”, finalizó.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/elecciones-2026-santiago-paz-quedaria-fuera-de-carrera-con-fallo-de-jee-morropon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Extinguen incendios forestales en distritos de Cusco, Ayacucho, Puno, Piura y Huancavelica</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Los incendios reportados en Cusco se registraron entre el 4 y 8 de octubre, los mismos que fueron liquidados por personal municipal distrital y provincial, efectivos de Serenazgo y pobladores locales, dejando un total de 963 hectáreas de cobertura natural destruida, sin daños a la vida y salud de la población.
+Todas estas emergencias se encuentran cerradas.
+Similar situación se presenta en los eventos registrados en las jurisdicciones ayacuchanas, donde el fuego fue sofocado por los respectivos municipios locales, con apoyo de bomberos voluntarios y pobladores locales.
+Hasta el momento se han consumido 576 hectáreas de vegetación y la Evaluación de Daños y Análisis de Necesidades (EDAN) que realizan las municipalidades distritales se mantiene en proceso.
+Asimismo, en Puno, los incendios que se desarrollaron entre el 7 y 8 de octubre también están extinguidos y reportaron 806 hectáreas de vegetación destruida.
+Cabe señalar que en Huacullani se registraron 2 personas heridas, quienes fueron atendidas en el centro de salud local.
+Igualmente, en Sondorillo (Piura) y Santo Tomás de Pata (Huancavelica) el fuego ya cesó y consumió 4.2 ha de cobertura natural.
+Incendios controlados y activos Por otro lado, aún se mantienen activos los incendios forestales que se presentan en los distritos de Mariscal Gamarra, Huancarama y Chuquibambilla (Apurímac); Sihuas (Áncash); mientras que en Carapo (Ayacucho) y Huando (Huancavelica) el fuego ya está controlado.
+De acuerdo a la EDAN que elaboran los gobiernos locales, hasta el momento se reportan, en total, la destrucción de 310 hectáreas de cobertura natural, además de 3 viviendas inhabitables en el distrito de Mariscal Gamarra.
+El Indeci, a través del Centro de Operaciones de Emergencia Nacional (COEN), continúa monitoreando este tipo de eventos que se registran en diferentes regiones, en coordinación con los Centros de Operaciones de Emergencia Regional, Provincial y Distrital, así como con las autoridades respectivas las acciones de respuesta en atención de la población damnificada y afectada.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-extinguen-incendios-forestales-distritos-cusco-ayacucho-puno-piura-y-huancavelica-1095392.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Gobierno trabajará en otra salida del río Piura tras rechazo de Chutuque</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>El Ejecutivo autorizó el listado de intervenciones priorizadas para que se ejecuten bajo la modalidad de obras por impuestos, para preparar a las regiones ante el fenómeno El Niño. De un total de 45 intervenciones a nivel nacional por 118 millones de soles, en el caso de la región se dio prioridad a una nueva salida del río Piura hacia las lagunas en el desierto de Sechura. El servicio se denomina “limpieza, descolmatación y conformación de bordos con material propio del cauce del río Piura – bifurcación a río Loco, sector río Piura – río Loco, distrito de Cristo Nos valga, provincia de Sechura”. Según el presidente de la Cámara de Comercio, Javier Bereche se trataría de una tercera alternativa luego que se descartara intervenir con dinamita el sector de Chutuque en el cauce del río. Este sector es considerado como un islote o un tapón de rocas del río de una extensión de 6.7 kilómetros que necesitaba un trabajo de medio año con explosivos y maquinaria minera. “La Cámara de Comercio desde el 8 de julio hizo un llamado al gobierno de Balcázar de empezar estos trabajos de voladura del tapón de Chutuque, pero ahora estamos octubre y no hay tiempo”, indicó. La segunda alternativa era descolmatar un canal de derivación de Chutuque, pero tampoco se consideró. “Unos kilómetros antes de llegar al tapón existe un canal tapado de arena que se usó en 1998. Es un brazo del río de 5 kilómetros que va hacia Pampa de Salinas. Lo malo es que se iba a volver a llenar de sedimento en la primera avenida y tendría que volver a limpiarse en enero”, informó. Esto fue un acuerdo con el gobierno, sin embargo, el lunes salió la resolución ministerial N° 411-2026-Midagri, en el cual aparece el listado que se indica “Han encontrado otra forma de sacar el río hacia las lagunas, que sería por Cristo Nos Valga”, dijo.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/gobierno-trabajara-en-otra-salida-del-rio-piura-tras-rechazo-de-chutuque/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>“Las fotopapeletas tienen contrato”, advierte regidora</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>La regidora y encargada del despacho de alcaldía, Lucy Chunga, se pronunció sobre el anuncio del alcalde electo Miguel Cueva, de anular las fotopapeletas y recordó que se trata de un servicio con un contrato vigente. “Ya son decisiones políticas en las que el nuevo alcalde electo tiene que ver todas las actuaciones y sobre todo decir la forma en cómo lo va a hacer considerando que dentro de la Municipalidad existe un contrato entre la entidad edil y la empresa que presta el servicio de fotopapeletas”, afirmó. Cabe indicar que el 3 de septiembre del 2025, la Municipalidad otorgó la buena pro por dos años para el servicio de instalación, operación y mantenimiento del sistema de fotopapeletas al consorcio Setrapi, conformado por las empresas SEMOECSA SAS y Prototipo del Perú SAC por S/2 millones 072 mil. En esa línea, la regidora consideró que hay un tema contractual que deben analizarse, sobre todo lo relacionado a las penalidades. “Son decisiones políticas que el nuevo alcalde tiene que analizar y ver la mejor salida”, manifestó. Recordó que se promovió el sistema para ordenar el tránsito en ciudad y proteger a la población.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/las-fotopapeletas-tienen-contrato-advierte-regidora/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>JEE declara válida la elección de Canchaque: Renovación Popular no apareció en cédula</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>El Jurado Electoral Especial de Morropón declaró válida la elección distrital en Canchaque pese a que se registró una grave irregularidad que perjudicó al partido Renovación Popular. Según el personero, el símbolo del partido no apareció en la cédula de sufragio para alcalde distrital, a pesar que el candidato estaba habilitado. El JEE consideró que era una grave irregularidad que afectó el derecho del candidato, sin embargo, consideró que no alteró resultados. “Ni la votación obtenida por “Renovación” en la elección regional utilizada como referencia, ni siquiera la consideración hipotética de la totalidad de votos blancos y nulos como potenciales votos a su favor, permiten advertir una incidencia suficiente para sostener que la omisión de incorporación de dicha organización en la cédula distrital hubiese modificado el resultado”, se lee.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/jee-declara-valida-la-eleccion-de-canchaque-renovacion-popular-no-aparecio-en-cedula/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Delincuentes desvalijan tienda de celulares en pleno centro de Catacaos</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>La delincuencia vuelve a golpear el corazón comercial de Catacaos. Esta vez, delincuentes ingresaron durante la madrugada a una tienda dedicada a la venta de celulares, ubicada en la intersección de la calle Chorrillos con la avenida José Cayetano Heredia, de donde sustrajeron mercadería y dejaron el establecimiento completamente revuelto. Según información proporcionada por efectivos de Serenazgo, alrededor de las 3:00 de la madrugada recibieron la alerta sobre un posible robo y se desplazaron hasta el establecimiento. Al llegar, encontraron la puerta enrollable parcialmente levantada, situación que despertó sus sospechas y motivó la comunicación inmediata con la Policía Nacional. Tras ser alertados, los agentes policiales acudieron al lugar para inspeccionar la escena y realizar las diligencias correspondientes. En el interior del negocio habrían encontrado un saco que presuntamente iba a ser utilizado por los delincuentes para trasladar la mercadería sustraída. De acuerdo con la información preliminar, los ladrones se habrían llevado carcasas para celulares, luego de violentar la puerta enrollable para ingresar al establecimiento. Aunque dejaron todo revuelto, no habrían conseguido llevarse los equipos celulares, considerados los productos de mayor valor del negocio. PRECUPACIÓN Sin embargo, este nuevo hecho genera preocupación entre los comerciantes, pues hace aproximadamente un mes la misma tienda habría sido víctima de otro robo, en aquella ocasión de celulares valorizados en más de 30 mil soles. Ante la reiteración de estos hechos delictivos, los comerciantes de las zonas aledañas hicieron un llamado a las autoridades policiales para que refuercen el patrullaje en el centro de Catacaos, especialmente durante la madrugada y en los sectores donde se concentra la actividad comercial. Los vecinos y empresarios expresaron su preocupación por la inseguridad que afecta al distrito y exigieron acciones concretas para prevenir nuevos asaltos y proteger sus negocios. La reiteración de robos mantiene en alerta a los comerciantes, quienes temen que sus establecimientos vuelvan a convertirse en blanco de la delincuencia.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/delincuentes-desvalijan-tienda-de-celulares-en-pleno-centro-de-catacaos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cinco días y no se conoce el rival de Hilbck para la segunda vuelta</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Hasta la fecha no se conoce quién será el candidato que se enfrentará a Reynaldo Hilbck de Alianza para el Progreso en la segunda vuelta electoral programada para el 29 de noviembre, aunque han pasado cinco días desde los comicios regionales y municipales. LOS SEPARAN 1123 VOTOS De acuerdo al conteo oficial, la diferencia entre La Torre y Paz solo es de 1123 votos, con lo cual resulta relevante conocer si la ONPE anulará o no las elecciones realizadas en el distrito de San Juan de Bigote, donde fue denunciada la destrucción de actas electorales. Para Somos Perú, es importante que se respete la voluntad popular y se proceda al reconteo de los votos que se encuentran en poder de la Fiscalía de Morropón tras el “lacrado de especies” efectuado en el lugar pasada la medianoche tras haberse llevado a cabo las elecciones. Según el personero legal titular de Somos Perú, Alex Ochoa, existe un total de 1,600 votos que favorecerían al candidato Paz. Mientras que el candidato Guillermo La Torre señaló durante la semana que dichas actas no deberían ser tomadas en cuenta. Indicó que en el peor de los casos y si se hace valer las elecciones en dicha jurisdicción mantendrían el margen electoral a su favor “y su paso a la segunda vuelta es irreversible”. “Matemáticamente es imposible que llegue el otro candidato a la segunda vuelta. Ya tenemos aquí las actas y están evaluadas, tenemos todo. Por eso digo con 100% de certeza que ya nuestro paso a la segunda vuelta es irreversible”, dijo, por ello exhortó a la ONPE celeridad en el proceso y se defina de una vez quiénes irán a segunda vuelta.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/cinco-dias-y-no-se-conoce-el-rival-de-hilbck-para-la-segunda-vuelta/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Advierten que candidatos al GORE no tienen un plan de acción frente al FEN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>El docente de la Universidad de Piura y especialista en temas electorales, Guillermo Chang Chuyes, cuestionó que los candidatos al Gobierno Regional solo hayan presentado generalidades y no un plan de acción detallado frente a la emergencia del anunciado Fenómeno el Niño (FEN). “Lo que más me llama la atención es que ninguno ha hecho un plan de acción a plazo inmediato para el tema del Fenómeno de El Niño, que ya está sobre nosotros (...). Yo me leo los planes de gobierno y, respecto del Fenómeno de El Niño, obviamente todos dicen cosas, pero son generalidades”, señaló Chang en entrevista a un medio digital local. SEGUNDA VUELTA El especialista de la UDEP también espera que los candidatos que pasen a la segunda vuelta determinen las medidas a implementar frente a la emergencia climática. “Yo creo que el debate se tiene que centrar en lo que se va a hacer inmediatamente. Sería bueno preguntarle a cada candidato: el Fenómeno de El Niño ya está encima, ¿cuál es su plan de contingencia ahora?”, manifestó. Asimismo, dejó en claro que el FEN no solo amenaza con inundaciones, ya está afectando otros sectores como la agricultura, la pesca, el abastecimiento de alimentos y la salud pública. En esa línea, cuestionó que los candidatos no detallen planes de contingencia frente al dengue, la chikungunya y otras enfermedades asociadas a las emergencias. “Lo que nos urge como ciudad y como región es sobrevivir a las lluvias”, resaltó.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/advierten-que-candidatos-al-gore-no-tienen-un-plan-de-accion-frente-al-fen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Piura: JEE anula elección en San Juan de Bigote por daños al material electoral</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>La resolución declara fundada la solicitud presentada por Julio César Seminario Espinoza, personero legal de Alianza para el Progreso, y aplica la causal prevista en el literal a) del artículo 36 de la Ley de Elecciones Municipales, referida a graves irregularidades que hayan modificado los resultados de la votación.
+Según información difundida por medios de comunicación, los actos vandálicos afectaron 20 de las 23 mesas de sufragio instaladas en el distrito.
+La afectación del material electoral impidió contar con condiciones para determinar los resultados de la elección municipal distrital.
+[Lea también: Resultados ONPE: ¿Qué departamentos ya contarían con nuevo gobernador regional? ] JEE rechaza pedido de recuento En su resolución, el JEE también desestimó la oposición presentada por Alexis Bryan Atencio Díaz, personero legal nacional del Partido Democrático Somos Perú, así como el pedido de recuento de las cédulas recuperadas.
+El JEE dispuso que el material electoral permanezca bajo custodia y preservación de las autoridades competentes.
+Asimismo, ordenó que, una vez consentida la resolución, se remita copia certificada a la Oficina Descentralizada de Procesos Electorales (ODPE) de Morropón y se ponga el caso en conocimiento del Segundo Despacho de la Segunda Fiscalía Provincial Penal Corporativa de Chulucanas.
+La resolución puede ser impugnada mediante un recurso de apelación dentro de los tres días hábiles siguientes a su publicación en el portal electrónico del Jurado Nacional de Elecciones (JNE).
+De presentarse el recurso, el expediente será elevado al pleno del máximo organismo electoral.
+[Lea también: ERM 2026: JNE registra más de 6,900 actas observadas y 66 actas siniestradas ] Más en Andina: ??La @ONPE_oficial entrega actas observadas de Lima Metropolitana a los JEE para su resolución https://t.co/61tcWJSal4 https://t.co/BMJKvfFqhY (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 10, 2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-piura-jee-anula-eleccion-san-juan-bigote-danos-al-material-electoral-1095375.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Días decisivos en la carrera por la región Piura</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>El Jurado Nacional de Elecciones (JNE) estableció nuevos plazos para las actas observadas de las Elecciones Regionales 2026. La ONPE deberá entregar la totalidad de estas actas a los Jurados Electorales Especiales (JEE) hasta el domingo 11 de octubre. Mientras tanto, el presidente del JNE, Roberto Burneo, precisó que el plazo máximo para resolver los recuentos derivados de actas observadas vence el 28 de octubre. “Máximo hasta el 28 de octubre se puede realizar recuentos y con ello estimamos que los primeros días, como máximo, de noviembre ya tendríamos resultados a nivel de gobiernos regionales y quizás de gobiernos locales”, dijo.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/dias-decisivos-en-la-carrera-por-la-region-piura/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Más de 2600 colegios de Piura en situación de vulnerabilidad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Las lluvias que se anuncian por el Fenómeno El Niño (FEN) podrían ser catastróficas para Piura: según la Red de Estudios para el Desarrollo (REDES), en la región existen más de 2600 colegios en situación de mayor vulnerabilidad; es decir, el impacto podría ser muy fuerte en la infraestructura educativa. Además, REDES advierte que con las lluvias intensas podrían resultar afectadas 396 mil viviendas y 812 establecimientos de salud. “Piura tiene una exposición histórica a las lluvias. El reto de las autoridades es actuar antes de la emergencia, proteger a la población y asegurar que los servicios y las actividades económicas puedan continuar frente a un escenario de lluvias más intensas”, indicó Germán Vega, economista de REDES. MÁS DE UN MILLÓN El Centro Nacional de Estimación, Prevención y Reducción del Riesgo de Desastres (CENEPRED) también advierte que más de 1 millón 357 mil personas en Piura se encuentran en alto riesgo ante inundaciones por lluvias intensas. Esta cifra representa alrededor del 64% de la población en la región, teniendo en cuenta el último censo, de allí la importancia de implementar planes de contingencia para mitigar el FEN. LIMITACIÓN PRESUPUESTAL La Contraloría también ha identificado este año que el Gobierno Regional de Piura no prioriza proyectos de inversión pública orientados a reducir los riesgos por inundaciones. Señalan que esa falta de planificación se refleja en las cifras de ejecución presupuestal 2026. Desde REDES, se identificó, por ejemplo, que cuatro de cinco proyectos destinados a la protección y reparación de infraestructura hídrica para evitar inundaciones empezaron el año con un presupuesto inicial de cero soles, lo que demuestra, según el informe, que no fueron priorizados desde un inicio y recibieron recursos sobre la marcha. Asimismo, detallan que aunque hoy estas intervenciones figuran con un 100% de avance, la mayoría son obras menores con presupuestos que, en algunos casos, apenas superan los 20 mil soles. Explican que un caso crítico lo representa la obra del mejoramiento del drenaje pluvial entre las avenidas Loreto, Málaga, Bolognesi y la ribera del Río Piura. Inicialmente se destinó una inversión de S/43 millones y luego el presupuesto se redujo a 14.3 millones. Pese a que se anuncian lluvias, su avance es del 68%.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/mas-de-2600-colegios-de-piura-en-situacion-de-vulnerabilidad/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Biblioteca Nacional del Perú inaugura su décima biblioteca rural</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Lee también: ["Galería de Arte de Surco abre muestra gráfica que recorre la historia del Congreso"] La nueva biblioteca cuenta con un área de 54 m², 1000 libros y tres computadoras , además de servicios de lectura en sala, préstamo a domicilio, acceso a información digital mediante internet, servicio de información, extensión bibliotecaria y estantería abierta.
 “La biblioteca pública no puede esperar a que las personas lleguen a ella; es la biblioteca la que debe llegar donde más se necesita”, ha señalado el jefe institucional de la BNP, Juan Yangali Quintanilla, al explicar la estrategia de implementación de bibliotecas rurales.
@@ -1362,110 +1761,27 @@
 https://t.co/lBVdR5EHNQ (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 9, 2026</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-biblioteca-nacional-del-peru-inaugura-su-decima-biblioteca-rural-1095271.aspx</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B43" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Piura: JEE anula elección en San Juan de Bigote por daños al material electoral</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>La resolución declara fundada la solicitud presentada por Julio César Seminario Espinoza, personero legal de Alianza para el Progreso, y aplica la causal prevista en el literal a) del artículo 36 de la Ley de Elecciones Municipales, referida a graves irregularidades que hayan modificado los resultados de la votación.
-Según información difundida por medios de comunicación, los actos vandálicos afectaron 20 de las 23 mesas de sufragio instaladas en el distrito.
-La afectación del material electoral impidió contar con condiciones para determinar los resultados de la elección municipal distrital.
-[Lea también: Resultados ONPE: ¿Qué departamentos ya contarían con nuevo gobernador regional? ] JEE rechaza pedido de recuento En su resolución, el JEE también desestimó la oposición presentada por Alexis Bryan Atencio Díaz, personero legal nacional del Partido Democrático Somos Perú, así como el pedido de recuento de las cédulas recuperadas.
-El JEE dispuso que el material electoral permanezca bajo custodia y preservación de las autoridades competentes.
-Asimismo, ordenó que, una vez consentida la resolución, se remita copia certificada a la Oficina Descentralizada de Procesos Electorales (ODPE) de Morropón y se ponga el caso en conocimiento del Segundo Despacho de la Segunda Fiscalía Provincial Penal Corporativa de Chulucanas.
-La resolución puede ser impugnada mediante un recurso de apelación dentro de los tres días hábiles siguientes a su publicación en el portal electrónico del Jurado Nacional de Elecciones (JNE).
-De presentarse el recurso, el expediente será elevado al pleno del máximo organismo electoral.
-[Lea también: ERM 2026: JNE registra más de 6,900 actas observadas y 66 actas siniestradas ] Más en Andina: ??La @ONPE_oficial entrega actas observadas de Lima Metropolitana a los JEE para su resolución https://t.co/61tcWJSal4 https://t.co/BMJKvfFqhY (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 10, 2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-piura-jee-anula-eleccion-san-juan-bigote-danos-al-material-electoral-1095375.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Advierten que candidatos al GORE no tienen un plan de acción frente al FEN</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>El docente de la Universidad de Piura y especialista en temas electorales, Guillermo Chang Chuyes, cuestionó que los candidatos al Gobierno Regional solo hayan presentado generalidades y no un plan de acción detallado frente a la emergencia del anunciado Fenómeno el Niño (FEN). “Lo que más me llama la atención es que ninguno ha hecho un plan de acción a plazo inmediato para el tema del Fenómeno de El Niño, que ya está sobre nosotros (...). Yo me leo los planes de gobierno y, respecto del Fenómeno de El Niño, obviamente todos dicen cosas, pero son generalidades”, señaló Chang en entrevista a un medio digital local. SEGUNDA VUELTA El especialista de la UDEP también espera que los candidatos que pasen a la segunda vuelta determinen las medidas a implementar frente a la emergencia climática. “Yo creo que el debate se tiene que centrar en lo que se va a hacer inmediatamente. Sería bueno preguntarle a cada candidato: el Fenómeno de El Niño ya está encima, ¿cuál es su plan de contingencia ahora?”, manifestó. Asimismo, dejó en claro que el FEN no solo amenaza con inundaciones, ya está afectando otros sectores como la agricultura, la pesca, el abastecimiento de alimentos y la salud pública. En esa línea, cuestionó que los candidatos no detallen planes de contingencia frente al dengue, la chikungunya y otras enfermedades asociadas a las emergencias. “Lo que nos urge como ciudad y como región es sobrevivir a las lluvias”, resaltó.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/advierten-que-candidatos-al-gore-no-tienen-un-plan-de-accion-frente-al-fen/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Cinco días y no se conoce el rival de Hilbck para la segunda vuelta</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Hasta la fecha no se conoce quién será el candidato que se enfrentará a Reynaldo Hilbck de Alianza para el Progreso en la segunda vuelta electoral programada para el 29 de noviembre, aunque han pasado cinco días desde los comicios regionales y municipales. LOS SEPARAN 1123 VOTOS De acuerdo al conteo oficial, la diferencia entre La Torre y Paz solo es de 1123 votos, con lo cual resulta relevante conocer si la ONPE anulará o no las elecciones realizadas en el distrito de San Juan de Bigote, donde fue denunciada la destrucción de actas electorales. Para Somos Perú, es importante que se respete la voluntad popular y se proceda al reconteo de los votos que se encuentran en poder de la Fiscalía de Morropón tras el “lacrado de especies” efectuado en el lugar pasada la medianoche tras haberse llevado a cabo las elecciones. Según el personero legal titular de Somos Perú, Alex Ochoa, existe un total de 1,600 votos que favorecerían al candidato Paz. Mientras que el candidato Guillermo La Torre señaló durante la semana que dichas actas no deberían ser tomadas en cuenta. Indicó que en el peor de los casos y si se hace valer las elecciones en dicha jurisdicción mantendrían el margen electoral a su favor “y su paso a la segunda vuelta es irreversible”. “Matemáticamente es imposible que llegue el otro candidato a la segunda vuelta. Ya tenemos aquí las actas y están evaluadas, tenemos todo. Por eso digo con 100% de certeza que ya nuestro paso a la segunda vuelta es irreversible”, dijo, por ello exhortó a la ONPE celeridad en el proceso y se defina de una vez quiénes irán a segunda vuelta.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/cinco-dias-y-no-se-conoce-el-rival-de-hilbck-para-la-segunda-vuelta/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>El Niño: Contraloría advierte demora para ejecutar plan de S/205 millones en red vial</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Esta situación podría afectar la transitabilidad y continuidad operativa de la red vial nacional no concesionada y, con ello, el acceso de la población a servicios esenciales, detalló la entidad de control.
 El Informe de Orientación de Oficio N° 018-2026-OCI/0661-SOO , correspondiente a la evaluación realizada del 14 al 21 de setiembre, examinó el estado de la gestión e implementación del referido plan e identificó situaciones adversas que requieren acciones por parte de Provías Nacional.
@@ -1486,306 +1802,77 @@
 Más información ?? https://t.co/zSIv3qczUr (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 9, 2026</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-el-nino-contraloria-advierte-demora-para-ejecutar-plan-s205-millones-red-vial-1095352.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Días decisivos en la carrera por la región Piura</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>El Jurado Nacional de Elecciones (JNE) estableció nuevos plazos para las actas observadas de las Elecciones Regionales 2026. La ONPE deberá entregar la totalidad de estas actas a los Jurados Electorales Especiales (JEE) hasta el domingo 11 de octubre. Mientras tanto, el presidente del JNE, Roberto Burneo, precisó que el plazo máximo para resolver los recuentos derivados de actas observadas vence el 28 de octubre. “Máximo hasta el 28 de octubre se puede realizar recuentos y con ello estimamos que los primeros días, como máximo, de noviembre ya tendríamos resultados a nivel de gobiernos regionales y quizás de gobiernos locales”, dijo.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/dias-decisivos-en-la-carrera-por-la-region-piura/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Más de 2600 colegios de Piura en situación de vulnerabilidad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Las lluvias que se anuncian por el Fenómeno El Niño (FEN) podrían ser catastróficas para Piura: según la Red de Estudios para el Desarrollo (REDES), en la región existen más de 2600 colegios en situación de mayor vulnerabilidad; es decir, el impacto podría ser muy fuerte en la infraestructura educativa. Además, REDES advierte que con las lluvias intensas podrían resultar afectadas 396 mil viviendas y 812 establecimientos de salud. “Piura tiene una exposición histórica a las lluvias. El reto de las autoridades es actuar antes de la emergencia, proteger a la población y asegurar que los servicios y las actividades económicas puedan continuar frente a un escenario de lluvias más intensas”, indicó Germán Vega, economista de REDES. MÁS DE UN MILLÓN El Centro Nacional de Estimación, Prevención y Reducción del Riesgo de Desastres (CENEPRED) también advierte que más de 1 millón 357 mil personas en Piura se encuentran en alto riesgo ante inundaciones por lluvias intensas. Esta cifra representa alrededor del 64% de la población en la región, teniendo en cuenta el último censo, de allí la importancia de implementar planes de contingencia para mitigar el FEN. LIMITACIÓN PRESUPUESTAL La Contraloría también ha identificado este año que el Gobierno Regional de Piura no prioriza proyectos de inversión pública orientados a reducir los riesgos por inundaciones. Señalan que esa falta de planificación se refleja en las cifras de ejecución presupuestal 2026. Desde REDES, se identificó, por ejemplo, que cuatro de cinco proyectos destinados a la protección y reparación de infraestructura hídrica para evitar inundaciones empezaron el año con un presupuesto inicial de cero soles, lo que demuestra, según el informe, que no fueron priorizados desde un inicio y recibieron recursos sobre la marcha. Asimismo, detallan que aunque hoy estas intervenciones figuran con un 100% de avance, la mayoría son obras menores con presupuestos que, en algunos casos, apenas superan los 20 mil soles. Explican que un caso crítico lo representa la obra del mejoramiento del drenaje pluvial entre las avenidas Loreto, Málaga, Bolognesi y la ribera del Río Piura. Inicialmente se destinó una inversión de S/43 millones y luego el presupuesto se redujo a 14.3 millones. Pese a que se anuncian lluvias, su avance es del 68%.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/mas-de-2600-colegios-de-piura-en-situacion-de-vulnerabilidad/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Piura: BNP inaugura biblioteca rural en Paita</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>La Biblioteca Nacional del Perú (BNP), entidad adscrita al Ministerio de Cultura, cumplió la meta anunciada por la actual gestión y llegó a su décima biblioteca rural y nativa implementada en menos de un año. Lo hizo en el Centro Poblado La Islilla, en Paita, Piura, donde inauguró la Biblioteca Pública “Pescando conocimiento”, un nuevo espacio de lectura, información y acceso al conocimiento para más de 2000 habitantes. La nueva biblioteca cuenta con un área de 54 m², 1000 libros y tres computadoras, además de servicios de lectura en sala, préstamo a domicilio, acceso a información digital mediante internet, servicio de información, extensión bibliotecaria y estantería abierta. “La biblioteca pública no puede esperar a que las personas lleguen a ella; es la biblioteca la que debe llegar donde más se necesita”, señaló el jefe institucional de la BNP, Juan Yangali Quintanilla, al explicar la estrategia de implementación de bibliotecas rurales. Durante la inauguración de “Pescando conocimiento”, el funcionario destacó que la esta nueva biblioteca en La Islilla representa mucho más que la apertura de un nuevo local. “Hoy no estamos poniendo punto final a un proyecto. Estamos escribiendo la primera página. Queremos que aquí muchos niños descubran su primer libro, que muchos jóvenes encuentren información para sus estudios y que muchas familias hagan de esta biblioteca un lugar propio”, agregó. La ceremonia de apertura reunió a autoridades locales como el alcalde de La Isilla, Roberto Rumiche, representantes de la comunidad educativa, familias y estudiantes, en torno a una jornada donde se realizaron actividades artísticas y culturales, como parte de los actos conmemorativos por el Combate de Angamos en Paita, tierra natal de nuestro héroe nacional Miguel Grau. Su implementación fue acompañada por la Municipalidad del Centro Poblado La Islilla y contó con el trabajo articulado de autoridades educativas y representantes de la comunidad. Una biblioteca que nace mirando al mar “Pescando conocimiento” no es un nombre elegido al azar. La Islilla es una comunidad con una profunda identidad marítima, donde la pesca artesanal constituye la principal actividad económica y ocupa a más del 60 % de su Población Económicamente Activa. Además, en los últimos años, el ecoturismo ha comenzado a ganar espacio gracias a la cercanía de la Isla Foca y a actividades como el avistamiento de lobos marinos, pingüinos de Humboldt y aves guaneras. En este contexto, la biblioteca busca convertirse en un espacio de encuentro para niños, jóvenes y familias; un lugar para estudiar, leer, acceder a información, utilizar herramientas digitales y descubrir nuevas oportunidades de aprendizaje. Diez bibliotecas, una misma apuesta Con la biblioteca de La Islilla, la BNP alcanza diez bibliotecas rurales y nativas implementadas en menos de un año en ocho regiones del país, consolidando una estrategia que busca llevar los servicios bibliotecarios a comunidades históricamente excluidas de estos espacios. Estos espacios se ubican en Huancavelica, Loreto, Junín, Amazonas, Lima, Ica (dos bibliotecas), Cusco (dos bibliotecas) y Piura. El modelo contempla no solo la entrega de libros, sino también la creación de espacios adecuados, mobiliario, tecnología, acceso a la Biblioteca Digital de la BNP, colecciones pertinentes y acompañamiento técnico para garantizar la sostenibilidad de los servicios. Datos: - El jefe institucional también participó en la inauguración de la Biblioteca Pública “Mario Vargas Llosa”, ubicada en el distrito de Salitral, provincia de Morropón, región Piura. - La BNP prestó asistencia técnica para su implementación, como parte de su estrategia para promover el cierre de brechas de acceso a la lectura en las regiones y el fortalecimiento del Sistema Nacional de Bibliotecas (SNB).</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/lima/sucesos/piura-bnp-inaugura-biblioteca-rural-en-paita-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Piura: Produce y FAP promueven consumo seguro de productos hidrobiológicos en Parachique</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>El equipo técnico de Sanipes compartió recomendaciones prácticas orientadas a mitigar riesgos sanitarios vinculados a variaciones climáticas y al fenómeno El Niño (FEN).
-En ese contexto, los especialistas enseñaron a los participantes a evaluar de manera rigurosa la calidad del pescado fresco a través de características clave como apariencia, olor, textura y estado general del recurso.
-Asimismo, brindaron pautas para la adquisición responsable de conservas de pescado , concientizando sobre la importancia de verificar que los envases se encuentren libres de hinchazones, abolladuras, filtraciones, óxido o perforaciones.
-De igual forma, se recalcó la necesidad de revisar la vigencia de la fecha de vencimiento, la legibilidad del etiquetado y la presencia del registro sanitario correspondiente.
-"Asumimos el compromiso firme de descentralizar la prevención e inocuidad alimentaria.
-Gracias a esta alianza estratégica con la FAP, llegamos directamente a la comunidad de Parachique para transferir conocimientos prácticos que garanticen que cada producto hidrobiológico que llega a las mesas piuranas sea seguro, fresco y altamente nutritivo", destacó la presidenta ejecutiva de Sanipes, Mónica Saavedra Chumbe .
-La titular de Sanipes enfatizó la relevancia de estas acciones en la actualidad: " Frente a las variaciones climáticas y el impacto del FEN, la capacitación oportuna es nuestra principal herramienta de protección.
-Enseñar a identificar la calidad del pescado fresco y verificar el estado de las conservas no solo salva vidas y previene enfermedades, sino que empodera a nuestras familias acuícolas y pesqueras en el cuidado de su salud".
-La actividad formativa se llevó a cabo en el marco de la octava edición del programa de ayuda humanitaria “Alas de Esperanza” de la FAP, iniciativa que brinda asistencia social y apoyo solidario a poblaciones en situación de vulnerabilidad y zonas de difícil acceso.
-Este despliegue conjunto se ejecutó bajo las directrices del convenio de colaboración interinstitucional suscrito entre Sanipes y la FAP el 3 de octubre de 2025.
-Más en Andina: Fenómeno El Niño: Ejército del Perú ejecuta descolmatación de 1.6 km en cauce del río Ica https://t.co/00113GgIQu a través de @Agencia_Andina https://t.co/Ln5wRvqioU (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Moisés Aylas Ortiz (@regionalesand) October 8, 2026</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-piura-produce-y-fap-promueven-consumo-seguro-productos-hidrobiologicos-parachique-1095159.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Con tradicionales novenas Ica inicia actividades en honor a su patrono el Señor de Luren</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Así lo anunció José Luis Santa Cruz Pereyra, párroco y superior del santuario del Señor de Luren, quien además informó que el 27 de noviembre la venerada imagen saldrá en procesión extraordinaria por los 80 años de creación de la Diócesis de Ica y los 75 años de presencia de los Padres Carmelitas Descalzos en la región.
-Sobre el primer recorrido procesional, indicó que se iniciará a las 17:00 horas del lunes 19.
-Previamente, a las 07:00 horas, se cumplirá con la tradicional bajada, y la efigie retornará a su santuario el martes 20 al mediodía.
-Lea también: Señor de Luren: ¿Qué representa esta devoción religiosa para la identidad de los iqueños? En cuanto al itinerario, el padre Santa Cruz detalló que la procesión avanzará por la calle Nasca y continuará por Piura, la avenida Cutervo, Lima, Andahuaylas, la avenida San Martín, Chiclayo y J.
-J.
-Elías.
-Posteriormente, la imagen ingresará a la I.
-E.
-San Luis Gonzaga y seguirá por Matías Manzanilla, la avenida Municipalidad, la calle Bolívar y la avenida Grau, para luego cruzar el puente Grau y avanzar hasta la avenida Siete, en el distrito de Parcona.
-Finalmente, el la pesada anda cruzará el puente Cutervo, avanzará por la avenida del mismo nombre, subirá por la calle Ayacucho y retornará al santuario.
-El segundo recorrido procesional está programado para el domingo 25 de octubre y comenzará a las 9:00 horas, según el programa oficial.
-La sagrada imagen recorrerá diversas calles y avenidas de la ciudad, entre las que figuran Ayacucho, Conde de Nieva, Francisco Flores, Nicolás de Rivera el Viejo, Juan Pablo Fernandini, Las Orquídeas, Los Tacones, Los Azahares y Los Nardos.
-La imagen ingresará a su santuario a las 17:00 horas, luego de derramar sus bendiciones sobre los feligreses, quienes le rendirán homenaje con cánticos, oraciones y la elaboración de alfombras de flores en agradecimiento por los favores concedidos.
-Más en Andina: ???? En Chimbote, rinden homenaje a Miguel Grau por el 147.° aniversario del Combate de Angamos https://t.co/TdcKBvAOGZ https://t.co/Iz3oqGcGw1 (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 8, 2026</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-con-tradicionales-novenas-ica-inicia-actividades-honor-a-su-patrono-senor-luren-1095195.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Fenómeno El Niño: Ejército del Perú ejecuta descolmatación de 1.6 km en cauce del río Ica</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Al respecto, el teniente coronel del Ejército del Perú (EP) Roberto Luis Miranda Arenas , comandante de esta unidad, declaró a la Agencia Andina que e stos trabajos se concretan mediante una acción estratégica articulada entre el Ministerio de Defensa (Mindef) y el Ministerio de Desarrollo Agrario y Riego (Midagri), fortaleciendo la coordinación interinstitucional para mitigar los riesgos en zonas vulnerables.
-Lea también: El Niño: Ejército del Perú acelera trabajos de descolmatación en río Piura “ Estamos realizando la descolmatación del río Ica en un tramo de aproximadamente 1,650 metros, la conformación de bordos con material propio y la eliminación de material excedente, con el objetivo de mejorar las condiciones del cauce y contribuir a la protección de las áreas agrícolas ante posibles desbordes”, aseveró.
-Lea también: Ministerio de Defensa desplazará batallones de ingeniería del Ejército frente a El Niño El oficial del Ejército agregó que los trabajos de prevención tendrán una duración de 30 días , para lo cual se han desplegado una excavadora, un cargador frontal, un tractor de oruga y volquetes que permitirán ejecutar las labores programadas.
-Por su parte, la alcaldesa distrital de Ocucaje, Laura Peña Valencia, pidió al ministro de Defensa, Rafael Belaúnde Llosa, que los trabajos se prolonguen 500 metros más para proteger con enrocado y enmallado la captación de agua potable que abastece a todo este distrito.
-El agricultor y poblador de Paraya Nieri Villagaray Gómez sostuvo que en 2026 los campos de cultivo de este sector fueron devastados por el desborde del río Ica, y destacó que estos trabajos amortiguarán los posibles efectos del fenómeno El Niño.
-El dato El Batallón de Asuntos Civiles N.° 4 del Comando de Apoyo al Desarrollo Nacional del Ejército del Perú (COADNE), realiza trabajos de defensa ribereña mediante la construcción de diques con enrocado en el sector de Santiaguillo en el distrito de Santiago (Ica).
-Más en Andina: ???? Papa León XIV obsequiará sudario confeccionado en el Vaticano al Señor de Los Temblores https://t.co/fpUAWh3UHa https://t.co/DuGgG6qQxt (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 8, 2026</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-fenomeno-nino-ejercito-del-peru-ejecuta-descolmatacion-16-km-cauce-del-rio-ica-1095144.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Presidenta de la junta de fiscales se pronuncia sobre elecciones en San Juan de Bigote: “La pérdida es del 90% del material y sobre esto no puede haber un resultado”</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>El candidato de Somos Perú, Santiago Paz , señala que la elección a segunda vuelta la tendrían asegurada con la información que salvaguardó la Fiscalía de Morropón durante los incidentes registrados el domingo último cuando un grupo de personas ingresó a las aulas y destruyó parte del material electoral. LEE MÁS ► Elecciones 2026 en Piura: Simpatizantes de Somos Perú protestan ante el JEE y exigen conteo de actas de San Juan de Bigote De acuerdo al “Acta de verificación fiscal y lacrado de especies” , el fiscal Luis Enrique Venegas Morales deja constancia de lo hallado en las 23 mesas de sufragio , básicamente cédulas de votación, cabinas, ánforas, así como el hallazgo de material electoral roto (cédulas y actas de sufragio). El documento también lleva las firmas de un representante del Ejército, coordinador del local, entre otros. ¿NULIDAD DE ELECCIÓN? Sobre el tema, La Hora entrevistó a la presidenta de la Junta de Fiscales Superiores del Distrito Fiscal de Piura , Faviola Susana Campos Hidalgo, quien dejó en claro que la pérdida del material electoral no fue mínima. “Aproximadamente la pérdida es del 90% del material electoral, lo que ha generado que la Fiscalía se constituya” , informó la representante del Ministerio Público quien agregó que está en manos del JNE tomar una decisión sobre la votación popilar. No obstante, agregó: “Lo oficial es del 90% [del material electoral perdido] y sobre esto no puede haber un resultado en ese local de 23 mesas” , señaló. Asimismo dijo que el JNE y otras entidades del sistema electoral ya han pedido información sobre lo acontecido en San Juan de Bigote. 2 A 8 AÑOS DE CÁRCEL Campos Hidalgo indicó que lo registrado en Morropón se enmarca en delitos contra la voluntad popular por la destrucción del material electoral. Informó que la ley sanciona estos casos con penas punitivas entre 2 a 8 años. Indicó que los videos, testimonios de los miembros de mesa entre otras pruebas serán evidencias para identificar a los responsables.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/presidenta-de-la-junta-de-fiscales-se-pronuncia-sobre-elecciones-en-san-juan-de-bigote-la-perdida-es-del-90-del-material-y-sobre-esto-no-puede-haber-un-resultado/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Piura: Amplian detención a investigado por feminicidio de madre de familia en Chulucanas</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Poder Judicial dispuso el plazo de siete días para que se realicen todas las diligencias con relación a crimen de la madre de sus 2 hijos. Por un plazo de siete días será investigado G. B. A. C., de 32 años , luego que el Poder Judicial ordenara dicha medida solicitado por la Fiscalía Especializada en Delitos de Violencia Contra la Mujer de Morropón. El detenido es sindicado del presunto delito de feminicidio. LEE MÁS ► Elecciones 2026 en la región Piura: así quedó el panorama político de los próximos cuatro años Durante la audiencia correspondiente, el fiscal provincial Eriksson Daniel Burga Villa presentó elementos razonables para considerar que el denunciado estaría involucrado en la muerte de su conviviente y madre de sus dos hijos, Leydi Maribel Gonza Chuica, en la vivienda conyugal ubicada en el caserío Platanal Bajo, distrito de Chulucanas . Violento episodio De acuerdo con las diligencias preliminares, el investigado habría sujetado del cuello a su pareja hasta provocarle la muerte, motivado presuntamente por celos, posteriormente, se habría comunicado con la madre de la víctima mortal, así como con los efectivos de la Comisaria de Chulucanas , dando cuenta a la Comisaría de Yapatera, quienes llegan al lugar y lo detienen. Con esta decisión judicial, la fiscalía continuará desarrollando los actos de investigación necesarios para esclarecer los hechos, determinar la participación del involucrado y sustentar las acciones penales que correspondan conforme a ley. Madre trabajadora Como se conoce, Leydi Gonza trabajaba en una planta agroindustrial dedicada a la producción de uva. Se sabe que el detenido constantemente la celaba por lo que siempre tenían problemas en casa. Las discusiones los llevaron a una separación temporal. Allegados a la víctima mortal indican que siempre discutía con el padre de sus dos hijos, pero luego se amistaban y continuaba la relación tormentosa que tuvo un trágico final en la vivienda familiar. Piden justicia Los padres de Leydi Gonza exigen a las autoridades una exhaustiva investigación a fin de conocer la verdad y reciba una drástica condena por la muerte de la madre de sus hijos menores. Debes Saber ■ De acuerdo a las investigaciones, el detenido cerca de la 1:35 de la madrugada llamó al padre de Leydi Gonza para indicarle que cuidara a sus dos hijos. ■ Agentes de la Comisaría de Chulucanas alertados del trágico suceso se desplazaron hasta el caserío Platanal Bajo para detener al principal sospechoso.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/piura-amplian-detencion-a-investigado-por-feminicidio-de-madre-de-familia-en-chulucanas/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>8 de octubre: Combate de Angamos y homenaje a Miguel Grau, el Caballero de los Mares</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Cada 8 de octubre , el Perú conmemora una de las fechas más representativas de su historia republicana. La jornada recuerda el Combate Naval de Angamos , ocurrido en 1879 durante la Guerra del Pacífico, y rinde homenaje al almirante Miguel Grau Seminario , quien murió durante aquel enfrentamiento mientras comandaba el monitor Huáscar. La fecha también está vinculada con la creación de la Marina de Guerra del Perú , institución que nació en los primeros años de la República y que, desde entonces, cumple funciones relacionadas con la defensa y protección de los espacios marítimos, fluviales y lacustres del país. A 147 años del Combate de Angamos, la figura de Grau continúa ocupando un lugar central en la memoria nacional. Su actuación durante la Guerra del Pacífico, caracterizada por el valor demostrado en combate y el respeto hacia sus adversarios, contribuyó a consolidar su imagen como uno de los principales héroes de la historia peruana. La creación de la Marina de Guerra del Perú La Marina de Guerra del Perú fue creada el 8 de octubre de 1821, durante el proceso de consolidación de la independencia nacional. El general José de San Martín impulsó la organización de una fuerza naval que permitiera proteger las costas y contribuir al control de las rutas marítimas. El primer comandante de la institución fue el marino británico Martín Jorge Guise , quien tuvo la responsabilidad de organizar las primeras fuerzas navales de la naciente República. Con el transcurso de los años, la Marina amplió sus responsabilidades. Actualmente, además de participar en tareas relacionadas con la defensa nacional, desarrolla labores de búsqueda y rescate , vigilancia de los espacios acuáticos, protección ambiental y apoyo a poblaciones ubicadas en zonas alejadas del territorio peruano. El Combate de Angamos y la muerte de Miguel Grau El 8 de octubre de 1879 , el monitor Huáscar, bajo el mando de Miguel Grau Seminario , enfrentó a una escuadra de la Armada de Chile en aguas cercanas a Punta Angamos. El enfrentamiento fue determinante para el desarrollo de la Guerra del Pacífico. Durante el combate, un proyectil impactó en la torre de mando del Huáscar y provocó la muerte de Grau. Tras varias horas de enfrentamiento, el monitor peruano fue capturado por las fuerzas chilenas. La pérdida del Huáscar significó un duro golpe para la capacidad naval peruana. La posterior supremacía marítima de Chile permitió facilitar el desplazamiento de tropas y recursos durante las siguientes etapas del conflicto. Sin embargo, la importancia histórica de Grau trascendió el resultado militar. Su conducta durante la guerra y el trato que brindó a sus adversarios contribuyeron a que fuera reconocido como el Caballero de los Mares , una denominación que permanece asociada a su figura hasta la actualidad. El legado de Grau permanece en la memoria nacional El homenaje que cada año se realiza el 8 de octubre no se limita a recordar un enfrentamiento militar. También representa una oportunidad para reflexionar sobre valores como el honor, la disciplina, el valor, la responsabilidad y el servicio al país . La figura de Miguel Grau se mantiene como un referente de entrega y compromiso con el deber. Su legado ha trascendido generaciones y continúa formando parte de la identidad histórica de la Marina y de la nación peruana. En esta fecha también se recuerda a los hombres y mujeres que, desde diferentes ámbitos, dedican sus capacidades al servicio de la población y a la protección de la vida. El Huáscar, un patrimonio histórico de la Guerra del Pacífico Después del Combate de Angamos, el monitor Huáscar pasó a formar parte de la Armada de Chile. Décadas después, la embarcación fue restaurada con el objetivo de recuperar características similares a las que tenía antes de la Guerra del Pacífico. El 8 de octubre de 1952 fue inaugurado como Museo Histórico Naval Huáscar , en Talcahuano, Chile. El buque conserva espacios, objetos y elementos vinculados con la historia naval del conflicto y con personajes como Miguel Grau, Arturo Prat y Manuel Thomson. Actualmente, el Huáscar es considerado una pieza de gran valor histórico y patrimonial. Su permanencia como museo permite conocer parte de la historia marítima de Chile y Perú y mantiene vigente el recuerdo de uno de los episodios más importantes de la Guerra del Pacífico. A 147 años del Combate de Angamos , el Perú recuerda a Miguel Grau y a los héroes del mar, destacando una enseñanza que permanece vigente: servir a la patria implica compromiso, responsabilidad y disposición para defender y proteger a los demás .</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/tendencias/8-de-octubre-combate-de-angamos-y-homenaje-a-miguel-grau-el-caballero-de-los-mares/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>¡Golpe a la delincuencia! Piura: Caen presuntos integrantes de banda criminal «La Gran Sangre»</t>
+          <t>Piura: BNP inaugura biblioteca rural en Paita</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>En una conferencia de prensa brindada en la DIVINCRI Piura, el comando de la Región Policial de Piura ofreció un balance detallado de los operativos desplegados contra la criminalidad organizada y el tráfico ilícito. LEE MÁS ► Piura: Amplian detención a investigado por feminicidio de madre de familia en Chulucanas Desarticulación de ‘La Gran Sangre’: Ataque a sangre fría y captura tras Plan Cerco Uno de los golpes más contundentes fue la captura en flagrancia de cuatro integrantes de la presunta banda criminal «La Gran Sangre», capturados tras asaltar a mano armada a dos ciudadanos (uno colombiano y otro venezolano) dedicados presuntamente al préstamo bajo la modalidad de «gota a gota» en la jurisdicción del distrito Veintiséis de Octubre. Durante el atraco, uno de los maleantes le disparó a quemarropa al ciudadano colombiano. Sobre el ataque, la autoridad policial señaló que «uno de estos sujetos sin piedad le dispara al ciudadano colombiano a sangre fría, al parecer con la finalidad de acabar con su vida. Sin embargo, la bala le cayó en el brazo y se encuentra con lesiones leves». Efectivos de la Comisaría de Veintiséis de Octubre ejecutaron de inmediato el Plan Cerco, logrando la detención de los cuatro delincuentes peruanos y la incautación de una motocicleta blanco con rojo requisitada por robo. El jefe policial detalló que el tirador registra un amplio prontuario. «Uno de ellos presenta gran cantidad de antecedentes policiales. Tiene denuncias y acusaciones fiscales por robo agravado a mano armada, por delito contra el patrimonio de receptación, tráfico de drogas, conducción en estado de ebriedad, entre otros hechos criminales» , señaló. Lucha contra el contrabando, microcomercialización y bandas locales Durante la presentación, la Policía Nacional del Perú dio a conocer otros importantes logros operativos. Resalta la captura de presuntos integrantes de «Los Verduleros del Norte» , en la cual,  Personal de la Depincri Piura, en coordinación con la SUNAT, intervino a la altura del peaje Piura-Sullana un camión con dos sujetos que transportaban 120 mallas plásticas con arveja fresca colombiana de contrabando, incautándose la mercadería y el vehículo valorizados en aproximadamente 120,000 soles. Asimismo, el mando polciial resalto la captura de presuntos integrantes de «Los Pollos de Castilla» , banda desarticulada el 5 de octubre en la zona de Tacalá (Castilla) , decomisándoseles más de 3,300 envoltorios de PBC, tres celulares y una motocicleta. Cifras de producción anual y reducción de la criminalidad En cuanto al balance del presente año, el comando policial, Daniel Jares destacó la realización d e 73,672 operativos policiales , que permitieron la captura en flagrancia de 9,162 personas, la detención de 3,403 requisitoriados, la retención de 517 menores de edad y la desarticulación de 481 bandas criminales. Asimismo, se han decomisado más de 200 armas de fuego, más de 96,000 «ketes» de PBC, 35 kg de PBC a granel y 122 kg de marihuana. Respecto al impacto en la seguridad ciudadana, la autoridad enfatizó la tendencia a la baja en delitos de alto impacto. «Podemos decir que el presente año hemos reducido lo que es robo y hurtos en un 15%, los homicidios en un 1% y en lo que es delito de extorsión un 58%» , concluyó Jares.</t>
+          <t>La Biblioteca Nacional del Perú (BNP), entidad adscrita al Ministerio de Cultura, cumplió la meta anunciada por la actual gestión y llegó a su décima biblioteca rural y nativa implementada en menos de un año. Lo hizo en el Centro Poblado La Islilla, en Paita, Piura, donde inauguró la Biblioteca Pública “Pescando conocimiento”, un nuevo espacio de lectura, información y acceso al conocimiento para más de 2000 habitantes. La nueva biblioteca cuenta con un área de 54 m², 1000 libros y tres computadoras, además de servicios de lectura en sala, préstamo a domicilio, acceso a información digital mediante internet, servicio de información, extensión bibliotecaria y estantería abierta. “La biblioteca pública no puede esperar a que las personas lleguen a ella; es la biblioteca la que debe llegar donde más se necesita”, señaló el jefe institucional de la BNP, Juan Yangali Quintanilla, al explicar la estrategia de implementación de bibliotecas rurales. Durante la inauguración de “Pescando conocimiento”, el funcionario destacó que la esta nueva biblioteca en La Islilla representa mucho más que la apertura de un nuevo local. “Hoy no estamos poniendo punto final a un proyecto. Estamos escribiendo la primera página. Queremos que aquí muchos niños descubran su primer libro, que muchos jóvenes encuentren información para sus estudios y que muchas familias hagan de esta biblioteca un lugar propio”, agregó. La ceremonia de apertura reunió a autoridades locales como el alcalde de La Isilla, Roberto Rumiche, representantes de la comunidad educativa, familias y estudiantes, en torno a una jornada donde se realizaron actividades artísticas y culturales, como parte de los actos conmemorativos por el Combate de Angamos en Paita, tierra natal de nuestro héroe nacional Miguel Grau. Su implementación fue acompañada por la Municipalidad del Centro Poblado La Islilla y contó con el trabajo articulado de autoridades educativas y representantes de la comunidad. Una biblioteca que nace mirando al mar “Pescando conocimiento” no es un nombre elegido al azar. La Islilla es una comunidad con una profunda identidad marítima, donde la pesca artesanal constituye la principal actividad económica y ocupa a más del 60 % de su Población Económicamente Activa. Además, en los últimos años, el ecoturismo ha comenzado a ganar espacio gracias a la cercanía de la Isla Foca y a actividades como el avistamiento de lobos marinos, pingüinos de Humboldt y aves guaneras. En este contexto, la biblioteca busca convertirse en un espacio de encuentro para niños, jóvenes y familias; un lugar para estudiar, leer, acceder a información, utilizar herramientas digitales y descubrir nuevas oportunidades de aprendizaje. Diez bibliotecas, una misma apuesta Con la biblioteca de La Islilla, la BNP alcanza diez bibliotecas rurales y nativas implementadas en menos de un año en ocho regiones del país, consolidando una estrategia que busca llevar los servicios bibliotecarios a comunidades históricamente excluidas de estos espacios. Estos espacios se ubican en Huancavelica, Loreto, Junín, Amazonas, Lima, Ica (dos bibliotecas), Cusco (dos bibliotecas) y Piura. El modelo contempla no solo la entrega de libros, sino también la creación de espacios adecuados, mobiliario, tecnología, acceso a la Biblioteca Digital de la BNP, colecciones pertinentes y acompañamiento técnico para garantizar la sostenibilidad de los servicios. Datos: - El jefe institucional también participó en la inauguración de la Biblioteca Pública “Mario Vargas Llosa”, ubicada en el distrito de Salitral, provincia de Morropón, región Piura. - La BNP prestó asistencia técnica para su implementación, como parte de su estrategia para promover el cierre de brechas de acceso a la lectura en las regiones y el fortalecimiento del Sistema Nacional de Bibliotecas (SNB).</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/golpe-a-la-delincuencia-piura-caen-presuntos-integrantes-de-banda-criminal-la-gran-sangre/</t>
+          <t>https://elcomercio.pe/lima/sucesos/piura-bnp-inaugura-biblioteca-rural-en-paita-noticia/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sucamec incauta 29 armas y cerca de 200 kilos de explosivos en Piura y Ayacucho</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>La Superintendencia Nacional de Control de Servicios de Seguridad, Armas, Municiones y Explosivos de Uso Civil (Sucamec) incautó en Ayacucho y Piura 29 armas de fuego y alrededor de 198 kilos de material explosivo que se encontraban fuera de las condiciones de autorización y seguridad. En San Juan Bautista, Ayacucho, la Sucamec retiró 23 armas de fuego de un establecimiento cuya autorización se encontraba vencida y que incumplía las condiciones exigidas para la custodia de armamento. En el marco de la estrategia del Ministerio del Interior (Mininter) para anticiparse al crimen y recuperar el control territorial, el material incautado en Ayacucho comprende 17 pistolas, cuatro revólveres y dos carabinas, informó la institución en una nota de prensa. Mientras tanto, en Paita (Piura) fueron retiradas otras seis armas de una empresa de vigilancia privada que no cumplía los requisitos para prestar servicios de seguridad con armamento: cuatro escopetas y dos carabinas. El superintendente nacional de la Sucamec, Eswin Manay Guerrero, destacó que estas acciones responden al compromiso de la gestión del ministro del Interior, César Astudillo, de reforzar la fiscalización a nivel nacional y cerrar espacios al accionar criminal. “Nuestra prioridad es fortalecer el control para contribuir a la lucha frontal contra la inseguridad y proteger a la ciudadanía –comentó Manay–. Cada arma que retiramos de una situación irregular reduce el riesgo de que pueda ser desviada o utilizada para fines ilícitos”. Explosivos sin autorización En Talara Alta, Piura, la Sucamec –junto con el Ministerio Público y unidades especializadas de la Policía Nacional del Perú– intervino un inmueble donde se almacenaban alrededor de 198 kilos de material explosivo “trasladado desde Loreto sin contar con la autorización correspondiente”. El material, utilizado para la perforación de pozos petroleros, fue retirado de inmediato debido al riesgo que representaba su almacenamiento en un lugar no autorizado, precisó la entidad. “Estas acciones forman parte del fortalecimiento de los controles impulsados por el Ministerio del Interior, a través de la Sucamec, para prevenir el desvío y uso ilícito de armas, municiones y explosivos, y contribuir a la seguridad de la ciudadanía”, finalizó el Mininter.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/sucamec-incauta-29-armas-y-cerca-de-200-kilos-de-explosivos-en-piura-y-ayacucho/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B46" s="2" t="n">
         <v>46303</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Sucamec incauta 29 armas y cerca de 200 kilos de explosivos en Ayacucho y Piura</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>En San Juan Bautista, Ayacucho, la Sucamec retiró 23 armas de fuego de un establecimiento cuya autorización se encontraba vencida y que incumplía las condiciones exigidas para la custodia de armamento.
 En el marco de la estrategia del Ministerio del Interior (Mininter) para anticiparse al crimen y recuperar el control territorial, el material incautado en Ayacucho comprende 17 pistolas, cuatro revólveres y dos carabinas, informó la institución en una nota de prensa.
@@ -1801,34 +1888,9 @@
 destaca avances en la lucha conjunta contra el crimen organizado en Perú ] Más en Andina: El excomandante General del Ejército Otto Guibovich consideró que el anuncio del Comando Unificado es un paso importante para dar una lucha frontal a la criminalidad.??https://t.co/G7hjfTTXtH https://t.co/zLozP9u2BT (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 8, 2026</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-sucamec-incauta-29-armas-y-cerca-200-kilos-explosivos-ayacucho-y-piura-1095225.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>46302</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Virtual alcalde: “Fotopapeletas no van más”</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Al 95.9% de las actas contabilizadas por la ONPE, el candidato Miguel Cueva Celi de Somos Perú, encabeza con un 20.2 % los votos de las preferencias para la Alcaldía provincial de Piura, seguido por el candidato de Podemos Perú Walther Guerrero con un 18.6% y, relegado en un tercer lugar, el candidato de Alianza para el Progreso Jorge Flores Bazán con un 18.1%. PUEDES LEER ► Joven de 20 años purgará condena en la cárcel por fraude informático de S/27 mil soles Con este porcentaje de votos a su favor y contabilizando las actas que tienen en su poder, el empresario Miguel Cueva Celi fue tajante en señalar que no peligra su elección. Por ello agradeció el respaldo popular y fue enfático en señalar que apenas ocupe el cargo tomará medidas drásticas en tres ejes importantes: el sector transporte, comercio informal en el Complejo de Mercado y reconstrucción de las pistas del centro de Piura. POZO DE TORMENTAS NO VA Sobre la obra de reconstucción de pistas del centro de la ciudad, fue tajante en señalar que, “definitivamente, no autorizará la construcción del pozo de tormentas” en la plazuela Tres Culturas, como lo contempla el expediente técnico y ha sido rechazado por un sector de la población. “Definitivamente no va, no estamos en estos momentos para estar con engreimientos”, remarcó Cueva Celi, quien agregó que una alternativa para la evacuación de las aguas pluviales podría ser los reservorios satélites. Asimismo dijo que no dará autorización para que a “diestra y siniestra se sigan abriendo calles” para los trabajos de reconstrucción de las pistas, en tanto no culminen las ya iniciadas. FOTOPAPELETAS Sobre el sector transporte advirtió que se impondrá autoridad para recuperar el orden. En diálogo con La Hora también aseguró que apenas asuma la gestión dispondrá la nulidad de las fotopapeletas. “Yo inmediamente lo voy a suspender, el tema legal ya verá para que se anulen [las multas aplicadas]. Definitivamente se anula, no va, está mal”, remarcó Cueva Celi quien dijo que la gestión saliente se ha precipitado con la ordenanza emitida por considerar que no se daban las condiciones para aplicar las fotopapeletas. AMBULANTES Sobre el caso del comercio informal del Complejo de Mercados dijo que pondrá en marcha un plan de reordenamiento, el cual ejecutará después del fenómeno El Niño y sin posibilidades de que los ambulantes regresen a invadir las vías públicas.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/virtual-alcalde-fotopapeletas-no-van-mas/</t>
         </is>
       </c>
     </row>
@@ -1839,21 +1901,21 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sigue la tensión por la segunda vuelta</t>
+          <t>8 de octubre: Combate de Angamos y homenaje a Miguel Grau, el Caballero de los Mares</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sigue la incertidumbre por conocer oficialmente los resultados de la ONPE y saber quién será el contrincante que acompañará al candidato Reynaldo Hilbck en la segunda vuelta electoral, que se llevará a cabo el próximo 29 de noviembre. Hibck lidera los resultados con un 22.039% que representa a un total de 211,003 votos válidos. Al 96.028% el candidato de Alianza para el Progreso se mantiene como el más votado en la elección regional. PUEDES LEER ► Joven de 20 años purgará condena en la cárcel por fraude informático de S/27 mil soles Disputa en conteo En segundo lugar figura el candidato de Podemos, Guillermo La Torre, con un 18.050% que representa 172,814 votos válidos ; mientras que el candidato Santiago Paz de Somos Perú quedó desplazado al tercer lugar con un 17.822% que representa a 170,626 de los votos válidos. La diferencia entre ambos es de 2,188 votos y aún existen 186 actas observadas. Denuncia sabotaje El candidato Santiago Paz denunció un supuesto sabotaje y anforazo en el proceso electoral. “Lo de San Juan de Bigote fue un sabotaje planeado para anular las mesas donde el pueblo nos dio la victoria, querían borrar los votos, pero fracasaron, las actas ya estaban selladas antes de la violencia. Esos votos están a salvo y darán el triunfo regional”, se pronunció el candidato por sus redes sociales, donde también hizo un llamado a la Fiscalía para que investigue porqué no les quisieron entregar las actas del proceso. “Se debe investigar porqué al personero no se le dio copia del acta, eso nos quita la única prueba para probar que los votos que salgan del colegio son los que llegan al centro de cómputo. Así es cómo se hacen los famosos anforazos y tenemos que tener cuidado”, expresó el candidato quien agregó que pasará a segunda vuelta.</t>
+          <t>Cada 8 de octubre , el Perú conmemora una de las fechas más representativas de su historia republicana. La jornada recuerda el Combate Naval de Angamos , ocurrido en 1879 durante la Guerra del Pacífico, y rinde homenaje al almirante Miguel Grau Seminario , quien murió durante aquel enfrentamiento mientras comandaba el monitor Huáscar. La fecha también está vinculada con la creación de la Marina de Guerra del Perú , institución que nació en los primeros años de la República y que, desde entonces, cumple funciones relacionadas con la defensa y protección de los espacios marítimos, fluviales y lacustres del país. A 147 años del Combate de Angamos, la figura de Grau continúa ocupando un lugar central en la memoria nacional. Su actuación durante la Guerra del Pacífico, caracterizada por el valor demostrado en combate y el respeto hacia sus adversarios, contribuyó a consolidar su imagen como uno de los principales héroes de la historia peruana. La creación de la Marina de Guerra del Perú La Marina de Guerra del Perú fue creada el 8 de octubre de 1821, durante el proceso de consolidación de la independencia nacional. El general José de San Martín impulsó la organización de una fuerza naval que permitiera proteger las costas y contribuir al control de las rutas marítimas. El primer comandante de la institución fue el marino británico Martín Jorge Guise , quien tuvo la responsabilidad de organizar las primeras fuerzas navales de la naciente República. Con el transcurso de los años, la Marina amplió sus responsabilidades. Actualmente, además de participar en tareas relacionadas con la defensa nacional, desarrolla labores de búsqueda y rescate , vigilancia de los espacios acuáticos, protección ambiental y apoyo a poblaciones ubicadas en zonas alejadas del territorio peruano. El Combate de Angamos y la muerte de Miguel Grau El 8 de octubre de 1879 , el monitor Huáscar, bajo el mando de Miguel Grau Seminario , enfrentó a una escuadra de la Armada de Chile en aguas cercanas a Punta Angamos. El enfrentamiento fue determinante para el desarrollo de la Guerra del Pacífico. Durante el combate, un proyectil impactó en la torre de mando del Huáscar y provocó la muerte de Grau. Tras varias horas de enfrentamiento, el monitor peruano fue capturado por las fuerzas chilenas. La pérdida del Huáscar significó un duro golpe para la capacidad naval peruana. La posterior supremacía marítima de Chile permitió facilitar el desplazamiento de tropas y recursos durante las siguientes etapas del conflicto. Sin embargo, la importancia histórica de Grau trascendió el resultado militar. Su conducta durante la guerra y el trato que brindó a sus adversarios contribuyeron a que fuera reconocido como el Caballero de los Mares , una denominación que permanece asociada a su figura hasta la actualidad. El legado de Grau permanece en la memoria nacional El homenaje que cada año se realiza el 8 de octubre no se limita a recordar un enfrentamiento militar. También representa una oportunidad para reflexionar sobre valores como el honor, la disciplina, el valor, la responsabilidad y el servicio al país . La figura de Miguel Grau se mantiene como un referente de entrega y compromiso con el deber. Su legado ha trascendido generaciones y continúa formando parte de la identidad histórica de la Marina y de la nación peruana. En esta fecha también se recuerda a los hombres y mujeres que, desde diferentes ámbitos, dedican sus capacidades al servicio de la población y a la protección de la vida. El Huáscar, un patrimonio histórico de la Guerra del Pacífico Después del Combate de Angamos, el monitor Huáscar pasó a formar parte de la Armada de Chile. Décadas después, la embarcación fue restaurada con el objetivo de recuperar características similares a las que tenía antes de la Guerra del Pacífico. El 8 de octubre de 1952 fue inaugurado como Museo Histórico Naval Huáscar , en Talcahuano, Chile. El buque conserva espacios, objetos y elementos vinculados con la historia naval del conflicto y con personajes como Miguel Grau, Arturo Prat y Manuel Thomson. Actualmente, el Huáscar es considerado una pieza de gran valor histórico y patrimonial. Su permanencia como museo permite conocer parte de la historia marítima de Chile y Perú y mantiene vigente el recuerdo de uno de los episodios más importantes de la Guerra del Pacífico. A 147 años del Combate de Angamos , el Perú recuerda a Miguel Grau y a los héroes del mar, destacando una enseñanza que permanece vigente: servir a la patria implica compromiso, responsabilidad y disposición para defender y proteger a los demás .</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/sigue-la-tension-por-la-segunda-vuelta/</t>
+          <t>https://eltiempo.pe/tendencias/8-de-octubre-combate-de-angamos-y-homenaje-a-miguel-grau-el-caballero-de-los-mares/</t>
         </is>
       </c>
     </row>
@@ -1864,21 +1926,21 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chulucanas: Sujeto asesina a su esposa por celos</t>
+          <t>Piura: Amplian detención a investigado por feminicidio de madre de familia en Chulucanas</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Una mujer de 32 años perdió la vida en circunstancias que son investigadas por las autoridades , en un presunto caso de feminicidio ocurrido en el caserío Platanal Bajo, jurisdicción del distrito de Chulucanas, provincia de Morropón. La víctima fue identificada como Leydi Maribel Gonza Chuica, quien deja en la orfandad a una niña de 3 años y un niño de 12. PUEDES LEER ► Virtual alcalde de Piura: “Vamos a recuperar la autoridad en la ciudad” El hecho se registró durante la madrugada de ayer martes, en el interior de la vivienda donde la mujer residía junto a su pareja, Guido A. C., de 34 años, quien es investigado como presunto autor del crimen. De acuerdo con la información proporcionada por familiares, Guido A. habría llamado aproximadamente a la 1:35 de la madrugada al padre de Leydi, Enrique Gonza Salvador, para decirle que “cuiden a mis hijos” . Posteriormente, el hombre habría comunicado lo ocurrido a su propia madre, quien alertó a la familia de la víctima. Ante la preocupación, los familiares acudieron inicialmente hacia el río Yapatera, debido a que el sospechoso se habría dirigido hacia ese sector. Sin embargo, no encontraron al sospechoso, ni a la víctima. Al retornar a la vivienda, ubicaron a Guido A. y le preguntaron por Leydi , quien, según la versión familiar, les indicó que ella se encontraba en la casa. SIN SIGNOS VITALES Al ingresar al inmueble encontraron a la mujer tendida sobre una cama y sin signos vitales. Familiares señalaron que presentaba marcas en el cuello, por lo que se presume que habría sido víctima de estrangulamiento. Tras regresar a su vivienda, el presunto homicida fue intervenido por efectivos policiales, luego de que el teniente gobernador alertara a las autoridades. Según la información preliminar, el hombre se habría entregado consciente de lo ocurrido. Inicialmente fue trasladado a la comisaría de Yapatera y posteriormente a la dependencia policial de Chulucanas , donde permanece en calidad de detenido e investigado. CELOS ASESINOS El padre de la víctima manifestó que la pareja habría tenido problemas debido a los celos del investigado, quien aparentemente habría cuestionado mensajes que Leydi recibía en su teléfono celular. Gonza Salvador pidió justicia para su hija y una sanción conforme a ley para quien resulte responsable. “Pedimos justicia para mi hija y que el responsable reciba una sanción ejemplar” , expresó.</t>
+          <t>Poder Judicial dispuso el plazo de siete días para que se realicen todas las diligencias con relación a crimen de la madre de sus 2 hijos. Por un plazo de siete días será investigado G. B. A. C., de 32 años , luego que el Poder Judicial ordenara dicha medida solicitado por la Fiscalía Especializada en Delitos de Violencia Contra la Mujer de Morropón. El detenido es sindicado del presunto delito de feminicidio. LEE MÁS ► Elecciones 2026 en la región Piura: así quedó el panorama político de los próximos cuatro años Durante la audiencia correspondiente, el fiscal provincial Eriksson Daniel Burga Villa presentó elementos razonables para considerar que el denunciado estaría involucrado en la muerte de su conviviente y madre de sus dos hijos, Leydi Maribel Gonza Chuica, en la vivienda conyugal ubicada en el caserío Platanal Bajo, distrito de Chulucanas . Violento episodio De acuerdo con las diligencias preliminares, el investigado habría sujetado del cuello a su pareja hasta provocarle la muerte, motivado presuntamente por celos, posteriormente, se habría comunicado con la madre de la víctima mortal, así como con los efectivos de la Comisaria de Chulucanas , dando cuenta a la Comisaría de Yapatera, quienes llegan al lugar y lo detienen. Con esta decisión judicial, la fiscalía continuará desarrollando los actos de investigación necesarios para esclarecer los hechos, determinar la participación del involucrado y sustentar las acciones penales que correspondan conforme a ley. Madre trabajadora Como se conoce, Leydi Gonza trabajaba en una planta agroindustrial dedicada a la producción de uva. Se sabe que el detenido constantemente la celaba por lo que siempre tenían problemas en casa. Las discusiones los llevaron a una separación temporal. Allegados a la víctima mortal indican que siempre discutía con el padre de sus dos hijos, pero luego se amistaban y continuaba la relación tormentosa que tuvo un trágico final en la vivienda familiar. Piden justicia Los padres de Leydi Gonza exigen a las autoridades una exhaustiva investigación a fin de conocer la verdad y reciba una drástica condena por la muerte de la madre de sus hijos menores. Debes Saber ■ De acuerdo a las investigaciones, el detenido cerca de la 1:35 de la madrugada llamó al padre de Leydi Gonza para indicarle que cuidara a sus dos hijos. ■ Agentes de la Comisaría de Chulucanas alertados del trágico suceso se desplazaron hasta el caserío Platanal Bajo para detener al principal sospechoso.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/chulucanas-sujeto-asesina-a-su-esposa-por-celos/</t>
+          <t>https://eltiempo.pe/local/piura-amplian-detencion-a-investigado-por-feminicidio-de-madre-de-familia-en-chulucanas/</t>
         </is>
       </c>
     </row>
@@ -1889,21 +1951,21 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Elecciones 2026 en Piura: Simpatizantes de Somos Perú protestan ante el JEE y exigen conteo de actas de San Juan de Bigote</t>
+          <t>¡Golpe a la delincuencia! Piura: Caen presuntos integrantes de banda criminal «La Gran Sangre»</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PIURA. Decenas de militantes y simpatizantes del partido político Somos Perú se concentraron en las afueras del local del Jurado Electoral Especial (JEE) de Piura , ubicado en la urbanización Cuatro de Enero, para exigir celeridad y transparencia en el escrutinio de las Elecciones Regionales 2026 . Con banderolas, megáfonos y arengas como “¡No al fraude!” y “¡El pueblo se respeta!” , los manifestantes reclamaron que se respeten los votos emitidos en la provincia de Morropón. Puedes Leer | Conteo de infarto para definir pase a la segunda vuelta La protesta busca asegurar el ingreso de su candidato regional, el Ing. Santiago Paz , a la segunda vuelta electoral. De acuerdo con las actas contabilizadas hasta el momento por los organismos electorales, el primer lugar de la contienda lo ocupa Reynaldo Hilbck , mientras que el segundo cupo disputado para la segunda vuelta mantiene una estrecha diferencia de votos entre Somos Perú y la agrupación PODEMOS . Exigen validar y contabilizar actas de San Juan de Bigote El eje central del reclamo se centra en los acontecimientos registrados en el distrito de San Juan de Bigote , donde la jornada electoral del domingo se vio empañada por enfrentamientos y la destrucción parcial de material electoral. Sin embargo, durante la manifestación, los simpatizantes de Somos Perú aseguraron que las actas correspondientes a dicha localidad fueron recuperadas y debidamente selladas por las autoridades electorales. Respeto al voto popular: Los manifestantes sostienen que la contabilización completa de las mesas de San Juan de Bigote dará la ventaja necesaria a Santiago Paz para consolidar su pase a la segunda vuelta. Exigencia a la ONPE y JEE: Exigen que la Oficina Nacional de Procesos Electorales (ONPE) y el JEE actúen con la máxima transparencia e imparcialidad para no vulnerar la voluntad popular. Resguardo policial: La sede del JEE Piura permaneció resguardada por un contingente de la Policía Nacional del Perú (PNP) para prevenir incidentes durante la movilización. Defensoría del Pueblo descarta fraude pero confirma incidencias Ante la escalada de tensión y las denuncias sobre presuntas irregularidades en el recuento, la Defensoría del Pueblo emitió un pronunciamiento tras supervisar el desarrollo del proceso en la región Piura. El organismo constitucional concluyó que no existen pruebas de un fraude electoral . No obstante, la institución confirmó en su reporte de supervisión que sí se registraron graves incidencias e imprevistos en puntos específicos del departamento, destacando los altercados ocurridos en San Juan de Bigote. Actualmente, el Jurado Electoral Especial continúa con la resolución de actas observadas e impugnadas para emitir los resultados oficiales definitivos que determinarán qué candidatos disputarán la gobernación regional de Piura en el balotaje.</t>
+          <t>En una conferencia de prensa brindada en la DIVINCRI Piura, el comando de la Región Policial de Piura ofreció un balance detallado de los operativos desplegados contra la criminalidad organizada y el tráfico ilícito. LEE MÁS ► Piura: Amplian detención a investigado por feminicidio de madre de familia en Chulucanas Desarticulación de ‘La Gran Sangre’: Ataque a sangre fría y captura tras Plan Cerco Uno de los golpes más contundentes fue la captura en flagrancia de cuatro integrantes de la presunta banda criminal «La Gran Sangre», capturados tras asaltar a mano armada a dos ciudadanos (uno colombiano y otro venezolano) dedicados presuntamente al préstamo bajo la modalidad de «gota a gota» en la jurisdicción del distrito Veintiséis de Octubre. Durante el atraco, uno de los maleantes le disparó a quemarropa al ciudadano colombiano. Sobre el ataque, la autoridad policial señaló que «uno de estos sujetos sin piedad le dispara al ciudadano colombiano a sangre fría, al parecer con la finalidad de acabar con su vida. Sin embargo, la bala le cayó en el brazo y se encuentra con lesiones leves». Efectivos de la Comisaría de Veintiséis de Octubre ejecutaron de inmediato el Plan Cerco, logrando la detención de los cuatro delincuentes peruanos y la incautación de una motocicleta blanco con rojo requisitada por robo. El jefe policial detalló que el tirador registra un amplio prontuario. «Uno de ellos presenta gran cantidad de antecedentes policiales. Tiene denuncias y acusaciones fiscales por robo agravado a mano armada, por delito contra el patrimonio de receptación, tráfico de drogas, conducción en estado de ebriedad, entre otros hechos criminales» , señaló. Lucha contra el contrabando, microcomercialización y bandas locales Durante la presentación, la Policía Nacional del Perú dio a conocer otros importantes logros operativos. Resalta la captura de presuntos integrantes de «Los Verduleros del Norte» , en la cual,  Personal de la Depincri Piura, en coordinación con la SUNAT, intervino a la altura del peaje Piura-Sullana un camión con dos sujetos que transportaban 120 mallas plásticas con arveja fresca colombiana de contrabando, incautándose la mercadería y el vehículo valorizados en aproximadamente 120,000 soles. Asimismo, el mando polciial resalto la captura de presuntos integrantes de «Los Pollos de Castilla» , banda desarticulada el 5 de octubre en la zona de Tacalá (Castilla) , decomisándoseles más de 3,300 envoltorios de PBC, tres celulares y una motocicleta. Cifras de producción anual y reducción de la criminalidad En cuanto al balance del presente año, el comando policial, Daniel Jares destacó la realización d e 73,672 operativos policiales , que permitieron la captura en flagrancia de 9,162 personas, la detención de 3,403 requisitoriados, la retención de 517 menores de edad y la desarticulación de 481 bandas criminales. Asimismo, se han decomisado más de 200 armas de fuego, más de 96,000 «ketes» de PBC, 35 kg de PBC a granel y 122 kg de marihuana. Respecto al impacto en la seguridad ciudadana, la autoridad enfatizó la tendencia a la baja en delitos de alto impacto. «Podemos decir que el presente año hemos reducido lo que es robo y hurtos en un 15%, los homicidios en un 1% y en lo que es delito de extorsión un 58%» , concluyó Jares.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/elecciones-2026-en-piura-simpatizantes-de-somos-peru-protestan-ante-el-jee-y-exigen-conteo-de-actas-de-san-juan-de-bigote/</t>
+          <t>https://eltiempo.pe/local/golpe-a-la-delincuencia-piura-caen-presuntos-integrantes-de-banda-criminal-la-gran-sangre/</t>
         </is>
       </c>
     </row>
@@ -1914,28 +1976,28 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sechura: Pescadores bloquearon las pistas exigiendo trato justo</t>
+          <t>Presidenta de la junta de fiscales se pronuncia sobre elecciones en San Juan de Bigote: “La pérdida es del 90% del material y sobre esto no puede haber un resultado”</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Durante las primeras horas de la jornada, cerca de cinco mil pescadores artesanales y armadores de la provincia de Sechura acataron una paralización provincial para hacer sentir su protesta ante la crisis que atraviesa la pesca de la pota. PUEDES LEER ► Joven de 20 años purgará condena en la cárcel por fraude informático de S/27 mil soles La medida de fuerza se ejecutó con el bloqueo de accesos viales y puentes estratégicos como El Melizo, Sechura, Bellavista de La Unión y los tramos hacia Parachique y Bayóvar, recibiendo el respaldo de sectores de la flota anchovetera. Los manifestantes protestaron contra la política punitiva del viceministro de Pesca, Jesús Eloy Barrientos Ruiz, el elevado costo del combustible — que llega a S/29 por galón sin subsidio — y la perjudicial aplicación de la Resolución Ministerial 348. El principal detonante de la protesta fue la regla de dos toneladas de pesca por una de hielo, normativa que según los pescadores beneficia a las embarcaciones de mayor tamaño y que les permitiría descargar hasta 22 toneladas, y generó una sobreoferta en muelle que hizo caer el precio del kilo de pota a S/1.20 y S/1.30. Como parte de las acciones de lucha, la Asociación Unificada de Pescadores Artesanales de la Provincia de Sechura (Asupaps) elevó el Oficio 019-2026 al vicepresidente del Senado, Alejandro Muñante, exigiendo la destitución del viceministro, el control a la flota extranjera fuera de las 200 millas y una reestructuración de Produce. Pasadas las dos de la tarde, los gremios acordaron el levantamiento del paro y procedieron a despejar completamente el tránsito en todos los puentes y carreteras bloqueadas. La decisión de suspender las medidas de fuerza se adoptó tras confirmarse la programación de la Mesa de Diálogo para el próximo viernes 9 de octubre.</t>
+          <t>El candidato de Somos Perú, Santiago Paz , señala que la elección a segunda vuelta la tendrían asegurada con la información que salvaguardó la Fiscalía de Morropón durante los incidentes registrados el domingo último cuando un grupo de personas ingresó a las aulas y destruyó parte del material electoral. LEE MÁS ► Elecciones 2026 en Piura: Simpatizantes de Somos Perú protestan ante el JEE y exigen conteo de actas de San Juan de Bigote De acuerdo al “Acta de verificación fiscal y lacrado de especies” , el fiscal Luis Enrique Venegas Morales deja constancia de lo hallado en las 23 mesas de sufragio , básicamente cédulas de votación, cabinas, ánforas, así como el hallazgo de material electoral roto (cédulas y actas de sufragio). El documento también lleva las firmas de un representante del Ejército, coordinador del local, entre otros. ¿NULIDAD DE ELECCIÓN? Sobre el tema, La Hora entrevistó a la presidenta de la Junta de Fiscales Superiores del Distrito Fiscal de Piura , Faviola Susana Campos Hidalgo, quien dejó en claro que la pérdida del material electoral no fue mínima. “Aproximadamente la pérdida es del 90% del material electoral, lo que ha generado que la Fiscalía se constituya” , informó la representante del Ministerio Público quien agregó que está en manos del JNE tomar una decisión sobre la votación popilar. No obstante, agregó: “Lo oficial es del 90% [del material electoral perdido] y sobre esto no puede haber un resultado en ese local de 23 mesas” , señaló. Asimismo dijo que el JNE y otras entidades del sistema electoral ya han pedido información sobre lo acontecido en San Juan de Bigote. 2 A 8 AÑOS DE CÁRCEL Campos Hidalgo indicó que lo registrado en Morropón se enmarca en delitos contra la voluntad popular por la destrucción del material electoral. Informó que la ley sanciona estos casos con penas punitivas entre 2 a 8 años. Indicó que los videos, testimonios de los miembros de mesa entre otras pruebas serán evidencias para identificar a los responsables.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/sechura-pescadores-bloquearon-las-pistas-exigiendo-trato-justo/</t>
+          <t>https://eltiempo.pe/local/presidenta-de-la-junta-de-fiscales-se-pronuncia-sobre-elecciones-en-san-juan-de-bigote-la-perdida-es-del-90-del-material-y-sobre-esto-no-puede-haber-un-resultado/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gestión</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -1943,17 +2005,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Autopista del Sol lleva más de nueve años esperando entrega de terrenos, advierte Contraloría</t>
+          <t>ODPE Piura culmina al 100% repliegue de material electoral tras las ERM 2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>La Contraloría General de la República (CGR) advirtió que han transcurrido más de nueve años desde que venció el plazo establecido para que el Ministerio de Transportes y Comunicaciones (MTC) entregue al concesionario de la Autopista del Sol las áreas necesarias para ejecutar y culminar la obra obligatoria Evitamiento Chiclayo–Lambayeque (EV-08) – Zona Norte, cuya inversión total asciende a US$ 51.8 millones. El contrato de concesión de la Autopista del Sol, que conecta Trujillo (La Libertad) con Sullana (Piura), fue suscrito el 25 de agosto de 2009 entre el MTC y un concesionario privado. La concesión tiene un plazo de 25 años y contempla una inversión de US$ 733.9 millones, de los cuales US$ 51.8 millones corresponden a la obra Evitamiento (EV-08) – Zona Norte. Este proyecto comprende la Vía de Evitamiento (EV-08), el Puente Lambayeque (EV-08) y el Intercambio Vial Lambayeque (EV-08). Según el Informe de Hito de Control N.° 12035-2026-CG/APP-SCC, elaborado tras una evaluación realizada entre el 14 de agosto y el 2 de setiembre de 2026, la inversión ejecutada reconocida por el Organismo Supervisor de la Inversión en Infraestructura de Transporte de Uso Público (Ositran), al 31 de julio de 2026, alcanzaba US$ 21.6 millones en la obra Evitamiento (EV-08), US$ 1.05 millones en el Puente Lambayeque y US$ 3.09 millones en el Intercambio Vial Lambayeque. De acuerdo con las condiciones establecidas en el contrato de concesión, el MTC, en su calidad de concedente, debía entregar al concesionario las áreas requeridas para la ejecución de la obra como máximo el 30 de agosto de 2017. Para verificar el cumplimiento de esta obligación, la Contraloría solicitó información sobre la entrega parcial o integral de las áreas involucradas. Como parte de la documentación recibida, se encuentra el Acta de Trato Directo acordada entre el concedente y el concesionario, que estableció tres etapas para la entrega de los terrenos. A la fecha de la evaluación, las dos primeras ya habían sido cumplidas. Sin embargo, al mes de setiembre permanecía pendiente la entrega de 83 predios para la ejecución de la obra. De este total, 52 ya habían sido adquiridos o transferidos y estaban inscritos registralmente a favor del MTC; 17 predios privados aún no habían sido adquiridos o transferidos; dos predios privados tenían pagos con mejoras; y en 12 casos no existía documentación que permitiera determinar su situación. La comisión de control también advirtió que el concesionario había ejecutado el tramo correspondiente a la tercera etapa del Acta de Trato Directo sin contar con la totalidad de las áreas entregadas. El MTC señaló que los 83 predios aún no habían sido entregados debido a la existencia de interferencias. No obstante, la Contraloría constató que todavía faltaba adquirir 29 predios. En una inspección realizada el 15 de julio de 2026 en la zona de la obra, los auditores identificaron seis interferencias. Una de ellas, correspondiente a una red eléctrica, ya fue liberada. Por ello, permanecen pendientes cinco interferencias: dos redes de telecomunicaciones, un pozo séptico, una red eléctrica y una red de gas natural. La Contraloría señaló que estas situaciones afectan la culminación de la obra y limitan el uso de la infraestructura vial por parte de los usuarios. Ante ello, recomendó comunicar las situaciones advertidas a la directora de la Dirección de Programas y Proyectos en Transportes del MTC y a la presidenta del Consejo Directivo del Ositran, con el objetivo de que adopten acciones correctivas urgentes que permitan culminar la obra y ponerla al servicio de la población beneficiaria.</t>
+          <t>La Oficina Descentralizada de Procesos Electorales (ODPE) Piura culminó al 100 % el repliegue del material electoral utilizado en los distritos de Piura y Veintiséis de Octubre durante las Elecciones Regionales y Municipales (ERM) 2026. PUEDES LEER ► Sullana: Policía resulta herido durante intervención El proceso se realizó luego de culminar el escrutinio de las mesas de sufragio instaladas en los locales de votación, como parte de las labores logísticas posteriores a la jornada electoral del domingo 4 de octubre. Para el traslado, las unidades de transporte terrestre retornaron el material electoral desde los centros de votación hasta la sede de la ODPE Piura. El operativo se desarrolló bajo medidas de seguridad y contó con el resguardo permanente de efectivos de la Policía Nacional del Perú (PNP) y el acompañamiento de representantes del Jurado Electoral Especial (JEE) Piura . En los distritos de Piura y Veintiséis de Octubre se habilitaron 67 locales de votación, donde fueron instaladas 884 mesas de sufragio para atender a un total de 264 089 electores habilitados durante las ERM 2026. El jefe de la ODPE Piura, Juan Roel Godofredo Valdivia , explicó que el repliegue respondió a una planificación logística previamente establecida. Precisó que el retorno del material no se realizó de manera simultánea, debido a que los tiempos dependieron del avance del escrutinio efectuado por los miembros de mesa en cada local. Por ello, el traslado se desarrolló de manera escalonada , conforme fueron culminando las actividades electorales en los distintos puntos de votación. Asimismo, Valdivia señaló que se garantizó la seguridad durante el traslado del material y el retorno del personal de la ONPE y el JNE , mediante la coordinación con las Fuerzas Armadas y la Policía Nacional del Perú. De esta manera, la ODPE Piura completó el repliegue del material electoral correspondiente a los distritos de Piura y Veintiséis de Octubre, como parte de las actividades posteriores a las Elecciones Regionales y Municipales 2026.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://gestion.pe/peru/autopista-del-sol-lleva-mas-de-nueve-anos-esperando-entrega-de-terrenos-advierte-contraloria-noticia/</t>
+          <t>https://eltiempo.pe/local/odpe-piura-culmina-al-100-repliegue-de-material-electoral-tras-las-erm-2026/</t>
         </is>
       </c>
     </row>
@@ -1968,24 +2030,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sullana: Policía resulta herido durante intervención</t>
+          <t>Elecciones 2026 en Piura: Simpatizantes de Somos Perú protestan ante el JEE y exigen conteo de actas de San Juan de Bigote</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Una intervención por un caso de violencia familiar terminó con un policía herido en la cabeza luego de recibir una pedrada cuando intervenía a un hombre denunciado por agredir físicamente a su propia hermana. El hecho ocurrió en el distrito de Querecotillo, provincia de Sullana. PUEDES LEER ► Atropellan a peregrinos cuando se iban a Ayabaca Los agentes de la comisaría de Querecotillo llegaron hasta la calle Alfonso Ugarte tras recibir una alerta sobre un caso de violencia familiar. Allí encontraron a la agraviada, identificada con las iniciales F. R. J., quien denunció que su hermano E. R. J., presuntamente en aparente estado de ebriedad, la había agredido con golpes de puño y también con el palo de una escoba. La mujer indicó que el ataque se produjo pese a que el denunciado tenía prohibido acercarse a ella, debido a que cuenta con medidas de protección dictadas a su favor. Ante la denuncia, los policías procedieron a intervenir y detener al presunto agresor en flagrancia. Sin embargo, cuando los agentes lo trasladaban hacia el patrullero, otro sujeto intentó impedir la detención y lanzó una piedra contra los efectivos. La piedra impactó directamente en la cabeza de uno de los policías, provocándole una herida que comenzó a sangrar. Ante esta situación, los agentes procedieron también a intervenir al agresor, quien fue trasladado a la comisaría de Querecotillo junto con el primer detenido. Cabe mencionar que el segundo intervenido será investigado por los presuntos delitos de desobediencia y resistencia a la autoridad, daños materiales y lesiones en agravio del efectivo policial.</t>
+          <t>PIURA. Decenas de militantes y simpatizantes del partido político Somos Perú se concentraron en las afueras del local del Jurado Electoral Especial (JEE) de Piura , ubicado en la urbanización Cuatro de Enero, para exigir celeridad y transparencia en el escrutinio de las Elecciones Regionales 2026 . Con banderolas, megáfonos y arengas como “¡No al fraude!” y “¡El pueblo se respeta!” , los manifestantes reclamaron que se respeten los votos emitidos en la provincia de Morropón. Puedes Leer | Conteo de infarto para definir pase a la segunda vuelta La protesta busca asegurar el ingreso de su candidato regional, el Ing. Santiago Paz , a la segunda vuelta electoral. De acuerdo con las actas contabilizadas hasta el momento por los organismos electorales, el primer lugar de la contienda lo ocupa Reynaldo Hilbck , mientras que el segundo cupo disputado para la segunda vuelta mantiene una estrecha diferencia de votos entre Somos Perú y la agrupación PODEMOS . Exigen validar y contabilizar actas de San Juan de Bigote El eje central del reclamo se centra en los acontecimientos registrados en el distrito de San Juan de Bigote , donde la jornada electoral del domingo se vio empañada por enfrentamientos y la destrucción parcial de material electoral. Sin embargo, durante la manifestación, los simpatizantes de Somos Perú aseguraron que las actas correspondientes a dicha localidad fueron recuperadas y debidamente selladas por las autoridades electorales. Respeto al voto popular: Los manifestantes sostienen que la contabilización completa de las mesas de San Juan de Bigote dará la ventaja necesaria a Santiago Paz para consolidar su pase a la segunda vuelta. Exigencia a la ONPE y JEE: Exigen que la Oficina Nacional de Procesos Electorales (ONPE) y el JEE actúen con la máxima transparencia e imparcialidad para no vulnerar la voluntad popular. Resguardo policial: La sede del JEE Piura permaneció resguardada por un contingente de la Policía Nacional del Perú (PNP) para prevenir incidentes durante la movilización. Defensoría del Pueblo descarta fraude pero confirma incidencias Ante la escalada de tensión y las denuncias sobre presuntas irregularidades en el recuento, la Defensoría del Pueblo emitió un pronunciamiento tras supervisar el desarrollo del proceso en la región Piura. El organismo constitucional concluyó que no existen pruebas de un fraude electoral . No obstante, la institución confirmó en su reporte de supervisión que sí se registraron graves incidencias e imprevistos en puntos específicos del departamento, destacando los altercados ocurridos en San Juan de Bigote. Actualmente, el Jurado Electoral Especial continúa con la resolución de actas observadas e impugnadas para emitir los resultados oficiales definitivos que determinarán qué candidatos disputarán la gobernación regional de Piura en el balotaje.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/sullana-policia-resulta-herido-durante-intervencion/</t>
+          <t>https://eltiempo.pe/local/elecciones-2026-en-piura-simpatizantes-de-somos-peru-protestan-ante-el-jee-y-exigen-conteo-de-actas-de-san-juan-de-bigote/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Gestión</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -1993,17 +2055,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Por un mes, El Alto no tendrá servicio de agua</t>
+          <t>Autopista del Sol lleva más de nueve años esperando entrega de terrenos, advierte Contraloría</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Los vecinos del distrito de El Alto no contarán con el servicio de agua potable durante 30 días debido a la complejidad en los trabajos que se realizan para reparar el eje principal que conforma la Estación 74, siendo insuficiente el abasteciendo del recurso hídricos a las viviendas a través de camiones cisternas. PUEDES LEER ► Sullana: Policía resulta herido durante intervención Fue el propio gerente de la EPS Grau, Pool Mogollón, quien durante una reunión en las oficinas de Talara con el virtual alcalde del distrito alteño, Jimmy Montalván Campaña , confirmó que la bomba principal de la estación mencionada se encuentra malograda y su reparación tomará aproximadamente 30 días, abasteciendo de agua potable a la población a través de camiones cisternas, las mismas que son insuficientes. Ante la difícil situación hídrica que atraviesa el pueblo alteño, tanto la EPS Grau como el electo alcalde del distrito se comprometieron en coordinar con algunas empresas privadas para incrementar el número de vehículos que permitan garantizar el abastecimiento inmediato mediante camiones cisterna para todas las familias alteñas, quienes por el momento se les otorga dos cilindros cada dos o tres días. El pasado 2 de octubre la EPS Grau comunicó sobre la rotura del eje principal de la bomba ubicada en la Estación N° 74, razón por la cual se restringe la distribución de agua potable en el distrito. Ello ocasionó que los presidentes de las juntas vecinales pidieran una audiencia pública para conformar una junta o un comité de usuarios para fiscalizar a la EPS. Mientras que la EPS Grau y representantes del Fondo de Desarrollo Social (FDS) del Lote X coordinan la urgente suscripción de un convenio.</t>
+          <t>La Contraloría General de la República (CGR) advirtió que han transcurrido más de nueve años desde que venció el plazo establecido para que el Ministerio de Transportes y Comunicaciones (MTC) entregue al concesionario de la Autopista del Sol las áreas necesarias para ejecutar y culminar la obra obligatoria Evitamiento Chiclayo–Lambayeque (EV-08) – Zona Norte, cuya inversión total asciende a US$ 51.8 millones. El contrato de concesión de la Autopista del Sol, que conecta Trujillo (La Libertad) con Sullana (Piura), fue suscrito el 25 de agosto de 2009 entre el MTC y un concesionario privado. La concesión tiene un plazo de 25 años y contempla una inversión de US$ 733.9 millones, de los cuales US$ 51.8 millones corresponden a la obra Evitamiento (EV-08) – Zona Norte. Este proyecto comprende la Vía de Evitamiento (EV-08), el Puente Lambayeque (EV-08) y el Intercambio Vial Lambayeque (EV-08). Según el Informe de Hito de Control N.° 12035-2026-CG/APP-SCC, elaborado tras una evaluación realizada entre el 14 de agosto y el 2 de setiembre de 2026, la inversión ejecutada reconocida por el Organismo Supervisor de la Inversión en Infraestructura de Transporte de Uso Público (Ositran), al 31 de julio de 2026, alcanzaba US$ 21.6 millones en la obra Evitamiento (EV-08), US$ 1.05 millones en el Puente Lambayeque y US$ 3.09 millones en el Intercambio Vial Lambayeque. De acuerdo con las condiciones establecidas en el contrato de concesión, el MTC, en su calidad de concedente, debía entregar al concesionario las áreas requeridas para la ejecución de la obra como máximo el 30 de agosto de 2017. Para verificar el cumplimiento de esta obligación, la Contraloría solicitó información sobre la entrega parcial o integral de las áreas involucradas. Como parte de la documentación recibida, se encuentra el Acta de Trato Directo acordada entre el concedente y el concesionario, que estableció tres etapas para la entrega de los terrenos. A la fecha de la evaluación, las dos primeras ya habían sido cumplidas. Sin embargo, al mes de setiembre permanecía pendiente la entrega de 83 predios para la ejecución de la obra. De este total, 52 ya habían sido adquiridos o transferidos y estaban inscritos registralmente a favor del MTC; 17 predios privados aún no habían sido adquiridos o transferidos; dos predios privados tenían pagos con mejoras; y en 12 casos no existía documentación que permitiera determinar su situación. La comisión de control también advirtió que el concesionario había ejecutado el tramo correspondiente a la tercera etapa del Acta de Trato Directo sin contar con la totalidad de las áreas entregadas. El MTC señaló que los 83 predios aún no habían sido entregados debido a la existencia de interferencias. No obstante, la Contraloría constató que todavía faltaba adquirir 29 predios. En una inspección realizada el 15 de julio de 2026 en la zona de la obra, los auditores identificaron seis interferencias. Una de ellas, correspondiente a una red eléctrica, ya fue liberada. Por ello, permanecen pendientes cinco interferencias: dos redes de telecomunicaciones, un pozo séptico, una red eléctrica y una red de gas natural. La Contraloría señaló que estas situaciones afectan la culminación de la obra y limitan el uso de la infraestructura vial por parte de los usuarios. Ante ello, recomendó comunicar las situaciones advertidas a la directora de la Dirección de Programas y Proyectos en Transportes del MTC y a la presidenta del Consejo Directivo del Ositran, con el objetivo de que adopten acciones correctivas urgentes que permitan culminar la obra y ponerla al servicio de la población beneficiaria.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/por-un-mes-el-alto-no-tendra-servicio-de-agua/</t>
+          <t>https://gestion.pe/peru/autopista-del-sol-lleva-mas-de-nueve-anos-esperando-entrega-de-terrenos-advierte-contraloria-noticia/</t>
         </is>
       </c>
     </row>
@@ -2018,17 +2080,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ODPE Piura culmina al 100% repliegue de material electoral tras las ERM 2026</t>
+          <t>Por un mes, El Alto no tendrá servicio de agua</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>La Oficina Descentralizada de Procesos Electorales (ODPE) Piura culminó al 100 % el repliegue del material electoral utilizado en los distritos de Piura y Veintiséis de Octubre durante las Elecciones Regionales y Municipales (ERM) 2026. PUEDES LEER ► Sullana: Policía resulta herido durante intervención El proceso se realizó luego de culminar el escrutinio de las mesas de sufragio instaladas en los locales de votación, como parte de las labores logísticas posteriores a la jornada electoral del domingo 4 de octubre. Para el traslado, las unidades de transporte terrestre retornaron el material electoral desde los centros de votación hasta la sede de la ODPE Piura. El operativo se desarrolló bajo medidas de seguridad y contó con el resguardo permanente de efectivos de la Policía Nacional del Perú (PNP) y el acompañamiento de representantes del Jurado Electoral Especial (JEE) Piura . En los distritos de Piura y Veintiséis de Octubre se habilitaron 67 locales de votación, donde fueron instaladas 884 mesas de sufragio para atender a un total de 264 089 electores habilitados durante las ERM 2026. El jefe de la ODPE Piura, Juan Roel Godofredo Valdivia , explicó que el repliegue respondió a una planificación logística previamente establecida. Precisó que el retorno del material no se realizó de manera simultánea, debido a que los tiempos dependieron del avance del escrutinio efectuado por los miembros de mesa en cada local. Por ello, el traslado se desarrolló de manera escalonada , conforme fueron culminando las actividades electorales en los distintos puntos de votación. Asimismo, Valdivia señaló que se garantizó la seguridad durante el traslado del material y el retorno del personal de la ONPE y el JNE , mediante la coordinación con las Fuerzas Armadas y la Policía Nacional del Perú. De esta manera, la ODPE Piura completó el repliegue del material electoral correspondiente a los distritos de Piura y Veintiséis de Octubre, como parte de las actividades posteriores a las Elecciones Regionales y Municipales 2026.</t>
+          <t>Los vecinos del distrito de El Alto no contarán con el servicio de agua potable durante 30 días debido a la complejidad en los trabajos que se realizan para reparar el eje principal que conforma la Estación 74, siendo insuficiente el abasteciendo del recurso hídricos a las viviendas a través de camiones cisternas. PUEDES LEER ► Sullana: Policía resulta herido durante intervención Fue el propio gerente de la EPS Grau, Pool Mogollón, quien durante una reunión en las oficinas de Talara con el virtual alcalde del distrito alteño, Jimmy Montalván Campaña , confirmó que la bomba principal de la estación mencionada se encuentra malograda y su reparación tomará aproximadamente 30 días, abasteciendo de agua potable a la población a través de camiones cisternas, las mismas que son insuficientes. Ante la difícil situación hídrica que atraviesa el pueblo alteño, tanto la EPS Grau como el electo alcalde del distrito se comprometieron en coordinar con algunas empresas privadas para incrementar el número de vehículos que permitan garantizar el abastecimiento inmediato mediante camiones cisterna para todas las familias alteñas, quienes por el momento se les otorga dos cilindros cada dos o tres días. El pasado 2 de octubre la EPS Grau comunicó sobre la rotura del eje principal de la bomba ubicada en la Estación N° 74, razón por la cual se restringe la distribución de agua potable en el distrito. Ello ocasionó que los presidentes de las juntas vecinales pidieran una audiencia pública para conformar una junta o un comité de usuarios para fiscalizar a la EPS. Mientras que la EPS Grau y representantes del Fondo de Desarrollo Social (FDS) del Lote X coordinan la urgente suscripción de un convenio.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/odpe-piura-culmina-al-100-repliegue-de-material-electoral-tras-las-erm-2026/</t>
+          <t>https://eltiempo.pe/local/por-un-mes-el-alto-no-tendra-servicio-de-agua/</t>
         </is>
       </c>
     </row>
@@ -2039,46 +2101,46 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Joven de 20 años purgará condena en la cárcel por fraude informático de S/27 mil soles</t>
+          <t>Sullana: Policía resulta herido durante intervención</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Un joven de 20 años fue sentenciado a 2 años, 2 meses y 20 días de prisión por su participación en un caso de fraude informático que ocasionó un perjuicio de S/27 mil a un ciudadano, en el distrito de Castilla. Puedes Leer | Virtual alcalde de Piura: “Vamos a recuperar la autoridad en la ciudad” La sentencia fue obtenida mediante proceso inmediato por el Tercer Despacho de la Fiscalía Provincial Penal Corporativa de Castilla, a cargo del fiscal provincial Carlos Barboza Campos. Según la investigación fiscal, D. S. D. S. colaboró intencionalmente con el delito al facilitar la transferencia, recepción y traslado de productos tecnológicos adquiridos ilícitamente tras la vulneración de las cuentas y tarjeta bancaria de la víctima. El sentenciado coordinaba el recojo de los equipos mediante repartidores y aplicativos de transporte. Fue intervenido en flagrancia por agentes de la Policía cuando acudió a recibir la mercadería en Castilla.</t>
+          <t>Una intervención por un caso de violencia familiar terminó con un policía herido en la cabeza luego de recibir una pedrada cuando intervenía a un hombre denunciado por agredir físicamente a su propia hermana. El hecho ocurrió en el distrito de Querecotillo, provincia de Sullana. PUEDES LEER ► Atropellan a peregrinos cuando se iban a Ayabaca Los agentes de la comisaría de Querecotillo llegaron hasta la calle Alfonso Ugarte tras recibir una alerta sobre un caso de violencia familiar. Allí encontraron a la agraviada, identificada con las iniciales F. R. J., quien denunció que su hermano E. R. J., presuntamente en aparente estado de ebriedad, la había agredido con golpes de puño y también con el palo de una escoba. La mujer indicó que el ataque se produjo pese a que el denunciado tenía prohibido acercarse a ella, debido a que cuenta con medidas de protección dictadas a su favor. Ante la denuncia, los policías procedieron a intervenir y detener al presunto agresor en flagrancia. Sin embargo, cuando los agentes lo trasladaban hacia el patrullero, otro sujeto intentó impedir la detención y lanzó una piedra contra los efectivos. La piedra impactó directamente en la cabeza de uno de los policías, provocándole una herida que comenzó a sangrar. Ante esta situación, los agentes procedieron también a intervenir al agresor, quien fue trasladado a la comisaría de Querecotillo junto con el primer detenido. Cabe mencionar que el segundo intervenido será investigado por los presuntos delitos de desobediencia y resistencia a la autoridad, daños materiales y lesiones en agravio del efectivo policial.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/joven-de-20-anos-purgara-condena-en-la-carcel-por-fraude-informatico-de-s-27-mil-soles/</t>
+          <t>https://eltiempo.pe/local/sullana-policia-resulta-herido-durante-intervencion/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la región de Piura</t>
+          <t>Chulucanas: Sujeto asesina a su esposa por celos</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Piura, según el conteo oficial de la ONPE al 96.028% , arroja el siguiente resultado (actualizado el 06/10/2026, a las 15:40.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Una mujer de 32 años perdió la vida en circunstancias que son investigadas por las autoridades , en un presunto caso de feminicidio ocurrido en el caserío Platanal Bajo, jurisdicción del distrito de Chulucanas, provincia de Morropón. La víctima fue identificada como Leydi Maribel Gonza Chuica, quien deja en la orfandad a una niña de 3 años y un niño de 12. PUEDES LEER ► Virtual alcalde de Piura: “Vamos a recuperar la autoridad en la ciudad” El hecho se registró durante la madrugada de ayer martes, en el interior de la vivienda donde la mujer residía junto a su pareja, Guido A. C., de 34 años, quien es investigado como presunto autor del crimen. De acuerdo con la información proporcionada por familiares, Guido A. habría llamado aproximadamente a la 1:35 de la madrugada al padre de Leydi, Enrique Gonza Salvador, para decirle que “cuiden a mis hijos” . Posteriormente, el hombre habría comunicado lo ocurrido a su propia madre, quien alertó a la familia de la víctima. Ante la preocupación, los familiares acudieron inicialmente hacia el río Yapatera, debido a que el sospechoso se habría dirigido hacia ese sector. Sin embargo, no encontraron al sospechoso, ni a la víctima. Al retornar a la vivienda, ubicaron a Guido A. y le preguntaron por Leydi , quien, según la versión familiar, les indicó que ella se encontraba en la casa. SIN SIGNOS VITALES Al ingresar al inmueble encontraron a la mujer tendida sobre una cama y sin signos vitales. Familiares señalaron que presentaba marcas en el cuello, por lo que se presume que habría sido víctima de estrangulamiento. Tras regresar a su vivienda, el presunto homicida fue intervenido por efectivos policiales, luego de que el teniente gobernador alertara a las autoridades. Según la información preliminar, el hombre se habría entregado consciente de lo ocurrido. Inicialmente fue trasladado a la comisaría de Yapatera y posteriormente a la dependencia policial de Chulucanas , donde permanece en calidad de detenido e investigado. CELOS ASESINOS El padre de la víctima manifestó que la pareja habría tenido problemas debido a los celos del investigado, quien aparentemente habría cuestionado mensajes que Leydi recibía en su teléfono celular. Gonza Salvador pidió justicia para su hija y una sanción conforme a ley para quien resulte responsable. “Pedimos justicia para mi hija y que el responsable reciba una sanción ejemplar” , expresó.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-region-de-piura-noticia/</t>
+          <t>https://eltiempo.pe/local/chulucanas-sujeto-asesina-a-su-esposa-por-celos/</t>
         </is>
       </c>
     </row>
@@ -2089,21 +2151,21 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Ayabaca (Piura)</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la región de Piura</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Ayabaca, según el conteo oficial de la ONPE al 99.235% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 21:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Piura, según el conteo oficial de la ONPE al 96.028% , arroja el siguiente resultado (actualizado el 06/10/2026, a las 15:40.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-ayabaca-piura-noticia/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-region-de-piura-noticia/</t>
         </is>
       </c>
     </row>
@@ -2118,17 +2180,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Sullana (Piura)</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Ayabaca (Piura)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Sullana, según el conteo oficial de la ONPE al 97.188% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 19:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Ayabaca, según el conteo oficial de la ONPE al 99.235% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 21:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-sullana-piura-noticia/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-ayabaca-piura-noticia/</t>
         </is>
       </c>
     </row>
@@ -2143,17 +2205,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Talara (Piura)</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Sullana (Piura)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Talara, según el conteo oficial de la ONPE al 96.094% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 19:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Sullana, según el conteo oficial de la ONPE al 97.188% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 19:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-talara-piura-noticia/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-sullana-piura-noticia/</t>
         </is>
       </c>
     </row>
@@ -2168,17 +2230,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Piura (Piura)</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Talara (Piura)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Piura, según el conteo oficial de la ONPE al 95.912% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 15:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Talara, según el conteo oficial de la ONPE al 96.094% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 19:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-piura-piura-noticia/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-talara-piura-noticia/</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2255,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Huancabamba (Piura)</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Piura (Piura)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Huancabamba, según el conteo oficial de la ONPE al 98.05% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 13:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Piura, según el conteo oficial de la ONPE al 95.912% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 15:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-huancabamba-piura-noticia/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-piura-piura-noticia/</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2280,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Paita (Piura)</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Huancabamba (Piura)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Paita, según el conteo oficial de la ONPE al 99.14% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 08:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Huancabamba, según el conteo oficial de la ONPE al 98.05% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 13:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-paita-piura-noticia/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-huancabamba-piura-noticia/</t>
         </is>
       </c>
     </row>
@@ -2243,15 +2305,40 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Paita (Piura)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Paita, según el conteo oficial de la ONPE al 99.14% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 08:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-paita-piura-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Sechura (Piura)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Sechura, según el conteo oficial de la ONPE al 99.074% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 08:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-sechura-piura-noticia/</t>
         </is>
